--- a/projects/or-form/or_consumption_form.xlsx
+++ b/projects/or-form/or_consumption_form.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
   <si>
     <t xml:space="preserve">راهنمای فرم ثبت دستکش و اقلام قابل دریافت اتاق عمل</t>
   </si>
@@ -147,13 +147,13 @@
     <t xml:space="preserve">• بیش از ۵ جفت در HIS ثبت نشود. مصرف واقعی بیشتر از ۵ جفت را در فرم بنویسید تا مصرف واقعی معلوم باشد، ولی در HIS فقط ۵ جفت ثبت کنید.</t>
   </si>
   <si>
-    <t xml:space="preserve">• چسب، سرنگ و گاز/باند هم اگر خارج از پک مصرف شود در اتاق عمل قابل دریافت است؛ تعدادش را بنویسید.</t>
+    <t xml:space="preserve">• چسب، سرنگ و گاز هم اگر خارج از پک مصرف شود در اتاق عمل قابل دریافت است و سقف ندارد؛ تعداد را بنویسید و همان تعداد را در HIS ثبت کنید. گاز را به «بسته ۵ عددی گاز استریل ۱۰×۱۰» بنویسید.</t>
   </si>
   <si>
     <t xml:space="preserve">نمونه یک ردیف (در برگه ثبت وارد نکنید)</t>
   </si>
   <si>
-    <t xml:space="preserve">1405/08/03 | پرونده 512340 | اتاق 2 | کوله‌سیستکتومی لاپاراسکوپیک | نیتریل 4 جفت | وینیل 2 جفت → جمع 6، قابل ثبت 5، مازاد 1 | چسب 2 | ثبت در HIS: بله → وضعیت «ثبت‌شده؛ مازاد بر سقف»</t>
+    <t xml:space="preserve">1405/08/03 | پرونده 512340 | اتاق 2 | کوله‌سیستکتومی لاپاراسکوپیک | نیتریل 4 جفت | وینیل 2 جفت → جمع 6، قابل ثبت 5، مازاد 1 | چسب 2، سرنگ 3، گاز 1 بسته | ثبت در HIS: بله → وضعیت «ثبت‌شده؛ مازاد بر سقف»</t>
   </si>
   <si>
     <t xml:space="preserve">راهنمای رنگ: زرد = ورود داده | آبی = محاسبه خودکار | قرمز = نیاز به پیگیری</t>
@@ -184,6 +184,24 @@
   </si>
   <si>
     <t xml:space="preserve">قیمت فروش هر عدد دستکش وینیل (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قیمت فروش هر واحد چسب (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرجع: چسب حصیری ۱۰×۱۰ نوافیکس (کد ۱۱۵۶۸۳)، پرمصرف‌ترین چسب؛ آخرین قیمت فروش HIS ۱۴۰۵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قیمت فروش هر سرنگ (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرجع: سرنگ ۱۰ سی‌سی ویمد (کد ۱۱۹۱۹۴)، پرمصرف‌ترین سرنگ؛ ۵ سی‌سی ۷۸٬۰۱۲ و ۲ سی‌سی ۷۰٬۹۲۱ ریال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قیمت فروش هر بسته گاز (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرجع: گاز ساده استریل ۱۰×۱۰ دولایه، بسته ۵ عددی (کد ۱۲۹۷۱۷)؛ آخرین قیمت فروش HIS ۱۴۰۵</t>
   </si>
   <si>
     <t xml:space="preserve">فرم ثبت مصرف دستکش معاینه و اقلام قابل دریافت — اتاق عمل بیمارستان جم</t>
@@ -228,13 +246,13 @@
     <t xml:space="preserve">مازاد بر سقف (جفت)</t>
   </si>
   <si>
-    <t xml:space="preserve">چسب خارج از پک (عدد)</t>
+    <t xml:space="preserve">چسب خارج از پک (واحد)</t>
   </si>
   <si>
     <t xml:space="preserve">سرنگ خارج از پک (عدد)</t>
   </si>
   <si>
-    <t xml:space="preserve">گاز/باند خارج از پک (عدد)</t>
+    <t xml:space="preserve">گاز استریل خارج از پک (بسته ۵ عددی)</t>
   </si>
   <si>
     <t xml:space="preserve">ثبت در HIS</t>
@@ -244,6 +262,12 @@
   </si>
   <si>
     <t xml:space="preserve">ارزش دستکش قابل ثبت (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارزش چسب، سرنگ و گاز (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جمع ارزش قابل ثبت (ریال)</t>
   </si>
   <si>
     <t xml:space="preserve">وضعیت</t>
@@ -285,10 +309,13 @@
     <t xml:space="preserve">میانگین دستکش به ازای هر عمل (جفت)</t>
   </si>
   <si>
-    <t xml:space="preserve">ارزش قابل ثبتی که در HIS ثبت نشده (ریال)</t>
+    <t xml:space="preserve">گاز استریل خارج از پک (بسته)</t>
   </si>
   <si>
-    <t xml:space="preserve">ارزش‌ها با قیمت‌های برگه «پارامترها» حساب می‌شوند. چسب، سرنگ و گاز/باند خارج از پک هم در اتاق عمل قابل دریافت‌اند (طبق جزوه هتلینگ) و فعلاً فقط شمرده می‌شوند.</t>
+    <t xml:space="preserve">جمع ارزش قابل ثبتی که در HIS ثبت نشده (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارزش‌ها با قیمت‌های برگه «پارامترها» حساب می‌شوند. قیمت چسب، سرنگ و گاز بر اساس پرمصرف‌ترین قلم هر گروه است؛ اگر اتاق عمل قلم دیگری مصرف می‌کند، قیمت را همان‌جا عوض کنید.</t>
   </si>
 </sst>
 </file>
@@ -876,7 +903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -918,7 +945,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -973,6 +1000,39 @@
       </c>
       <c r="C5" s="8" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>181489</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>110813</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>454026</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +1051,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:T303"/>
+  <dimension ref="A1:V303"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1002,84 +1062,91 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="18" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1116,11 +1183,19 @@
         <f aca="false">IF(OR(C4="",N(J4)=0),"",K4*2*(N(H4)*پارامترها!$B$4+N(I4)*پارامترها!$B$5)/J4)</f>
         <v/>
       </c>
-      <c r="S4" s="10" t="str">
+      <c r="S4" s="12" t="str">
+        <f aca="false">IF(C4="","",N(M4)*پارامترها!$B$6+N(N4)*پارامترها!$B$7+N(O4)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T4" s="12" t="str">
+        <f aca="false">IF(C4="","",N(R4)+N(S4))</f>
+        <v/>
+      </c>
+      <c r="U4" s="10" t="str">
         <f aca="false">IF(C4="","",IF(P4&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L4)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T4" s="11"/>
+      <c r="V4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="str">
@@ -1156,11 +1231,19 @@
         <f aca="false">IF(OR(C5="",N(J5)=0),"",K5*2*(N(H5)*پارامترها!$B$4+N(I5)*پارامترها!$B$5)/J5)</f>
         <v/>
       </c>
-      <c r="S5" s="10" t="str">
+      <c r="S5" s="12" t="str">
+        <f aca="false">IF(C5="","",N(M5)*پارامترها!$B$6+N(N5)*پارامترها!$B$7+N(O5)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T5" s="12" t="str">
+        <f aca="false">IF(C5="","",N(R5)+N(S5))</f>
+        <v/>
+      </c>
+      <c r="U5" s="10" t="str">
         <f aca="false">IF(C5="","",IF(P5&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L5)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T5" s="11"/>
+      <c r="V5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="str">
@@ -1196,11 +1279,19 @@
         <f aca="false">IF(OR(C6="",N(J6)=0),"",K6*2*(N(H6)*پارامترها!$B$4+N(I6)*پارامترها!$B$5)/J6)</f>
         <v/>
       </c>
-      <c r="S6" s="10" t="str">
+      <c r="S6" s="12" t="str">
+        <f aca="false">IF(C6="","",N(M6)*پارامترها!$B$6+N(N6)*پارامترها!$B$7+N(O6)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T6" s="12" t="str">
+        <f aca="false">IF(C6="","",N(R6)+N(S6))</f>
+        <v/>
+      </c>
+      <c r="U6" s="10" t="str">
         <f aca="false">IF(C6="","",IF(P6&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L6)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T6" s="11"/>
+      <c r="V6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="str">
@@ -1236,11 +1327,19 @@
         <f aca="false">IF(OR(C7="",N(J7)=0),"",K7*2*(N(H7)*پارامترها!$B$4+N(I7)*پارامترها!$B$5)/J7)</f>
         <v/>
       </c>
-      <c r="S7" s="10" t="str">
+      <c r="S7" s="12" t="str">
+        <f aca="false">IF(C7="","",N(M7)*پارامترها!$B$6+N(N7)*پارامترها!$B$7+N(O7)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T7" s="12" t="str">
+        <f aca="false">IF(C7="","",N(R7)+N(S7))</f>
+        <v/>
+      </c>
+      <c r="U7" s="10" t="str">
         <f aca="false">IF(C7="","",IF(P7&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L7)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T7" s="11"/>
+      <c r="V7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="str">
@@ -1276,11 +1375,19 @@
         <f aca="false">IF(OR(C8="",N(J8)=0),"",K8*2*(N(H8)*پارامترها!$B$4+N(I8)*پارامترها!$B$5)/J8)</f>
         <v/>
       </c>
-      <c r="S8" s="10" t="str">
+      <c r="S8" s="12" t="str">
+        <f aca="false">IF(C8="","",N(M8)*پارامترها!$B$6+N(N8)*پارامترها!$B$7+N(O8)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="12" t="str">
+        <f aca="false">IF(C8="","",N(R8)+N(S8))</f>
+        <v/>
+      </c>
+      <c r="U8" s="10" t="str">
         <f aca="false">IF(C8="","",IF(P8&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L8)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T8" s="11"/>
+      <c r="V8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="str">
@@ -1316,11 +1423,19 @@
         <f aca="false">IF(OR(C9="",N(J9)=0),"",K9*2*(N(H9)*پارامترها!$B$4+N(I9)*پارامترها!$B$5)/J9)</f>
         <v/>
       </c>
-      <c r="S9" s="10" t="str">
+      <c r="S9" s="12" t="str">
+        <f aca="false">IF(C9="","",N(M9)*پارامترها!$B$6+N(N9)*پارامترها!$B$7+N(O9)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T9" s="12" t="str">
+        <f aca="false">IF(C9="","",N(R9)+N(S9))</f>
+        <v/>
+      </c>
+      <c r="U9" s="10" t="str">
         <f aca="false">IF(C9="","",IF(P9&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L9)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T9" s="11"/>
+      <c r="V9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="str">
@@ -1356,11 +1471,19 @@
         <f aca="false">IF(OR(C10="",N(J10)=0),"",K10*2*(N(H10)*پارامترها!$B$4+N(I10)*پارامترها!$B$5)/J10)</f>
         <v/>
       </c>
-      <c r="S10" s="10" t="str">
+      <c r="S10" s="12" t="str">
+        <f aca="false">IF(C10="","",N(M10)*پارامترها!$B$6+N(N10)*پارامترها!$B$7+N(O10)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T10" s="12" t="str">
+        <f aca="false">IF(C10="","",N(R10)+N(S10))</f>
+        <v/>
+      </c>
+      <c r="U10" s="10" t="str">
         <f aca="false">IF(C10="","",IF(P10&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L10)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T10" s="11"/>
+      <c r="V10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="str">
@@ -1396,11 +1519,19 @@
         <f aca="false">IF(OR(C11="",N(J11)=0),"",K11*2*(N(H11)*پارامترها!$B$4+N(I11)*پارامترها!$B$5)/J11)</f>
         <v/>
       </c>
-      <c r="S11" s="10" t="str">
+      <c r="S11" s="12" t="str">
+        <f aca="false">IF(C11="","",N(M11)*پارامترها!$B$6+N(N11)*پارامترها!$B$7+N(O11)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T11" s="12" t="str">
+        <f aca="false">IF(C11="","",N(R11)+N(S11))</f>
+        <v/>
+      </c>
+      <c r="U11" s="10" t="str">
         <f aca="false">IF(C11="","",IF(P11&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L11)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T11" s="11"/>
+      <c r="V11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="str">
@@ -1436,11 +1567,19 @@
         <f aca="false">IF(OR(C12="",N(J12)=0),"",K12*2*(N(H12)*پارامترها!$B$4+N(I12)*پارامترها!$B$5)/J12)</f>
         <v/>
       </c>
-      <c r="S12" s="10" t="str">
+      <c r="S12" s="12" t="str">
+        <f aca="false">IF(C12="","",N(M12)*پارامترها!$B$6+N(N12)*پارامترها!$B$7+N(O12)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T12" s="12" t="str">
+        <f aca="false">IF(C12="","",N(R12)+N(S12))</f>
+        <v/>
+      </c>
+      <c r="U12" s="10" t="str">
         <f aca="false">IF(C12="","",IF(P12&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L12)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T12" s="11"/>
+      <c r="V12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="str">
@@ -1476,11 +1615,19 @@
         <f aca="false">IF(OR(C13="",N(J13)=0),"",K13*2*(N(H13)*پارامترها!$B$4+N(I13)*پارامترها!$B$5)/J13)</f>
         <v/>
       </c>
-      <c r="S13" s="10" t="str">
+      <c r="S13" s="12" t="str">
+        <f aca="false">IF(C13="","",N(M13)*پارامترها!$B$6+N(N13)*پارامترها!$B$7+N(O13)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T13" s="12" t="str">
+        <f aca="false">IF(C13="","",N(R13)+N(S13))</f>
+        <v/>
+      </c>
+      <c r="U13" s="10" t="str">
         <f aca="false">IF(C13="","",IF(P13&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L13)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T13" s="11"/>
+      <c r="V13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="str">
@@ -1516,11 +1663,19 @@
         <f aca="false">IF(OR(C14="",N(J14)=0),"",K14*2*(N(H14)*پارامترها!$B$4+N(I14)*پارامترها!$B$5)/J14)</f>
         <v/>
       </c>
-      <c r="S14" s="10" t="str">
+      <c r="S14" s="12" t="str">
+        <f aca="false">IF(C14="","",N(M14)*پارامترها!$B$6+N(N14)*پارامترها!$B$7+N(O14)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T14" s="12" t="str">
+        <f aca="false">IF(C14="","",N(R14)+N(S14))</f>
+        <v/>
+      </c>
+      <c r="U14" s="10" t="str">
         <f aca="false">IF(C14="","",IF(P14&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L14)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T14" s="11"/>
+      <c r="V14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="str">
@@ -1556,11 +1711,19 @@
         <f aca="false">IF(OR(C15="",N(J15)=0),"",K15*2*(N(H15)*پارامترها!$B$4+N(I15)*پارامترها!$B$5)/J15)</f>
         <v/>
       </c>
-      <c r="S15" s="10" t="str">
+      <c r="S15" s="12" t="str">
+        <f aca="false">IF(C15="","",N(M15)*پارامترها!$B$6+N(N15)*پارامترها!$B$7+N(O15)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T15" s="12" t="str">
+        <f aca="false">IF(C15="","",N(R15)+N(S15))</f>
+        <v/>
+      </c>
+      <c r="U15" s="10" t="str">
         <f aca="false">IF(C15="","",IF(P15&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L15)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T15" s="11"/>
+      <c r="V15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="str">
@@ -1596,11 +1759,19 @@
         <f aca="false">IF(OR(C16="",N(J16)=0),"",K16*2*(N(H16)*پارامترها!$B$4+N(I16)*پارامترها!$B$5)/J16)</f>
         <v/>
       </c>
-      <c r="S16" s="10" t="str">
+      <c r="S16" s="12" t="str">
+        <f aca="false">IF(C16="","",N(M16)*پارامترها!$B$6+N(N16)*پارامترها!$B$7+N(O16)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T16" s="12" t="str">
+        <f aca="false">IF(C16="","",N(R16)+N(S16))</f>
+        <v/>
+      </c>
+      <c r="U16" s="10" t="str">
         <f aca="false">IF(C16="","",IF(P16&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L16)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T16" s="11"/>
+      <c r="V16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="str">
@@ -1636,11 +1807,19 @@
         <f aca="false">IF(OR(C17="",N(J17)=0),"",K17*2*(N(H17)*پارامترها!$B$4+N(I17)*پارامترها!$B$5)/J17)</f>
         <v/>
       </c>
-      <c r="S17" s="10" t="str">
+      <c r="S17" s="12" t="str">
+        <f aca="false">IF(C17="","",N(M17)*پارامترها!$B$6+N(N17)*پارامترها!$B$7+N(O17)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T17" s="12" t="str">
+        <f aca="false">IF(C17="","",N(R17)+N(S17))</f>
+        <v/>
+      </c>
+      <c r="U17" s="10" t="str">
         <f aca="false">IF(C17="","",IF(P17&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L17)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T17" s="11"/>
+      <c r="V17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="str">
@@ -1676,11 +1855,19 @@
         <f aca="false">IF(OR(C18="",N(J18)=0),"",K18*2*(N(H18)*پارامترها!$B$4+N(I18)*پارامترها!$B$5)/J18)</f>
         <v/>
       </c>
-      <c r="S18" s="10" t="str">
+      <c r="S18" s="12" t="str">
+        <f aca="false">IF(C18="","",N(M18)*پارامترها!$B$6+N(N18)*پارامترها!$B$7+N(O18)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T18" s="12" t="str">
+        <f aca="false">IF(C18="","",N(R18)+N(S18))</f>
+        <v/>
+      </c>
+      <c r="U18" s="10" t="str">
         <f aca="false">IF(C18="","",IF(P18&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L18)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T18" s="11"/>
+      <c r="V18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="str">
@@ -1716,11 +1903,19 @@
         <f aca="false">IF(OR(C19="",N(J19)=0),"",K19*2*(N(H19)*پارامترها!$B$4+N(I19)*پارامترها!$B$5)/J19)</f>
         <v/>
       </c>
-      <c r="S19" s="10" t="str">
+      <c r="S19" s="12" t="str">
+        <f aca="false">IF(C19="","",N(M19)*پارامترها!$B$6+N(N19)*پارامترها!$B$7+N(O19)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T19" s="12" t="str">
+        <f aca="false">IF(C19="","",N(R19)+N(S19))</f>
+        <v/>
+      </c>
+      <c r="U19" s="10" t="str">
         <f aca="false">IF(C19="","",IF(P19&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L19)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T19" s="11"/>
+      <c r="V19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="str">
@@ -1756,11 +1951,19 @@
         <f aca="false">IF(OR(C20="",N(J20)=0),"",K20*2*(N(H20)*پارامترها!$B$4+N(I20)*پارامترها!$B$5)/J20)</f>
         <v/>
       </c>
-      <c r="S20" s="10" t="str">
+      <c r="S20" s="12" t="str">
+        <f aca="false">IF(C20="","",N(M20)*پارامترها!$B$6+N(N20)*پارامترها!$B$7+N(O20)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T20" s="12" t="str">
+        <f aca="false">IF(C20="","",N(R20)+N(S20))</f>
+        <v/>
+      </c>
+      <c r="U20" s="10" t="str">
         <f aca="false">IF(C20="","",IF(P20&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L20)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T20" s="11"/>
+      <c r="V20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="str">
@@ -1796,11 +1999,19 @@
         <f aca="false">IF(OR(C21="",N(J21)=0),"",K21*2*(N(H21)*پارامترها!$B$4+N(I21)*پارامترها!$B$5)/J21)</f>
         <v/>
       </c>
-      <c r="S21" s="10" t="str">
+      <c r="S21" s="12" t="str">
+        <f aca="false">IF(C21="","",N(M21)*پارامترها!$B$6+N(N21)*پارامترها!$B$7+N(O21)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T21" s="12" t="str">
+        <f aca="false">IF(C21="","",N(R21)+N(S21))</f>
+        <v/>
+      </c>
+      <c r="U21" s="10" t="str">
         <f aca="false">IF(C21="","",IF(P21&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L21)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T21" s="11"/>
+      <c r="V21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="str">
@@ -1836,11 +2047,19 @@
         <f aca="false">IF(OR(C22="",N(J22)=0),"",K22*2*(N(H22)*پارامترها!$B$4+N(I22)*پارامترها!$B$5)/J22)</f>
         <v/>
       </c>
-      <c r="S22" s="10" t="str">
+      <c r="S22" s="12" t="str">
+        <f aca="false">IF(C22="","",N(M22)*پارامترها!$B$6+N(N22)*پارامترها!$B$7+N(O22)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T22" s="12" t="str">
+        <f aca="false">IF(C22="","",N(R22)+N(S22))</f>
+        <v/>
+      </c>
+      <c r="U22" s="10" t="str">
         <f aca="false">IF(C22="","",IF(P22&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L22)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T22" s="11"/>
+      <c r="V22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="str">
@@ -1876,11 +2095,19 @@
         <f aca="false">IF(OR(C23="",N(J23)=0),"",K23*2*(N(H23)*پارامترها!$B$4+N(I23)*پارامترها!$B$5)/J23)</f>
         <v/>
       </c>
-      <c r="S23" s="10" t="str">
+      <c r="S23" s="12" t="str">
+        <f aca="false">IF(C23="","",N(M23)*پارامترها!$B$6+N(N23)*پارامترها!$B$7+N(O23)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T23" s="12" t="str">
+        <f aca="false">IF(C23="","",N(R23)+N(S23))</f>
+        <v/>
+      </c>
+      <c r="U23" s="10" t="str">
         <f aca="false">IF(C23="","",IF(P23&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L23)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T23" s="11"/>
+      <c r="V23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="str">
@@ -1916,11 +2143,19 @@
         <f aca="false">IF(OR(C24="",N(J24)=0),"",K24*2*(N(H24)*پارامترها!$B$4+N(I24)*پارامترها!$B$5)/J24)</f>
         <v/>
       </c>
-      <c r="S24" s="10" t="str">
+      <c r="S24" s="12" t="str">
+        <f aca="false">IF(C24="","",N(M24)*پارامترها!$B$6+N(N24)*پارامترها!$B$7+N(O24)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T24" s="12" t="str">
+        <f aca="false">IF(C24="","",N(R24)+N(S24))</f>
+        <v/>
+      </c>
+      <c r="U24" s="10" t="str">
         <f aca="false">IF(C24="","",IF(P24&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L24)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T24" s="11"/>
+      <c r="V24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="str">
@@ -1956,11 +2191,19 @@
         <f aca="false">IF(OR(C25="",N(J25)=0),"",K25*2*(N(H25)*پارامترها!$B$4+N(I25)*پارامترها!$B$5)/J25)</f>
         <v/>
       </c>
-      <c r="S25" s="10" t="str">
+      <c r="S25" s="12" t="str">
+        <f aca="false">IF(C25="","",N(M25)*پارامترها!$B$6+N(N25)*پارامترها!$B$7+N(O25)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T25" s="12" t="str">
+        <f aca="false">IF(C25="","",N(R25)+N(S25))</f>
+        <v/>
+      </c>
+      <c r="U25" s="10" t="str">
         <f aca="false">IF(C25="","",IF(P25&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L25)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T25" s="11"/>
+      <c r="V25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="str">
@@ -1996,11 +2239,19 @@
         <f aca="false">IF(OR(C26="",N(J26)=0),"",K26*2*(N(H26)*پارامترها!$B$4+N(I26)*پارامترها!$B$5)/J26)</f>
         <v/>
       </c>
-      <c r="S26" s="10" t="str">
+      <c r="S26" s="12" t="str">
+        <f aca="false">IF(C26="","",N(M26)*پارامترها!$B$6+N(N26)*پارامترها!$B$7+N(O26)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T26" s="12" t="str">
+        <f aca="false">IF(C26="","",N(R26)+N(S26))</f>
+        <v/>
+      </c>
+      <c r="U26" s="10" t="str">
         <f aca="false">IF(C26="","",IF(P26&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L26)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T26" s="11"/>
+      <c r="V26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="str">
@@ -2036,11 +2287,19 @@
         <f aca="false">IF(OR(C27="",N(J27)=0),"",K27*2*(N(H27)*پارامترها!$B$4+N(I27)*پارامترها!$B$5)/J27)</f>
         <v/>
       </c>
-      <c r="S27" s="10" t="str">
+      <c r="S27" s="12" t="str">
+        <f aca="false">IF(C27="","",N(M27)*پارامترها!$B$6+N(N27)*پارامترها!$B$7+N(O27)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T27" s="12" t="str">
+        <f aca="false">IF(C27="","",N(R27)+N(S27))</f>
+        <v/>
+      </c>
+      <c r="U27" s="10" t="str">
         <f aca="false">IF(C27="","",IF(P27&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L27)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T27" s="11"/>
+      <c r="V27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="str">
@@ -2076,11 +2335,19 @@
         <f aca="false">IF(OR(C28="",N(J28)=0),"",K28*2*(N(H28)*پارامترها!$B$4+N(I28)*پارامترها!$B$5)/J28)</f>
         <v/>
       </c>
-      <c r="S28" s="10" t="str">
+      <c r="S28" s="12" t="str">
+        <f aca="false">IF(C28="","",N(M28)*پارامترها!$B$6+N(N28)*پارامترها!$B$7+N(O28)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T28" s="12" t="str">
+        <f aca="false">IF(C28="","",N(R28)+N(S28))</f>
+        <v/>
+      </c>
+      <c r="U28" s="10" t="str">
         <f aca="false">IF(C28="","",IF(P28&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L28)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T28" s="11"/>
+      <c r="V28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="str">
@@ -2116,11 +2383,19 @@
         <f aca="false">IF(OR(C29="",N(J29)=0),"",K29*2*(N(H29)*پارامترها!$B$4+N(I29)*پارامترها!$B$5)/J29)</f>
         <v/>
       </c>
-      <c r="S29" s="10" t="str">
+      <c r="S29" s="12" t="str">
+        <f aca="false">IF(C29="","",N(M29)*پارامترها!$B$6+N(N29)*پارامترها!$B$7+N(O29)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T29" s="12" t="str">
+        <f aca="false">IF(C29="","",N(R29)+N(S29))</f>
+        <v/>
+      </c>
+      <c r="U29" s="10" t="str">
         <f aca="false">IF(C29="","",IF(P29&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L29)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T29" s="11"/>
+      <c r="V29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="str">
@@ -2156,11 +2431,19 @@
         <f aca="false">IF(OR(C30="",N(J30)=0),"",K30*2*(N(H30)*پارامترها!$B$4+N(I30)*پارامترها!$B$5)/J30)</f>
         <v/>
       </c>
-      <c r="S30" s="10" t="str">
+      <c r="S30" s="12" t="str">
+        <f aca="false">IF(C30="","",N(M30)*پارامترها!$B$6+N(N30)*پارامترها!$B$7+N(O30)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T30" s="12" t="str">
+        <f aca="false">IF(C30="","",N(R30)+N(S30))</f>
+        <v/>
+      </c>
+      <c r="U30" s="10" t="str">
         <f aca="false">IF(C30="","",IF(P30&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L30)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T30" s="11"/>
+      <c r="V30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="str">
@@ -2196,11 +2479,19 @@
         <f aca="false">IF(OR(C31="",N(J31)=0),"",K31*2*(N(H31)*پارامترها!$B$4+N(I31)*پارامترها!$B$5)/J31)</f>
         <v/>
       </c>
-      <c r="S31" s="10" t="str">
+      <c r="S31" s="12" t="str">
+        <f aca="false">IF(C31="","",N(M31)*پارامترها!$B$6+N(N31)*پارامترها!$B$7+N(O31)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T31" s="12" t="str">
+        <f aca="false">IF(C31="","",N(R31)+N(S31))</f>
+        <v/>
+      </c>
+      <c r="U31" s="10" t="str">
         <f aca="false">IF(C31="","",IF(P31&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L31)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T31" s="11"/>
+      <c r="V31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="str">
@@ -2236,11 +2527,19 @@
         <f aca="false">IF(OR(C32="",N(J32)=0),"",K32*2*(N(H32)*پارامترها!$B$4+N(I32)*پارامترها!$B$5)/J32)</f>
         <v/>
       </c>
-      <c r="S32" s="10" t="str">
+      <c r="S32" s="12" t="str">
+        <f aca="false">IF(C32="","",N(M32)*پارامترها!$B$6+N(N32)*پارامترها!$B$7+N(O32)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T32" s="12" t="str">
+        <f aca="false">IF(C32="","",N(R32)+N(S32))</f>
+        <v/>
+      </c>
+      <c r="U32" s="10" t="str">
         <f aca="false">IF(C32="","",IF(P32&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L32)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T32" s="11"/>
+      <c r="V32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="str">
@@ -2276,11 +2575,19 @@
         <f aca="false">IF(OR(C33="",N(J33)=0),"",K33*2*(N(H33)*پارامترها!$B$4+N(I33)*پارامترها!$B$5)/J33)</f>
         <v/>
       </c>
-      <c r="S33" s="10" t="str">
+      <c r="S33" s="12" t="str">
+        <f aca="false">IF(C33="","",N(M33)*پارامترها!$B$6+N(N33)*پارامترها!$B$7+N(O33)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T33" s="12" t="str">
+        <f aca="false">IF(C33="","",N(R33)+N(S33))</f>
+        <v/>
+      </c>
+      <c r="U33" s="10" t="str">
         <f aca="false">IF(C33="","",IF(P33&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L33)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T33" s="11"/>
+      <c r="V33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="str">
@@ -2316,11 +2623,19 @@
         <f aca="false">IF(OR(C34="",N(J34)=0),"",K34*2*(N(H34)*پارامترها!$B$4+N(I34)*پارامترها!$B$5)/J34)</f>
         <v/>
       </c>
-      <c r="S34" s="10" t="str">
+      <c r="S34" s="12" t="str">
+        <f aca="false">IF(C34="","",N(M34)*پارامترها!$B$6+N(N34)*پارامترها!$B$7+N(O34)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T34" s="12" t="str">
+        <f aca="false">IF(C34="","",N(R34)+N(S34))</f>
+        <v/>
+      </c>
+      <c r="U34" s="10" t="str">
         <f aca="false">IF(C34="","",IF(P34&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L34)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T34" s="11"/>
+      <c r="V34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="str">
@@ -2356,11 +2671,19 @@
         <f aca="false">IF(OR(C35="",N(J35)=0),"",K35*2*(N(H35)*پارامترها!$B$4+N(I35)*پارامترها!$B$5)/J35)</f>
         <v/>
       </c>
-      <c r="S35" s="10" t="str">
+      <c r="S35" s="12" t="str">
+        <f aca="false">IF(C35="","",N(M35)*پارامترها!$B$6+N(N35)*پارامترها!$B$7+N(O35)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T35" s="12" t="str">
+        <f aca="false">IF(C35="","",N(R35)+N(S35))</f>
+        <v/>
+      </c>
+      <c r="U35" s="10" t="str">
         <f aca="false">IF(C35="","",IF(P35&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L35)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T35" s="11"/>
+      <c r="V35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="str">
@@ -2396,11 +2719,19 @@
         <f aca="false">IF(OR(C36="",N(J36)=0),"",K36*2*(N(H36)*پارامترها!$B$4+N(I36)*پارامترها!$B$5)/J36)</f>
         <v/>
       </c>
-      <c r="S36" s="10" t="str">
+      <c r="S36" s="12" t="str">
+        <f aca="false">IF(C36="","",N(M36)*پارامترها!$B$6+N(N36)*پارامترها!$B$7+N(O36)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T36" s="12" t="str">
+        <f aca="false">IF(C36="","",N(R36)+N(S36))</f>
+        <v/>
+      </c>
+      <c r="U36" s="10" t="str">
         <f aca="false">IF(C36="","",IF(P36&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L36)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T36" s="11"/>
+      <c r="V36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="str">
@@ -2436,11 +2767,19 @@
         <f aca="false">IF(OR(C37="",N(J37)=0),"",K37*2*(N(H37)*پارامترها!$B$4+N(I37)*پارامترها!$B$5)/J37)</f>
         <v/>
       </c>
-      <c r="S37" s="10" t="str">
+      <c r="S37" s="12" t="str">
+        <f aca="false">IF(C37="","",N(M37)*پارامترها!$B$6+N(N37)*پارامترها!$B$7+N(O37)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T37" s="12" t="str">
+        <f aca="false">IF(C37="","",N(R37)+N(S37))</f>
+        <v/>
+      </c>
+      <c r="U37" s="10" t="str">
         <f aca="false">IF(C37="","",IF(P37&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L37)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T37" s="11"/>
+      <c r="V37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="str">
@@ -2476,11 +2815,19 @@
         <f aca="false">IF(OR(C38="",N(J38)=0),"",K38*2*(N(H38)*پارامترها!$B$4+N(I38)*پارامترها!$B$5)/J38)</f>
         <v/>
       </c>
-      <c r="S38" s="10" t="str">
+      <c r="S38" s="12" t="str">
+        <f aca="false">IF(C38="","",N(M38)*پارامترها!$B$6+N(N38)*پارامترها!$B$7+N(O38)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T38" s="12" t="str">
+        <f aca="false">IF(C38="","",N(R38)+N(S38))</f>
+        <v/>
+      </c>
+      <c r="U38" s="10" t="str">
         <f aca="false">IF(C38="","",IF(P38&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L38)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T38" s="11"/>
+      <c r="V38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="str">
@@ -2516,11 +2863,19 @@
         <f aca="false">IF(OR(C39="",N(J39)=0),"",K39*2*(N(H39)*پارامترها!$B$4+N(I39)*پارامترها!$B$5)/J39)</f>
         <v/>
       </c>
-      <c r="S39" s="10" t="str">
+      <c r="S39" s="12" t="str">
+        <f aca="false">IF(C39="","",N(M39)*پارامترها!$B$6+N(N39)*پارامترها!$B$7+N(O39)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T39" s="12" t="str">
+        <f aca="false">IF(C39="","",N(R39)+N(S39))</f>
+        <v/>
+      </c>
+      <c r="U39" s="10" t="str">
         <f aca="false">IF(C39="","",IF(P39&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L39)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T39" s="11"/>
+      <c r="V39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="str">
@@ -2556,11 +2911,19 @@
         <f aca="false">IF(OR(C40="",N(J40)=0),"",K40*2*(N(H40)*پارامترها!$B$4+N(I40)*پارامترها!$B$5)/J40)</f>
         <v/>
       </c>
-      <c r="S40" s="10" t="str">
+      <c r="S40" s="12" t="str">
+        <f aca="false">IF(C40="","",N(M40)*پارامترها!$B$6+N(N40)*پارامترها!$B$7+N(O40)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T40" s="12" t="str">
+        <f aca="false">IF(C40="","",N(R40)+N(S40))</f>
+        <v/>
+      </c>
+      <c r="U40" s="10" t="str">
         <f aca="false">IF(C40="","",IF(P40&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L40)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T40" s="11"/>
+      <c r="V40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="str">
@@ -2596,11 +2959,19 @@
         <f aca="false">IF(OR(C41="",N(J41)=0),"",K41*2*(N(H41)*پارامترها!$B$4+N(I41)*پارامترها!$B$5)/J41)</f>
         <v/>
       </c>
-      <c r="S41" s="10" t="str">
+      <c r="S41" s="12" t="str">
+        <f aca="false">IF(C41="","",N(M41)*پارامترها!$B$6+N(N41)*پارامترها!$B$7+N(O41)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T41" s="12" t="str">
+        <f aca="false">IF(C41="","",N(R41)+N(S41))</f>
+        <v/>
+      </c>
+      <c r="U41" s="10" t="str">
         <f aca="false">IF(C41="","",IF(P41&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L41)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T41" s="11"/>
+      <c r="V41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="str">
@@ -2636,11 +3007,19 @@
         <f aca="false">IF(OR(C42="",N(J42)=0),"",K42*2*(N(H42)*پارامترها!$B$4+N(I42)*پارامترها!$B$5)/J42)</f>
         <v/>
       </c>
-      <c r="S42" s="10" t="str">
+      <c r="S42" s="12" t="str">
+        <f aca="false">IF(C42="","",N(M42)*پارامترها!$B$6+N(N42)*پارامترها!$B$7+N(O42)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T42" s="12" t="str">
+        <f aca="false">IF(C42="","",N(R42)+N(S42))</f>
+        <v/>
+      </c>
+      <c r="U42" s="10" t="str">
         <f aca="false">IF(C42="","",IF(P42&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L42)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T42" s="11"/>
+      <c r="V42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="str">
@@ -2676,11 +3055,19 @@
         <f aca="false">IF(OR(C43="",N(J43)=0),"",K43*2*(N(H43)*پارامترها!$B$4+N(I43)*پارامترها!$B$5)/J43)</f>
         <v/>
       </c>
-      <c r="S43" s="10" t="str">
+      <c r="S43" s="12" t="str">
+        <f aca="false">IF(C43="","",N(M43)*پارامترها!$B$6+N(N43)*پارامترها!$B$7+N(O43)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T43" s="12" t="str">
+        <f aca="false">IF(C43="","",N(R43)+N(S43))</f>
+        <v/>
+      </c>
+      <c r="U43" s="10" t="str">
         <f aca="false">IF(C43="","",IF(P43&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L43)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T43" s="11"/>
+      <c r="V43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="str">
@@ -2716,11 +3103,19 @@
         <f aca="false">IF(OR(C44="",N(J44)=0),"",K44*2*(N(H44)*پارامترها!$B$4+N(I44)*پارامترها!$B$5)/J44)</f>
         <v/>
       </c>
-      <c r="S44" s="10" t="str">
+      <c r="S44" s="12" t="str">
+        <f aca="false">IF(C44="","",N(M44)*پارامترها!$B$6+N(N44)*پارامترها!$B$7+N(O44)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T44" s="12" t="str">
+        <f aca="false">IF(C44="","",N(R44)+N(S44))</f>
+        <v/>
+      </c>
+      <c r="U44" s="10" t="str">
         <f aca="false">IF(C44="","",IF(P44&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L44)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T44" s="11"/>
+      <c r="V44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="str">
@@ -2756,11 +3151,19 @@
         <f aca="false">IF(OR(C45="",N(J45)=0),"",K45*2*(N(H45)*پارامترها!$B$4+N(I45)*پارامترها!$B$5)/J45)</f>
         <v/>
       </c>
-      <c r="S45" s="10" t="str">
+      <c r="S45" s="12" t="str">
+        <f aca="false">IF(C45="","",N(M45)*پارامترها!$B$6+N(N45)*پارامترها!$B$7+N(O45)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T45" s="12" t="str">
+        <f aca="false">IF(C45="","",N(R45)+N(S45))</f>
+        <v/>
+      </c>
+      <c r="U45" s="10" t="str">
         <f aca="false">IF(C45="","",IF(P45&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L45)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T45" s="11"/>
+      <c r="V45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="str">
@@ -2796,11 +3199,19 @@
         <f aca="false">IF(OR(C46="",N(J46)=0),"",K46*2*(N(H46)*پارامترها!$B$4+N(I46)*پارامترها!$B$5)/J46)</f>
         <v/>
       </c>
-      <c r="S46" s="10" t="str">
+      <c r="S46" s="12" t="str">
+        <f aca="false">IF(C46="","",N(M46)*پارامترها!$B$6+N(N46)*پارامترها!$B$7+N(O46)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T46" s="12" t="str">
+        <f aca="false">IF(C46="","",N(R46)+N(S46))</f>
+        <v/>
+      </c>
+      <c r="U46" s="10" t="str">
         <f aca="false">IF(C46="","",IF(P46&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L46)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T46" s="11"/>
+      <c r="V46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="str">
@@ -2836,11 +3247,19 @@
         <f aca="false">IF(OR(C47="",N(J47)=0),"",K47*2*(N(H47)*پارامترها!$B$4+N(I47)*پارامترها!$B$5)/J47)</f>
         <v/>
       </c>
-      <c r="S47" s="10" t="str">
+      <c r="S47" s="12" t="str">
+        <f aca="false">IF(C47="","",N(M47)*پارامترها!$B$6+N(N47)*پارامترها!$B$7+N(O47)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T47" s="12" t="str">
+        <f aca="false">IF(C47="","",N(R47)+N(S47))</f>
+        <v/>
+      </c>
+      <c r="U47" s="10" t="str">
         <f aca="false">IF(C47="","",IF(P47&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L47)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T47" s="11"/>
+      <c r="V47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="str">
@@ -2876,11 +3295,19 @@
         <f aca="false">IF(OR(C48="",N(J48)=0),"",K48*2*(N(H48)*پارامترها!$B$4+N(I48)*پارامترها!$B$5)/J48)</f>
         <v/>
       </c>
-      <c r="S48" s="10" t="str">
+      <c r="S48" s="12" t="str">
+        <f aca="false">IF(C48="","",N(M48)*پارامترها!$B$6+N(N48)*پارامترها!$B$7+N(O48)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T48" s="12" t="str">
+        <f aca="false">IF(C48="","",N(R48)+N(S48))</f>
+        <v/>
+      </c>
+      <c r="U48" s="10" t="str">
         <f aca="false">IF(C48="","",IF(P48&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L48)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T48" s="11"/>
+      <c r="V48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="str">
@@ -2916,11 +3343,19 @@
         <f aca="false">IF(OR(C49="",N(J49)=0),"",K49*2*(N(H49)*پارامترها!$B$4+N(I49)*پارامترها!$B$5)/J49)</f>
         <v/>
       </c>
-      <c r="S49" s="10" t="str">
+      <c r="S49" s="12" t="str">
+        <f aca="false">IF(C49="","",N(M49)*پارامترها!$B$6+N(N49)*پارامترها!$B$7+N(O49)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T49" s="12" t="str">
+        <f aca="false">IF(C49="","",N(R49)+N(S49))</f>
+        <v/>
+      </c>
+      <c r="U49" s="10" t="str">
         <f aca="false">IF(C49="","",IF(P49&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L49)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T49" s="11"/>
+      <c r="V49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="str">
@@ -2956,11 +3391,19 @@
         <f aca="false">IF(OR(C50="",N(J50)=0),"",K50*2*(N(H50)*پارامترها!$B$4+N(I50)*پارامترها!$B$5)/J50)</f>
         <v/>
       </c>
-      <c r="S50" s="10" t="str">
+      <c r="S50" s="12" t="str">
+        <f aca="false">IF(C50="","",N(M50)*پارامترها!$B$6+N(N50)*پارامترها!$B$7+N(O50)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T50" s="12" t="str">
+        <f aca="false">IF(C50="","",N(R50)+N(S50))</f>
+        <v/>
+      </c>
+      <c r="U50" s="10" t="str">
         <f aca="false">IF(C50="","",IF(P50&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L50)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T50" s="11"/>
+      <c r="V50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="str">
@@ -2996,11 +3439,19 @@
         <f aca="false">IF(OR(C51="",N(J51)=0),"",K51*2*(N(H51)*پارامترها!$B$4+N(I51)*پارامترها!$B$5)/J51)</f>
         <v/>
       </c>
-      <c r="S51" s="10" t="str">
+      <c r="S51" s="12" t="str">
+        <f aca="false">IF(C51="","",N(M51)*پارامترها!$B$6+N(N51)*پارامترها!$B$7+N(O51)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T51" s="12" t="str">
+        <f aca="false">IF(C51="","",N(R51)+N(S51))</f>
+        <v/>
+      </c>
+      <c r="U51" s="10" t="str">
         <f aca="false">IF(C51="","",IF(P51&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L51)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T51" s="11"/>
+      <c r="V51" s="11"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="str">
@@ -3036,11 +3487,19 @@
         <f aca="false">IF(OR(C52="",N(J52)=0),"",K52*2*(N(H52)*پارامترها!$B$4+N(I52)*پارامترها!$B$5)/J52)</f>
         <v/>
       </c>
-      <c r="S52" s="10" t="str">
+      <c r="S52" s="12" t="str">
+        <f aca="false">IF(C52="","",N(M52)*پارامترها!$B$6+N(N52)*پارامترها!$B$7+N(O52)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T52" s="12" t="str">
+        <f aca="false">IF(C52="","",N(R52)+N(S52))</f>
+        <v/>
+      </c>
+      <c r="U52" s="10" t="str">
         <f aca="false">IF(C52="","",IF(P52&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L52)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T52" s="11"/>
+      <c r="V52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="str">
@@ -3076,11 +3535,19 @@
         <f aca="false">IF(OR(C53="",N(J53)=0),"",K53*2*(N(H53)*پارامترها!$B$4+N(I53)*پارامترها!$B$5)/J53)</f>
         <v/>
       </c>
-      <c r="S53" s="10" t="str">
+      <c r="S53" s="12" t="str">
+        <f aca="false">IF(C53="","",N(M53)*پارامترها!$B$6+N(N53)*پارامترها!$B$7+N(O53)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T53" s="12" t="str">
+        <f aca="false">IF(C53="","",N(R53)+N(S53))</f>
+        <v/>
+      </c>
+      <c r="U53" s="10" t="str">
         <f aca="false">IF(C53="","",IF(P53&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L53)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T53" s="11"/>
+      <c r="V53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="str">
@@ -3116,11 +3583,19 @@
         <f aca="false">IF(OR(C54="",N(J54)=0),"",K54*2*(N(H54)*پارامترها!$B$4+N(I54)*پارامترها!$B$5)/J54)</f>
         <v/>
       </c>
-      <c r="S54" s="10" t="str">
+      <c r="S54" s="12" t="str">
+        <f aca="false">IF(C54="","",N(M54)*پارامترها!$B$6+N(N54)*پارامترها!$B$7+N(O54)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T54" s="12" t="str">
+        <f aca="false">IF(C54="","",N(R54)+N(S54))</f>
+        <v/>
+      </c>
+      <c r="U54" s="10" t="str">
         <f aca="false">IF(C54="","",IF(P54&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L54)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T54" s="11"/>
+      <c r="V54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="str">
@@ -3156,11 +3631,19 @@
         <f aca="false">IF(OR(C55="",N(J55)=0),"",K55*2*(N(H55)*پارامترها!$B$4+N(I55)*پارامترها!$B$5)/J55)</f>
         <v/>
       </c>
-      <c r="S55" s="10" t="str">
+      <c r="S55" s="12" t="str">
+        <f aca="false">IF(C55="","",N(M55)*پارامترها!$B$6+N(N55)*پارامترها!$B$7+N(O55)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T55" s="12" t="str">
+        <f aca="false">IF(C55="","",N(R55)+N(S55))</f>
+        <v/>
+      </c>
+      <c r="U55" s="10" t="str">
         <f aca="false">IF(C55="","",IF(P55&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L55)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T55" s="11"/>
+      <c r="V55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="str">
@@ -3196,11 +3679,19 @@
         <f aca="false">IF(OR(C56="",N(J56)=0),"",K56*2*(N(H56)*پارامترها!$B$4+N(I56)*پارامترها!$B$5)/J56)</f>
         <v/>
       </c>
-      <c r="S56" s="10" t="str">
+      <c r="S56" s="12" t="str">
+        <f aca="false">IF(C56="","",N(M56)*پارامترها!$B$6+N(N56)*پارامترها!$B$7+N(O56)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T56" s="12" t="str">
+        <f aca="false">IF(C56="","",N(R56)+N(S56))</f>
+        <v/>
+      </c>
+      <c r="U56" s="10" t="str">
         <f aca="false">IF(C56="","",IF(P56&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L56)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T56" s="11"/>
+      <c r="V56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="str">
@@ -3236,11 +3727,19 @@
         <f aca="false">IF(OR(C57="",N(J57)=0),"",K57*2*(N(H57)*پارامترها!$B$4+N(I57)*پارامترها!$B$5)/J57)</f>
         <v/>
       </c>
-      <c r="S57" s="10" t="str">
+      <c r="S57" s="12" t="str">
+        <f aca="false">IF(C57="","",N(M57)*پارامترها!$B$6+N(N57)*پارامترها!$B$7+N(O57)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T57" s="12" t="str">
+        <f aca="false">IF(C57="","",N(R57)+N(S57))</f>
+        <v/>
+      </c>
+      <c r="U57" s="10" t="str">
         <f aca="false">IF(C57="","",IF(P57&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L57)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T57" s="11"/>
+      <c r="V57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="str">
@@ -3276,11 +3775,19 @@
         <f aca="false">IF(OR(C58="",N(J58)=0),"",K58*2*(N(H58)*پارامترها!$B$4+N(I58)*پارامترها!$B$5)/J58)</f>
         <v/>
       </c>
-      <c r="S58" s="10" t="str">
+      <c r="S58" s="12" t="str">
+        <f aca="false">IF(C58="","",N(M58)*پارامترها!$B$6+N(N58)*پارامترها!$B$7+N(O58)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T58" s="12" t="str">
+        <f aca="false">IF(C58="","",N(R58)+N(S58))</f>
+        <v/>
+      </c>
+      <c r="U58" s="10" t="str">
         <f aca="false">IF(C58="","",IF(P58&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L58)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T58" s="11"/>
+      <c r="V58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="str">
@@ -3316,11 +3823,19 @@
         <f aca="false">IF(OR(C59="",N(J59)=0),"",K59*2*(N(H59)*پارامترها!$B$4+N(I59)*پارامترها!$B$5)/J59)</f>
         <v/>
       </c>
-      <c r="S59" s="10" t="str">
+      <c r="S59" s="12" t="str">
+        <f aca="false">IF(C59="","",N(M59)*پارامترها!$B$6+N(N59)*پارامترها!$B$7+N(O59)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T59" s="12" t="str">
+        <f aca="false">IF(C59="","",N(R59)+N(S59))</f>
+        <v/>
+      </c>
+      <c r="U59" s="10" t="str">
         <f aca="false">IF(C59="","",IF(P59&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L59)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T59" s="11"/>
+      <c r="V59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="str">
@@ -3356,11 +3871,19 @@
         <f aca="false">IF(OR(C60="",N(J60)=0),"",K60*2*(N(H60)*پارامترها!$B$4+N(I60)*پارامترها!$B$5)/J60)</f>
         <v/>
       </c>
-      <c r="S60" s="10" t="str">
+      <c r="S60" s="12" t="str">
+        <f aca="false">IF(C60="","",N(M60)*پارامترها!$B$6+N(N60)*پارامترها!$B$7+N(O60)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T60" s="12" t="str">
+        <f aca="false">IF(C60="","",N(R60)+N(S60))</f>
+        <v/>
+      </c>
+      <c r="U60" s="10" t="str">
         <f aca="false">IF(C60="","",IF(P60&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L60)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T60" s="11"/>
+      <c r="V60" s="11"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="str">
@@ -3396,11 +3919,19 @@
         <f aca="false">IF(OR(C61="",N(J61)=0),"",K61*2*(N(H61)*پارامترها!$B$4+N(I61)*پارامترها!$B$5)/J61)</f>
         <v/>
       </c>
-      <c r="S61" s="10" t="str">
+      <c r="S61" s="12" t="str">
+        <f aca="false">IF(C61="","",N(M61)*پارامترها!$B$6+N(N61)*پارامترها!$B$7+N(O61)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T61" s="12" t="str">
+        <f aca="false">IF(C61="","",N(R61)+N(S61))</f>
+        <v/>
+      </c>
+      <c r="U61" s="10" t="str">
         <f aca="false">IF(C61="","",IF(P61&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L61)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T61" s="11"/>
+      <c r="V61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="str">
@@ -3436,11 +3967,19 @@
         <f aca="false">IF(OR(C62="",N(J62)=0),"",K62*2*(N(H62)*پارامترها!$B$4+N(I62)*پارامترها!$B$5)/J62)</f>
         <v/>
       </c>
-      <c r="S62" s="10" t="str">
+      <c r="S62" s="12" t="str">
+        <f aca="false">IF(C62="","",N(M62)*پارامترها!$B$6+N(N62)*پارامترها!$B$7+N(O62)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T62" s="12" t="str">
+        <f aca="false">IF(C62="","",N(R62)+N(S62))</f>
+        <v/>
+      </c>
+      <c r="U62" s="10" t="str">
         <f aca="false">IF(C62="","",IF(P62&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L62)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T62" s="11"/>
+      <c r="V62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="str">
@@ -3476,11 +4015,19 @@
         <f aca="false">IF(OR(C63="",N(J63)=0),"",K63*2*(N(H63)*پارامترها!$B$4+N(I63)*پارامترها!$B$5)/J63)</f>
         <v/>
       </c>
-      <c r="S63" s="10" t="str">
+      <c r="S63" s="12" t="str">
+        <f aca="false">IF(C63="","",N(M63)*پارامترها!$B$6+N(N63)*پارامترها!$B$7+N(O63)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T63" s="12" t="str">
+        <f aca="false">IF(C63="","",N(R63)+N(S63))</f>
+        <v/>
+      </c>
+      <c r="U63" s="10" t="str">
         <f aca="false">IF(C63="","",IF(P63&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L63)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T63" s="11"/>
+      <c r="V63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="str">
@@ -3516,11 +4063,19 @@
         <f aca="false">IF(OR(C64="",N(J64)=0),"",K64*2*(N(H64)*پارامترها!$B$4+N(I64)*پارامترها!$B$5)/J64)</f>
         <v/>
       </c>
-      <c r="S64" s="10" t="str">
+      <c r="S64" s="12" t="str">
+        <f aca="false">IF(C64="","",N(M64)*پارامترها!$B$6+N(N64)*پارامترها!$B$7+N(O64)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T64" s="12" t="str">
+        <f aca="false">IF(C64="","",N(R64)+N(S64))</f>
+        <v/>
+      </c>
+      <c r="U64" s="10" t="str">
         <f aca="false">IF(C64="","",IF(P64&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L64)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T64" s="11"/>
+      <c r="V64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="str">
@@ -3556,11 +4111,19 @@
         <f aca="false">IF(OR(C65="",N(J65)=0),"",K65*2*(N(H65)*پارامترها!$B$4+N(I65)*پارامترها!$B$5)/J65)</f>
         <v/>
       </c>
-      <c r="S65" s="10" t="str">
+      <c r="S65" s="12" t="str">
+        <f aca="false">IF(C65="","",N(M65)*پارامترها!$B$6+N(N65)*پارامترها!$B$7+N(O65)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T65" s="12" t="str">
+        <f aca="false">IF(C65="","",N(R65)+N(S65))</f>
+        <v/>
+      </c>
+      <c r="U65" s="10" t="str">
         <f aca="false">IF(C65="","",IF(P65&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L65)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T65" s="11"/>
+      <c r="V65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="str">
@@ -3596,11 +4159,19 @@
         <f aca="false">IF(OR(C66="",N(J66)=0),"",K66*2*(N(H66)*پارامترها!$B$4+N(I66)*پارامترها!$B$5)/J66)</f>
         <v/>
       </c>
-      <c r="S66" s="10" t="str">
+      <c r="S66" s="12" t="str">
+        <f aca="false">IF(C66="","",N(M66)*پارامترها!$B$6+N(N66)*پارامترها!$B$7+N(O66)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T66" s="12" t="str">
+        <f aca="false">IF(C66="","",N(R66)+N(S66))</f>
+        <v/>
+      </c>
+      <c r="U66" s="10" t="str">
         <f aca="false">IF(C66="","",IF(P66&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L66)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T66" s="11"/>
+      <c r="V66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="str">
@@ -3636,11 +4207,19 @@
         <f aca="false">IF(OR(C67="",N(J67)=0),"",K67*2*(N(H67)*پارامترها!$B$4+N(I67)*پارامترها!$B$5)/J67)</f>
         <v/>
       </c>
-      <c r="S67" s="10" t="str">
+      <c r="S67" s="12" t="str">
+        <f aca="false">IF(C67="","",N(M67)*پارامترها!$B$6+N(N67)*پارامترها!$B$7+N(O67)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T67" s="12" t="str">
+        <f aca="false">IF(C67="","",N(R67)+N(S67))</f>
+        <v/>
+      </c>
+      <c r="U67" s="10" t="str">
         <f aca="false">IF(C67="","",IF(P67&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L67)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T67" s="11"/>
+      <c r="V67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="str">
@@ -3676,11 +4255,19 @@
         <f aca="false">IF(OR(C68="",N(J68)=0),"",K68*2*(N(H68)*پارامترها!$B$4+N(I68)*پارامترها!$B$5)/J68)</f>
         <v/>
       </c>
-      <c r="S68" s="10" t="str">
+      <c r="S68" s="12" t="str">
+        <f aca="false">IF(C68="","",N(M68)*پارامترها!$B$6+N(N68)*پارامترها!$B$7+N(O68)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T68" s="12" t="str">
+        <f aca="false">IF(C68="","",N(R68)+N(S68))</f>
+        <v/>
+      </c>
+      <c r="U68" s="10" t="str">
         <f aca="false">IF(C68="","",IF(P68&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L68)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T68" s="11"/>
+      <c r="V68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="str">
@@ -3716,11 +4303,19 @@
         <f aca="false">IF(OR(C69="",N(J69)=0),"",K69*2*(N(H69)*پارامترها!$B$4+N(I69)*پارامترها!$B$5)/J69)</f>
         <v/>
       </c>
-      <c r="S69" s="10" t="str">
+      <c r="S69" s="12" t="str">
+        <f aca="false">IF(C69="","",N(M69)*پارامترها!$B$6+N(N69)*پارامترها!$B$7+N(O69)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T69" s="12" t="str">
+        <f aca="false">IF(C69="","",N(R69)+N(S69))</f>
+        <v/>
+      </c>
+      <c r="U69" s="10" t="str">
         <f aca="false">IF(C69="","",IF(P69&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L69)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T69" s="11"/>
+      <c r="V69" s="11"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="str">
@@ -3756,11 +4351,19 @@
         <f aca="false">IF(OR(C70="",N(J70)=0),"",K70*2*(N(H70)*پارامترها!$B$4+N(I70)*پارامترها!$B$5)/J70)</f>
         <v/>
       </c>
-      <c r="S70" s="10" t="str">
+      <c r="S70" s="12" t="str">
+        <f aca="false">IF(C70="","",N(M70)*پارامترها!$B$6+N(N70)*پارامترها!$B$7+N(O70)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T70" s="12" t="str">
+        <f aca="false">IF(C70="","",N(R70)+N(S70))</f>
+        <v/>
+      </c>
+      <c r="U70" s="10" t="str">
         <f aca="false">IF(C70="","",IF(P70&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L70)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T70" s="11"/>
+      <c r="V70" s="11"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="str">
@@ -3796,11 +4399,19 @@
         <f aca="false">IF(OR(C71="",N(J71)=0),"",K71*2*(N(H71)*پارامترها!$B$4+N(I71)*پارامترها!$B$5)/J71)</f>
         <v/>
       </c>
-      <c r="S71" s="10" t="str">
+      <c r="S71" s="12" t="str">
+        <f aca="false">IF(C71="","",N(M71)*پارامترها!$B$6+N(N71)*پارامترها!$B$7+N(O71)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T71" s="12" t="str">
+        <f aca="false">IF(C71="","",N(R71)+N(S71))</f>
+        <v/>
+      </c>
+      <c r="U71" s="10" t="str">
         <f aca="false">IF(C71="","",IF(P71&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L71)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T71" s="11"/>
+      <c r="V71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="str">
@@ -3836,11 +4447,19 @@
         <f aca="false">IF(OR(C72="",N(J72)=0),"",K72*2*(N(H72)*پارامترها!$B$4+N(I72)*پارامترها!$B$5)/J72)</f>
         <v/>
       </c>
-      <c r="S72" s="10" t="str">
+      <c r="S72" s="12" t="str">
+        <f aca="false">IF(C72="","",N(M72)*پارامترها!$B$6+N(N72)*پارامترها!$B$7+N(O72)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T72" s="12" t="str">
+        <f aca="false">IF(C72="","",N(R72)+N(S72))</f>
+        <v/>
+      </c>
+      <c r="U72" s="10" t="str">
         <f aca="false">IF(C72="","",IF(P72&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L72)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T72" s="11"/>
+      <c r="V72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="str">
@@ -3876,11 +4495,19 @@
         <f aca="false">IF(OR(C73="",N(J73)=0),"",K73*2*(N(H73)*پارامترها!$B$4+N(I73)*پارامترها!$B$5)/J73)</f>
         <v/>
       </c>
-      <c r="S73" s="10" t="str">
+      <c r="S73" s="12" t="str">
+        <f aca="false">IF(C73="","",N(M73)*پارامترها!$B$6+N(N73)*پارامترها!$B$7+N(O73)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T73" s="12" t="str">
+        <f aca="false">IF(C73="","",N(R73)+N(S73))</f>
+        <v/>
+      </c>
+      <c r="U73" s="10" t="str">
         <f aca="false">IF(C73="","",IF(P73&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L73)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T73" s="11"/>
+      <c r="V73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="str">
@@ -3916,11 +4543,19 @@
         <f aca="false">IF(OR(C74="",N(J74)=0),"",K74*2*(N(H74)*پارامترها!$B$4+N(I74)*پارامترها!$B$5)/J74)</f>
         <v/>
       </c>
-      <c r="S74" s="10" t="str">
+      <c r="S74" s="12" t="str">
+        <f aca="false">IF(C74="","",N(M74)*پارامترها!$B$6+N(N74)*پارامترها!$B$7+N(O74)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T74" s="12" t="str">
+        <f aca="false">IF(C74="","",N(R74)+N(S74))</f>
+        <v/>
+      </c>
+      <c r="U74" s="10" t="str">
         <f aca="false">IF(C74="","",IF(P74&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L74)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T74" s="11"/>
+      <c r="V74" s="11"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="str">
@@ -3956,11 +4591,19 @@
         <f aca="false">IF(OR(C75="",N(J75)=0),"",K75*2*(N(H75)*پارامترها!$B$4+N(I75)*پارامترها!$B$5)/J75)</f>
         <v/>
       </c>
-      <c r="S75" s="10" t="str">
+      <c r="S75" s="12" t="str">
+        <f aca="false">IF(C75="","",N(M75)*پارامترها!$B$6+N(N75)*پارامترها!$B$7+N(O75)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T75" s="12" t="str">
+        <f aca="false">IF(C75="","",N(R75)+N(S75))</f>
+        <v/>
+      </c>
+      <c r="U75" s="10" t="str">
         <f aca="false">IF(C75="","",IF(P75&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L75)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T75" s="11"/>
+      <c r="V75" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="str">
@@ -3996,11 +4639,19 @@
         <f aca="false">IF(OR(C76="",N(J76)=0),"",K76*2*(N(H76)*پارامترها!$B$4+N(I76)*پارامترها!$B$5)/J76)</f>
         <v/>
       </c>
-      <c r="S76" s="10" t="str">
+      <c r="S76" s="12" t="str">
+        <f aca="false">IF(C76="","",N(M76)*پارامترها!$B$6+N(N76)*پارامترها!$B$7+N(O76)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T76" s="12" t="str">
+        <f aca="false">IF(C76="","",N(R76)+N(S76))</f>
+        <v/>
+      </c>
+      <c r="U76" s="10" t="str">
         <f aca="false">IF(C76="","",IF(P76&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L76)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T76" s="11"/>
+      <c r="V76" s="11"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="str">
@@ -4036,11 +4687,19 @@
         <f aca="false">IF(OR(C77="",N(J77)=0),"",K77*2*(N(H77)*پارامترها!$B$4+N(I77)*پارامترها!$B$5)/J77)</f>
         <v/>
       </c>
-      <c r="S77" s="10" t="str">
+      <c r="S77" s="12" t="str">
+        <f aca="false">IF(C77="","",N(M77)*پارامترها!$B$6+N(N77)*پارامترها!$B$7+N(O77)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T77" s="12" t="str">
+        <f aca="false">IF(C77="","",N(R77)+N(S77))</f>
+        <v/>
+      </c>
+      <c r="U77" s="10" t="str">
         <f aca="false">IF(C77="","",IF(P77&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L77)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T77" s="11"/>
+      <c r="V77" s="11"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="str">
@@ -4076,11 +4735,19 @@
         <f aca="false">IF(OR(C78="",N(J78)=0),"",K78*2*(N(H78)*پارامترها!$B$4+N(I78)*پارامترها!$B$5)/J78)</f>
         <v/>
       </c>
-      <c r="S78" s="10" t="str">
+      <c r="S78" s="12" t="str">
+        <f aca="false">IF(C78="","",N(M78)*پارامترها!$B$6+N(N78)*پارامترها!$B$7+N(O78)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T78" s="12" t="str">
+        <f aca="false">IF(C78="","",N(R78)+N(S78))</f>
+        <v/>
+      </c>
+      <c r="U78" s="10" t="str">
         <f aca="false">IF(C78="","",IF(P78&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L78)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T78" s="11"/>
+      <c r="V78" s="11"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="str">
@@ -4116,11 +4783,19 @@
         <f aca="false">IF(OR(C79="",N(J79)=0),"",K79*2*(N(H79)*پارامترها!$B$4+N(I79)*پارامترها!$B$5)/J79)</f>
         <v/>
       </c>
-      <c r="S79" s="10" t="str">
+      <c r="S79" s="12" t="str">
+        <f aca="false">IF(C79="","",N(M79)*پارامترها!$B$6+N(N79)*پارامترها!$B$7+N(O79)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T79" s="12" t="str">
+        <f aca="false">IF(C79="","",N(R79)+N(S79))</f>
+        <v/>
+      </c>
+      <c r="U79" s="10" t="str">
         <f aca="false">IF(C79="","",IF(P79&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L79)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T79" s="11"/>
+      <c r="V79" s="11"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="str">
@@ -4156,11 +4831,19 @@
         <f aca="false">IF(OR(C80="",N(J80)=0),"",K80*2*(N(H80)*پارامترها!$B$4+N(I80)*پارامترها!$B$5)/J80)</f>
         <v/>
       </c>
-      <c r="S80" s="10" t="str">
+      <c r="S80" s="12" t="str">
+        <f aca="false">IF(C80="","",N(M80)*پارامترها!$B$6+N(N80)*پارامترها!$B$7+N(O80)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T80" s="12" t="str">
+        <f aca="false">IF(C80="","",N(R80)+N(S80))</f>
+        <v/>
+      </c>
+      <c r="U80" s="10" t="str">
         <f aca="false">IF(C80="","",IF(P80&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L80)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T80" s="11"/>
+      <c r="V80" s="11"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="str">
@@ -4196,11 +4879,19 @@
         <f aca="false">IF(OR(C81="",N(J81)=0),"",K81*2*(N(H81)*پارامترها!$B$4+N(I81)*پارامترها!$B$5)/J81)</f>
         <v/>
       </c>
-      <c r="S81" s="10" t="str">
+      <c r="S81" s="12" t="str">
+        <f aca="false">IF(C81="","",N(M81)*پارامترها!$B$6+N(N81)*پارامترها!$B$7+N(O81)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T81" s="12" t="str">
+        <f aca="false">IF(C81="","",N(R81)+N(S81))</f>
+        <v/>
+      </c>
+      <c r="U81" s="10" t="str">
         <f aca="false">IF(C81="","",IF(P81&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L81)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T81" s="11"/>
+      <c r="V81" s="11"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="str">
@@ -4236,11 +4927,19 @@
         <f aca="false">IF(OR(C82="",N(J82)=0),"",K82*2*(N(H82)*پارامترها!$B$4+N(I82)*پارامترها!$B$5)/J82)</f>
         <v/>
       </c>
-      <c r="S82" s="10" t="str">
+      <c r="S82" s="12" t="str">
+        <f aca="false">IF(C82="","",N(M82)*پارامترها!$B$6+N(N82)*پارامترها!$B$7+N(O82)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T82" s="12" t="str">
+        <f aca="false">IF(C82="","",N(R82)+N(S82))</f>
+        <v/>
+      </c>
+      <c r="U82" s="10" t="str">
         <f aca="false">IF(C82="","",IF(P82&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L82)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T82" s="11"/>
+      <c r="V82" s="11"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="str">
@@ -4276,11 +4975,19 @@
         <f aca="false">IF(OR(C83="",N(J83)=0),"",K83*2*(N(H83)*پارامترها!$B$4+N(I83)*پارامترها!$B$5)/J83)</f>
         <v/>
       </c>
-      <c r="S83" s="10" t="str">
+      <c r="S83" s="12" t="str">
+        <f aca="false">IF(C83="","",N(M83)*پارامترها!$B$6+N(N83)*پارامترها!$B$7+N(O83)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T83" s="12" t="str">
+        <f aca="false">IF(C83="","",N(R83)+N(S83))</f>
+        <v/>
+      </c>
+      <c r="U83" s="10" t="str">
         <f aca="false">IF(C83="","",IF(P83&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L83)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T83" s="11"/>
+      <c r="V83" s="11"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="str">
@@ -4316,11 +5023,19 @@
         <f aca="false">IF(OR(C84="",N(J84)=0),"",K84*2*(N(H84)*پارامترها!$B$4+N(I84)*پارامترها!$B$5)/J84)</f>
         <v/>
       </c>
-      <c r="S84" s="10" t="str">
+      <c r="S84" s="12" t="str">
+        <f aca="false">IF(C84="","",N(M84)*پارامترها!$B$6+N(N84)*پارامترها!$B$7+N(O84)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T84" s="12" t="str">
+        <f aca="false">IF(C84="","",N(R84)+N(S84))</f>
+        <v/>
+      </c>
+      <c r="U84" s="10" t="str">
         <f aca="false">IF(C84="","",IF(P84&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L84)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T84" s="11"/>
+      <c r="V84" s="11"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="str">
@@ -4356,11 +5071,19 @@
         <f aca="false">IF(OR(C85="",N(J85)=0),"",K85*2*(N(H85)*پارامترها!$B$4+N(I85)*پارامترها!$B$5)/J85)</f>
         <v/>
       </c>
-      <c r="S85" s="10" t="str">
+      <c r="S85" s="12" t="str">
+        <f aca="false">IF(C85="","",N(M85)*پارامترها!$B$6+N(N85)*پارامترها!$B$7+N(O85)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T85" s="12" t="str">
+        <f aca="false">IF(C85="","",N(R85)+N(S85))</f>
+        <v/>
+      </c>
+      <c r="U85" s="10" t="str">
         <f aca="false">IF(C85="","",IF(P85&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L85)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T85" s="11"/>
+      <c r="V85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="str">
@@ -4396,11 +5119,19 @@
         <f aca="false">IF(OR(C86="",N(J86)=0),"",K86*2*(N(H86)*پارامترها!$B$4+N(I86)*پارامترها!$B$5)/J86)</f>
         <v/>
       </c>
-      <c r="S86" s="10" t="str">
+      <c r="S86" s="12" t="str">
+        <f aca="false">IF(C86="","",N(M86)*پارامترها!$B$6+N(N86)*پارامترها!$B$7+N(O86)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T86" s="12" t="str">
+        <f aca="false">IF(C86="","",N(R86)+N(S86))</f>
+        <v/>
+      </c>
+      <c r="U86" s="10" t="str">
         <f aca="false">IF(C86="","",IF(P86&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L86)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T86" s="11"/>
+      <c r="V86" s="11"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="str">
@@ -4436,11 +5167,19 @@
         <f aca="false">IF(OR(C87="",N(J87)=0),"",K87*2*(N(H87)*پارامترها!$B$4+N(I87)*پارامترها!$B$5)/J87)</f>
         <v/>
       </c>
-      <c r="S87" s="10" t="str">
+      <c r="S87" s="12" t="str">
+        <f aca="false">IF(C87="","",N(M87)*پارامترها!$B$6+N(N87)*پارامترها!$B$7+N(O87)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T87" s="12" t="str">
+        <f aca="false">IF(C87="","",N(R87)+N(S87))</f>
+        <v/>
+      </c>
+      <c r="U87" s="10" t="str">
         <f aca="false">IF(C87="","",IF(P87&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L87)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T87" s="11"/>
+      <c r="V87" s="11"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="str">
@@ -4476,11 +5215,19 @@
         <f aca="false">IF(OR(C88="",N(J88)=0),"",K88*2*(N(H88)*پارامترها!$B$4+N(I88)*پارامترها!$B$5)/J88)</f>
         <v/>
       </c>
-      <c r="S88" s="10" t="str">
+      <c r="S88" s="12" t="str">
+        <f aca="false">IF(C88="","",N(M88)*پارامترها!$B$6+N(N88)*پارامترها!$B$7+N(O88)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T88" s="12" t="str">
+        <f aca="false">IF(C88="","",N(R88)+N(S88))</f>
+        <v/>
+      </c>
+      <c r="U88" s="10" t="str">
         <f aca="false">IF(C88="","",IF(P88&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L88)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T88" s="11"/>
+      <c r="V88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="str">
@@ -4516,11 +5263,19 @@
         <f aca="false">IF(OR(C89="",N(J89)=0),"",K89*2*(N(H89)*پارامترها!$B$4+N(I89)*پارامترها!$B$5)/J89)</f>
         <v/>
       </c>
-      <c r="S89" s="10" t="str">
+      <c r="S89" s="12" t="str">
+        <f aca="false">IF(C89="","",N(M89)*پارامترها!$B$6+N(N89)*پارامترها!$B$7+N(O89)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T89" s="12" t="str">
+        <f aca="false">IF(C89="","",N(R89)+N(S89))</f>
+        <v/>
+      </c>
+      <c r="U89" s="10" t="str">
         <f aca="false">IF(C89="","",IF(P89&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L89)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T89" s="11"/>
+      <c r="V89" s="11"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="str">
@@ -4556,11 +5311,19 @@
         <f aca="false">IF(OR(C90="",N(J90)=0),"",K90*2*(N(H90)*پارامترها!$B$4+N(I90)*پارامترها!$B$5)/J90)</f>
         <v/>
       </c>
-      <c r="S90" s="10" t="str">
+      <c r="S90" s="12" t="str">
+        <f aca="false">IF(C90="","",N(M90)*پارامترها!$B$6+N(N90)*پارامترها!$B$7+N(O90)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T90" s="12" t="str">
+        <f aca="false">IF(C90="","",N(R90)+N(S90))</f>
+        <v/>
+      </c>
+      <c r="U90" s="10" t="str">
         <f aca="false">IF(C90="","",IF(P90&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L90)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T90" s="11"/>
+      <c r="V90" s="11"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="str">
@@ -4596,11 +5359,19 @@
         <f aca="false">IF(OR(C91="",N(J91)=0),"",K91*2*(N(H91)*پارامترها!$B$4+N(I91)*پارامترها!$B$5)/J91)</f>
         <v/>
       </c>
-      <c r="S91" s="10" t="str">
+      <c r="S91" s="12" t="str">
+        <f aca="false">IF(C91="","",N(M91)*پارامترها!$B$6+N(N91)*پارامترها!$B$7+N(O91)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T91" s="12" t="str">
+        <f aca="false">IF(C91="","",N(R91)+N(S91))</f>
+        <v/>
+      </c>
+      <c r="U91" s="10" t="str">
         <f aca="false">IF(C91="","",IF(P91&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L91)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T91" s="11"/>
+      <c r="V91" s="11"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="str">
@@ -4636,11 +5407,19 @@
         <f aca="false">IF(OR(C92="",N(J92)=0),"",K92*2*(N(H92)*پارامترها!$B$4+N(I92)*پارامترها!$B$5)/J92)</f>
         <v/>
       </c>
-      <c r="S92" s="10" t="str">
+      <c r="S92" s="12" t="str">
+        <f aca="false">IF(C92="","",N(M92)*پارامترها!$B$6+N(N92)*پارامترها!$B$7+N(O92)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T92" s="12" t="str">
+        <f aca="false">IF(C92="","",N(R92)+N(S92))</f>
+        <v/>
+      </c>
+      <c r="U92" s="10" t="str">
         <f aca="false">IF(C92="","",IF(P92&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L92)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T92" s="11"/>
+      <c r="V92" s="11"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="str">
@@ -4676,11 +5455,19 @@
         <f aca="false">IF(OR(C93="",N(J93)=0),"",K93*2*(N(H93)*پارامترها!$B$4+N(I93)*پارامترها!$B$5)/J93)</f>
         <v/>
       </c>
-      <c r="S93" s="10" t="str">
+      <c r="S93" s="12" t="str">
+        <f aca="false">IF(C93="","",N(M93)*پارامترها!$B$6+N(N93)*پارامترها!$B$7+N(O93)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T93" s="12" t="str">
+        <f aca="false">IF(C93="","",N(R93)+N(S93))</f>
+        <v/>
+      </c>
+      <c r="U93" s="10" t="str">
         <f aca="false">IF(C93="","",IF(P93&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L93)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T93" s="11"/>
+      <c r="V93" s="11"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="str">
@@ -4716,11 +5503,19 @@
         <f aca="false">IF(OR(C94="",N(J94)=0),"",K94*2*(N(H94)*پارامترها!$B$4+N(I94)*پارامترها!$B$5)/J94)</f>
         <v/>
       </c>
-      <c r="S94" s="10" t="str">
+      <c r="S94" s="12" t="str">
+        <f aca="false">IF(C94="","",N(M94)*پارامترها!$B$6+N(N94)*پارامترها!$B$7+N(O94)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T94" s="12" t="str">
+        <f aca="false">IF(C94="","",N(R94)+N(S94))</f>
+        <v/>
+      </c>
+      <c r="U94" s="10" t="str">
         <f aca="false">IF(C94="","",IF(P94&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L94)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T94" s="11"/>
+      <c r="V94" s="11"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="str">
@@ -4756,11 +5551,19 @@
         <f aca="false">IF(OR(C95="",N(J95)=0),"",K95*2*(N(H95)*پارامترها!$B$4+N(I95)*پارامترها!$B$5)/J95)</f>
         <v/>
       </c>
-      <c r="S95" s="10" t="str">
+      <c r="S95" s="12" t="str">
+        <f aca="false">IF(C95="","",N(M95)*پارامترها!$B$6+N(N95)*پارامترها!$B$7+N(O95)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T95" s="12" t="str">
+        <f aca="false">IF(C95="","",N(R95)+N(S95))</f>
+        <v/>
+      </c>
+      <c r="U95" s="10" t="str">
         <f aca="false">IF(C95="","",IF(P95&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L95)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T95" s="11"/>
+      <c r="V95" s="11"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="str">
@@ -4796,11 +5599,19 @@
         <f aca="false">IF(OR(C96="",N(J96)=0),"",K96*2*(N(H96)*پارامترها!$B$4+N(I96)*پارامترها!$B$5)/J96)</f>
         <v/>
       </c>
-      <c r="S96" s="10" t="str">
+      <c r="S96" s="12" t="str">
+        <f aca="false">IF(C96="","",N(M96)*پارامترها!$B$6+N(N96)*پارامترها!$B$7+N(O96)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T96" s="12" t="str">
+        <f aca="false">IF(C96="","",N(R96)+N(S96))</f>
+        <v/>
+      </c>
+      <c r="U96" s="10" t="str">
         <f aca="false">IF(C96="","",IF(P96&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L96)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T96" s="11"/>
+      <c r="V96" s="11"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="str">
@@ -4836,11 +5647,19 @@
         <f aca="false">IF(OR(C97="",N(J97)=0),"",K97*2*(N(H97)*پارامترها!$B$4+N(I97)*پارامترها!$B$5)/J97)</f>
         <v/>
       </c>
-      <c r="S97" s="10" t="str">
+      <c r="S97" s="12" t="str">
+        <f aca="false">IF(C97="","",N(M97)*پارامترها!$B$6+N(N97)*پارامترها!$B$7+N(O97)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T97" s="12" t="str">
+        <f aca="false">IF(C97="","",N(R97)+N(S97))</f>
+        <v/>
+      </c>
+      <c r="U97" s="10" t="str">
         <f aca="false">IF(C97="","",IF(P97&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L97)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T97" s="11"/>
+      <c r="V97" s="11"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="str">
@@ -4876,11 +5695,19 @@
         <f aca="false">IF(OR(C98="",N(J98)=0),"",K98*2*(N(H98)*پارامترها!$B$4+N(I98)*پارامترها!$B$5)/J98)</f>
         <v/>
       </c>
-      <c r="S98" s="10" t="str">
+      <c r="S98" s="12" t="str">
+        <f aca="false">IF(C98="","",N(M98)*پارامترها!$B$6+N(N98)*پارامترها!$B$7+N(O98)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T98" s="12" t="str">
+        <f aca="false">IF(C98="","",N(R98)+N(S98))</f>
+        <v/>
+      </c>
+      <c r="U98" s="10" t="str">
         <f aca="false">IF(C98="","",IF(P98&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L98)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T98" s="11"/>
+      <c r="V98" s="11"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="str">
@@ -4916,11 +5743,19 @@
         <f aca="false">IF(OR(C99="",N(J99)=0),"",K99*2*(N(H99)*پارامترها!$B$4+N(I99)*پارامترها!$B$5)/J99)</f>
         <v/>
       </c>
-      <c r="S99" s="10" t="str">
+      <c r="S99" s="12" t="str">
+        <f aca="false">IF(C99="","",N(M99)*پارامترها!$B$6+N(N99)*پارامترها!$B$7+N(O99)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T99" s="12" t="str">
+        <f aca="false">IF(C99="","",N(R99)+N(S99))</f>
+        <v/>
+      </c>
+      <c r="U99" s="10" t="str">
         <f aca="false">IF(C99="","",IF(P99&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L99)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T99" s="11"/>
+      <c r="V99" s="11"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="str">
@@ -4956,11 +5791,19 @@
         <f aca="false">IF(OR(C100="",N(J100)=0),"",K100*2*(N(H100)*پارامترها!$B$4+N(I100)*پارامترها!$B$5)/J100)</f>
         <v/>
       </c>
-      <c r="S100" s="10" t="str">
+      <c r="S100" s="12" t="str">
+        <f aca="false">IF(C100="","",N(M100)*پارامترها!$B$6+N(N100)*پارامترها!$B$7+N(O100)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T100" s="12" t="str">
+        <f aca="false">IF(C100="","",N(R100)+N(S100))</f>
+        <v/>
+      </c>
+      <c r="U100" s="10" t="str">
         <f aca="false">IF(C100="","",IF(P100&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L100)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T100" s="11"/>
+      <c r="V100" s="11"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="str">
@@ -4996,11 +5839,19 @@
         <f aca="false">IF(OR(C101="",N(J101)=0),"",K101*2*(N(H101)*پارامترها!$B$4+N(I101)*پارامترها!$B$5)/J101)</f>
         <v/>
       </c>
-      <c r="S101" s="10" t="str">
+      <c r="S101" s="12" t="str">
+        <f aca="false">IF(C101="","",N(M101)*پارامترها!$B$6+N(N101)*پارامترها!$B$7+N(O101)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T101" s="12" t="str">
+        <f aca="false">IF(C101="","",N(R101)+N(S101))</f>
+        <v/>
+      </c>
+      <c r="U101" s="10" t="str">
         <f aca="false">IF(C101="","",IF(P101&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L101)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T101" s="11"/>
+      <c r="V101" s="11"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="str">
@@ -5036,11 +5887,19 @@
         <f aca="false">IF(OR(C102="",N(J102)=0),"",K102*2*(N(H102)*پارامترها!$B$4+N(I102)*پارامترها!$B$5)/J102)</f>
         <v/>
       </c>
-      <c r="S102" s="10" t="str">
+      <c r="S102" s="12" t="str">
+        <f aca="false">IF(C102="","",N(M102)*پارامترها!$B$6+N(N102)*پارامترها!$B$7+N(O102)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T102" s="12" t="str">
+        <f aca="false">IF(C102="","",N(R102)+N(S102))</f>
+        <v/>
+      </c>
+      <c r="U102" s="10" t="str">
         <f aca="false">IF(C102="","",IF(P102&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L102)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T102" s="11"/>
+      <c r="V102" s="11"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="str">
@@ -5076,11 +5935,19 @@
         <f aca="false">IF(OR(C103="",N(J103)=0),"",K103*2*(N(H103)*پارامترها!$B$4+N(I103)*پارامترها!$B$5)/J103)</f>
         <v/>
       </c>
-      <c r="S103" s="10" t="str">
+      <c r="S103" s="12" t="str">
+        <f aca="false">IF(C103="","",N(M103)*پارامترها!$B$6+N(N103)*پارامترها!$B$7+N(O103)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T103" s="12" t="str">
+        <f aca="false">IF(C103="","",N(R103)+N(S103))</f>
+        <v/>
+      </c>
+      <c r="U103" s="10" t="str">
         <f aca="false">IF(C103="","",IF(P103&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L103)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T103" s="11"/>
+      <c r="V103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="str">
@@ -5116,11 +5983,19 @@
         <f aca="false">IF(OR(C104="",N(J104)=0),"",K104*2*(N(H104)*پارامترها!$B$4+N(I104)*پارامترها!$B$5)/J104)</f>
         <v/>
       </c>
-      <c r="S104" s="10" t="str">
+      <c r="S104" s="12" t="str">
+        <f aca="false">IF(C104="","",N(M104)*پارامترها!$B$6+N(N104)*پارامترها!$B$7+N(O104)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T104" s="12" t="str">
+        <f aca="false">IF(C104="","",N(R104)+N(S104))</f>
+        <v/>
+      </c>
+      <c r="U104" s="10" t="str">
         <f aca="false">IF(C104="","",IF(P104&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L104)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T104" s="11"/>
+      <c r="V104" s="11"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="str">
@@ -5156,11 +6031,19 @@
         <f aca="false">IF(OR(C105="",N(J105)=0),"",K105*2*(N(H105)*پارامترها!$B$4+N(I105)*پارامترها!$B$5)/J105)</f>
         <v/>
       </c>
-      <c r="S105" s="10" t="str">
+      <c r="S105" s="12" t="str">
+        <f aca="false">IF(C105="","",N(M105)*پارامترها!$B$6+N(N105)*پارامترها!$B$7+N(O105)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T105" s="12" t="str">
+        <f aca="false">IF(C105="","",N(R105)+N(S105))</f>
+        <v/>
+      </c>
+      <c r="U105" s="10" t="str">
         <f aca="false">IF(C105="","",IF(P105&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L105)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T105" s="11"/>
+      <c r="V105" s="11"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="str">
@@ -5196,11 +6079,19 @@
         <f aca="false">IF(OR(C106="",N(J106)=0),"",K106*2*(N(H106)*پارامترها!$B$4+N(I106)*پارامترها!$B$5)/J106)</f>
         <v/>
       </c>
-      <c r="S106" s="10" t="str">
+      <c r="S106" s="12" t="str">
+        <f aca="false">IF(C106="","",N(M106)*پارامترها!$B$6+N(N106)*پارامترها!$B$7+N(O106)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T106" s="12" t="str">
+        <f aca="false">IF(C106="","",N(R106)+N(S106))</f>
+        <v/>
+      </c>
+      <c r="U106" s="10" t="str">
         <f aca="false">IF(C106="","",IF(P106&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L106)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T106" s="11"/>
+      <c r="V106" s="11"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="str">
@@ -5236,11 +6127,19 @@
         <f aca="false">IF(OR(C107="",N(J107)=0),"",K107*2*(N(H107)*پارامترها!$B$4+N(I107)*پارامترها!$B$5)/J107)</f>
         <v/>
       </c>
-      <c r="S107" s="10" t="str">
+      <c r="S107" s="12" t="str">
+        <f aca="false">IF(C107="","",N(M107)*پارامترها!$B$6+N(N107)*پارامترها!$B$7+N(O107)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T107" s="12" t="str">
+        <f aca="false">IF(C107="","",N(R107)+N(S107))</f>
+        <v/>
+      </c>
+      <c r="U107" s="10" t="str">
         <f aca="false">IF(C107="","",IF(P107&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L107)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T107" s="11"/>
+      <c r="V107" s="11"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="str">
@@ -5276,11 +6175,19 @@
         <f aca="false">IF(OR(C108="",N(J108)=0),"",K108*2*(N(H108)*پارامترها!$B$4+N(I108)*پارامترها!$B$5)/J108)</f>
         <v/>
       </c>
-      <c r="S108" s="10" t="str">
+      <c r="S108" s="12" t="str">
+        <f aca="false">IF(C108="","",N(M108)*پارامترها!$B$6+N(N108)*پارامترها!$B$7+N(O108)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T108" s="12" t="str">
+        <f aca="false">IF(C108="","",N(R108)+N(S108))</f>
+        <v/>
+      </c>
+      <c r="U108" s="10" t="str">
         <f aca="false">IF(C108="","",IF(P108&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L108)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T108" s="11"/>
+      <c r="V108" s="11"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="str">
@@ -5316,11 +6223,19 @@
         <f aca="false">IF(OR(C109="",N(J109)=0),"",K109*2*(N(H109)*پارامترها!$B$4+N(I109)*پارامترها!$B$5)/J109)</f>
         <v/>
       </c>
-      <c r="S109" s="10" t="str">
+      <c r="S109" s="12" t="str">
+        <f aca="false">IF(C109="","",N(M109)*پارامترها!$B$6+N(N109)*پارامترها!$B$7+N(O109)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T109" s="12" t="str">
+        <f aca="false">IF(C109="","",N(R109)+N(S109))</f>
+        <v/>
+      </c>
+      <c r="U109" s="10" t="str">
         <f aca="false">IF(C109="","",IF(P109&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L109)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T109" s="11"/>
+      <c r="V109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="str">
@@ -5356,11 +6271,19 @@
         <f aca="false">IF(OR(C110="",N(J110)=0),"",K110*2*(N(H110)*پارامترها!$B$4+N(I110)*پارامترها!$B$5)/J110)</f>
         <v/>
       </c>
-      <c r="S110" s="10" t="str">
+      <c r="S110" s="12" t="str">
+        <f aca="false">IF(C110="","",N(M110)*پارامترها!$B$6+N(N110)*پارامترها!$B$7+N(O110)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T110" s="12" t="str">
+        <f aca="false">IF(C110="","",N(R110)+N(S110))</f>
+        <v/>
+      </c>
+      <c r="U110" s="10" t="str">
         <f aca="false">IF(C110="","",IF(P110&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L110)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T110" s="11"/>
+      <c r="V110" s="11"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="str">
@@ -5396,11 +6319,19 @@
         <f aca="false">IF(OR(C111="",N(J111)=0),"",K111*2*(N(H111)*پارامترها!$B$4+N(I111)*پارامترها!$B$5)/J111)</f>
         <v/>
       </c>
-      <c r="S111" s="10" t="str">
+      <c r="S111" s="12" t="str">
+        <f aca="false">IF(C111="","",N(M111)*پارامترها!$B$6+N(N111)*پارامترها!$B$7+N(O111)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T111" s="12" t="str">
+        <f aca="false">IF(C111="","",N(R111)+N(S111))</f>
+        <v/>
+      </c>
+      <c r="U111" s="10" t="str">
         <f aca="false">IF(C111="","",IF(P111&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L111)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T111" s="11"/>
+      <c r="V111" s="11"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="str">
@@ -5436,11 +6367,19 @@
         <f aca="false">IF(OR(C112="",N(J112)=0),"",K112*2*(N(H112)*پارامترها!$B$4+N(I112)*پارامترها!$B$5)/J112)</f>
         <v/>
       </c>
-      <c r="S112" s="10" t="str">
+      <c r="S112" s="12" t="str">
+        <f aca="false">IF(C112="","",N(M112)*پارامترها!$B$6+N(N112)*پارامترها!$B$7+N(O112)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T112" s="12" t="str">
+        <f aca="false">IF(C112="","",N(R112)+N(S112))</f>
+        <v/>
+      </c>
+      <c r="U112" s="10" t="str">
         <f aca="false">IF(C112="","",IF(P112&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L112)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T112" s="11"/>
+      <c r="V112" s="11"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="str">
@@ -5476,11 +6415,19 @@
         <f aca="false">IF(OR(C113="",N(J113)=0),"",K113*2*(N(H113)*پارامترها!$B$4+N(I113)*پارامترها!$B$5)/J113)</f>
         <v/>
       </c>
-      <c r="S113" s="10" t="str">
+      <c r="S113" s="12" t="str">
+        <f aca="false">IF(C113="","",N(M113)*پارامترها!$B$6+N(N113)*پارامترها!$B$7+N(O113)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T113" s="12" t="str">
+        <f aca="false">IF(C113="","",N(R113)+N(S113))</f>
+        <v/>
+      </c>
+      <c r="U113" s="10" t="str">
         <f aca="false">IF(C113="","",IF(P113&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L113)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T113" s="11"/>
+      <c r="V113" s="11"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="str">
@@ -5516,11 +6463,19 @@
         <f aca="false">IF(OR(C114="",N(J114)=0),"",K114*2*(N(H114)*پارامترها!$B$4+N(I114)*پارامترها!$B$5)/J114)</f>
         <v/>
       </c>
-      <c r="S114" s="10" t="str">
+      <c r="S114" s="12" t="str">
+        <f aca="false">IF(C114="","",N(M114)*پارامترها!$B$6+N(N114)*پارامترها!$B$7+N(O114)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T114" s="12" t="str">
+        <f aca="false">IF(C114="","",N(R114)+N(S114))</f>
+        <v/>
+      </c>
+      <c r="U114" s="10" t="str">
         <f aca="false">IF(C114="","",IF(P114&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L114)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T114" s="11"/>
+      <c r="V114" s="11"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="str">
@@ -5556,11 +6511,19 @@
         <f aca="false">IF(OR(C115="",N(J115)=0),"",K115*2*(N(H115)*پارامترها!$B$4+N(I115)*پارامترها!$B$5)/J115)</f>
         <v/>
       </c>
-      <c r="S115" s="10" t="str">
+      <c r="S115" s="12" t="str">
+        <f aca="false">IF(C115="","",N(M115)*پارامترها!$B$6+N(N115)*پارامترها!$B$7+N(O115)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T115" s="12" t="str">
+        <f aca="false">IF(C115="","",N(R115)+N(S115))</f>
+        <v/>
+      </c>
+      <c r="U115" s="10" t="str">
         <f aca="false">IF(C115="","",IF(P115&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L115)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T115" s="11"/>
+      <c r="V115" s="11"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="str">
@@ -5596,11 +6559,19 @@
         <f aca="false">IF(OR(C116="",N(J116)=0),"",K116*2*(N(H116)*پارامترها!$B$4+N(I116)*پارامترها!$B$5)/J116)</f>
         <v/>
       </c>
-      <c r="S116" s="10" t="str">
+      <c r="S116" s="12" t="str">
+        <f aca="false">IF(C116="","",N(M116)*پارامترها!$B$6+N(N116)*پارامترها!$B$7+N(O116)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T116" s="12" t="str">
+        <f aca="false">IF(C116="","",N(R116)+N(S116))</f>
+        <v/>
+      </c>
+      <c r="U116" s="10" t="str">
         <f aca="false">IF(C116="","",IF(P116&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L116)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T116" s="11"/>
+      <c r="V116" s="11"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="str">
@@ -5636,11 +6607,19 @@
         <f aca="false">IF(OR(C117="",N(J117)=0),"",K117*2*(N(H117)*پارامترها!$B$4+N(I117)*پارامترها!$B$5)/J117)</f>
         <v/>
       </c>
-      <c r="S117" s="10" t="str">
+      <c r="S117" s="12" t="str">
+        <f aca="false">IF(C117="","",N(M117)*پارامترها!$B$6+N(N117)*پارامترها!$B$7+N(O117)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T117" s="12" t="str">
+        <f aca="false">IF(C117="","",N(R117)+N(S117))</f>
+        <v/>
+      </c>
+      <c r="U117" s="10" t="str">
         <f aca="false">IF(C117="","",IF(P117&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L117)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T117" s="11"/>
+      <c r="V117" s="11"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="str">
@@ -5676,11 +6655,19 @@
         <f aca="false">IF(OR(C118="",N(J118)=0),"",K118*2*(N(H118)*پارامترها!$B$4+N(I118)*پارامترها!$B$5)/J118)</f>
         <v/>
       </c>
-      <c r="S118" s="10" t="str">
+      <c r="S118" s="12" t="str">
+        <f aca="false">IF(C118="","",N(M118)*پارامترها!$B$6+N(N118)*پارامترها!$B$7+N(O118)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T118" s="12" t="str">
+        <f aca="false">IF(C118="","",N(R118)+N(S118))</f>
+        <v/>
+      </c>
+      <c r="U118" s="10" t="str">
         <f aca="false">IF(C118="","",IF(P118&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L118)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T118" s="11"/>
+      <c r="V118" s="11"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="str">
@@ -5716,11 +6703,19 @@
         <f aca="false">IF(OR(C119="",N(J119)=0),"",K119*2*(N(H119)*پارامترها!$B$4+N(I119)*پارامترها!$B$5)/J119)</f>
         <v/>
       </c>
-      <c r="S119" s="10" t="str">
+      <c r="S119" s="12" t="str">
+        <f aca="false">IF(C119="","",N(M119)*پارامترها!$B$6+N(N119)*پارامترها!$B$7+N(O119)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T119" s="12" t="str">
+        <f aca="false">IF(C119="","",N(R119)+N(S119))</f>
+        <v/>
+      </c>
+      <c r="U119" s="10" t="str">
         <f aca="false">IF(C119="","",IF(P119&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L119)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T119" s="11"/>
+      <c r="V119" s="11"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="str">
@@ -5756,11 +6751,19 @@
         <f aca="false">IF(OR(C120="",N(J120)=0),"",K120*2*(N(H120)*پارامترها!$B$4+N(I120)*پارامترها!$B$5)/J120)</f>
         <v/>
       </c>
-      <c r="S120" s="10" t="str">
+      <c r="S120" s="12" t="str">
+        <f aca="false">IF(C120="","",N(M120)*پارامترها!$B$6+N(N120)*پارامترها!$B$7+N(O120)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T120" s="12" t="str">
+        <f aca="false">IF(C120="","",N(R120)+N(S120))</f>
+        <v/>
+      </c>
+      <c r="U120" s="10" t="str">
         <f aca="false">IF(C120="","",IF(P120&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L120)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T120" s="11"/>
+      <c r="V120" s="11"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="str">
@@ -5796,11 +6799,19 @@
         <f aca="false">IF(OR(C121="",N(J121)=0),"",K121*2*(N(H121)*پارامترها!$B$4+N(I121)*پارامترها!$B$5)/J121)</f>
         <v/>
       </c>
-      <c r="S121" s="10" t="str">
+      <c r="S121" s="12" t="str">
+        <f aca="false">IF(C121="","",N(M121)*پارامترها!$B$6+N(N121)*پارامترها!$B$7+N(O121)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T121" s="12" t="str">
+        <f aca="false">IF(C121="","",N(R121)+N(S121))</f>
+        <v/>
+      </c>
+      <c r="U121" s="10" t="str">
         <f aca="false">IF(C121="","",IF(P121&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L121)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T121" s="11"/>
+      <c r="V121" s="11"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="str">
@@ -5836,11 +6847,19 @@
         <f aca="false">IF(OR(C122="",N(J122)=0),"",K122*2*(N(H122)*پارامترها!$B$4+N(I122)*پارامترها!$B$5)/J122)</f>
         <v/>
       </c>
-      <c r="S122" s="10" t="str">
+      <c r="S122" s="12" t="str">
+        <f aca="false">IF(C122="","",N(M122)*پارامترها!$B$6+N(N122)*پارامترها!$B$7+N(O122)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T122" s="12" t="str">
+        <f aca="false">IF(C122="","",N(R122)+N(S122))</f>
+        <v/>
+      </c>
+      <c r="U122" s="10" t="str">
         <f aca="false">IF(C122="","",IF(P122&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L122)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T122" s="11"/>
+      <c r="V122" s="11"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="str">
@@ -5876,11 +6895,19 @@
         <f aca="false">IF(OR(C123="",N(J123)=0),"",K123*2*(N(H123)*پارامترها!$B$4+N(I123)*پارامترها!$B$5)/J123)</f>
         <v/>
       </c>
-      <c r="S123" s="10" t="str">
+      <c r="S123" s="12" t="str">
+        <f aca="false">IF(C123="","",N(M123)*پارامترها!$B$6+N(N123)*پارامترها!$B$7+N(O123)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T123" s="12" t="str">
+        <f aca="false">IF(C123="","",N(R123)+N(S123))</f>
+        <v/>
+      </c>
+      <c r="U123" s="10" t="str">
         <f aca="false">IF(C123="","",IF(P123&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L123)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T123" s="11"/>
+      <c r="V123" s="11"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="str">
@@ -5916,11 +6943,19 @@
         <f aca="false">IF(OR(C124="",N(J124)=0),"",K124*2*(N(H124)*پارامترها!$B$4+N(I124)*پارامترها!$B$5)/J124)</f>
         <v/>
       </c>
-      <c r="S124" s="10" t="str">
+      <c r="S124" s="12" t="str">
+        <f aca="false">IF(C124="","",N(M124)*پارامترها!$B$6+N(N124)*پارامترها!$B$7+N(O124)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T124" s="12" t="str">
+        <f aca="false">IF(C124="","",N(R124)+N(S124))</f>
+        <v/>
+      </c>
+      <c r="U124" s="10" t="str">
         <f aca="false">IF(C124="","",IF(P124&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L124)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T124" s="11"/>
+      <c r="V124" s="11"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="str">
@@ -5956,11 +6991,19 @@
         <f aca="false">IF(OR(C125="",N(J125)=0),"",K125*2*(N(H125)*پارامترها!$B$4+N(I125)*پارامترها!$B$5)/J125)</f>
         <v/>
       </c>
-      <c r="S125" s="10" t="str">
+      <c r="S125" s="12" t="str">
+        <f aca="false">IF(C125="","",N(M125)*پارامترها!$B$6+N(N125)*پارامترها!$B$7+N(O125)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T125" s="12" t="str">
+        <f aca="false">IF(C125="","",N(R125)+N(S125))</f>
+        <v/>
+      </c>
+      <c r="U125" s="10" t="str">
         <f aca="false">IF(C125="","",IF(P125&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L125)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T125" s="11"/>
+      <c r="V125" s="11"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="str">
@@ -5996,11 +7039,19 @@
         <f aca="false">IF(OR(C126="",N(J126)=0),"",K126*2*(N(H126)*پارامترها!$B$4+N(I126)*پارامترها!$B$5)/J126)</f>
         <v/>
       </c>
-      <c r="S126" s="10" t="str">
+      <c r="S126" s="12" t="str">
+        <f aca="false">IF(C126="","",N(M126)*پارامترها!$B$6+N(N126)*پارامترها!$B$7+N(O126)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T126" s="12" t="str">
+        <f aca="false">IF(C126="","",N(R126)+N(S126))</f>
+        <v/>
+      </c>
+      <c r="U126" s="10" t="str">
         <f aca="false">IF(C126="","",IF(P126&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L126)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T126" s="11"/>
+      <c r="V126" s="11"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="str">
@@ -6036,11 +7087,19 @@
         <f aca="false">IF(OR(C127="",N(J127)=0),"",K127*2*(N(H127)*پارامترها!$B$4+N(I127)*پارامترها!$B$5)/J127)</f>
         <v/>
       </c>
-      <c r="S127" s="10" t="str">
+      <c r="S127" s="12" t="str">
+        <f aca="false">IF(C127="","",N(M127)*پارامترها!$B$6+N(N127)*پارامترها!$B$7+N(O127)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T127" s="12" t="str">
+        <f aca="false">IF(C127="","",N(R127)+N(S127))</f>
+        <v/>
+      </c>
+      <c r="U127" s="10" t="str">
         <f aca="false">IF(C127="","",IF(P127&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L127)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T127" s="11"/>
+      <c r="V127" s="11"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="str">
@@ -6076,11 +7135,19 @@
         <f aca="false">IF(OR(C128="",N(J128)=0),"",K128*2*(N(H128)*پارامترها!$B$4+N(I128)*پارامترها!$B$5)/J128)</f>
         <v/>
       </c>
-      <c r="S128" s="10" t="str">
+      <c r="S128" s="12" t="str">
+        <f aca="false">IF(C128="","",N(M128)*پارامترها!$B$6+N(N128)*پارامترها!$B$7+N(O128)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T128" s="12" t="str">
+        <f aca="false">IF(C128="","",N(R128)+N(S128))</f>
+        <v/>
+      </c>
+      <c r="U128" s="10" t="str">
         <f aca="false">IF(C128="","",IF(P128&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L128)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T128" s="11"/>
+      <c r="V128" s="11"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="str">
@@ -6116,11 +7183,19 @@
         <f aca="false">IF(OR(C129="",N(J129)=0),"",K129*2*(N(H129)*پارامترها!$B$4+N(I129)*پارامترها!$B$5)/J129)</f>
         <v/>
       </c>
-      <c r="S129" s="10" t="str">
+      <c r="S129" s="12" t="str">
+        <f aca="false">IF(C129="","",N(M129)*پارامترها!$B$6+N(N129)*پارامترها!$B$7+N(O129)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T129" s="12" t="str">
+        <f aca="false">IF(C129="","",N(R129)+N(S129))</f>
+        <v/>
+      </c>
+      <c r="U129" s="10" t="str">
         <f aca="false">IF(C129="","",IF(P129&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L129)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T129" s="11"/>
+      <c r="V129" s="11"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="str">
@@ -6156,11 +7231,19 @@
         <f aca="false">IF(OR(C130="",N(J130)=0),"",K130*2*(N(H130)*پارامترها!$B$4+N(I130)*پارامترها!$B$5)/J130)</f>
         <v/>
       </c>
-      <c r="S130" s="10" t="str">
+      <c r="S130" s="12" t="str">
+        <f aca="false">IF(C130="","",N(M130)*پارامترها!$B$6+N(N130)*پارامترها!$B$7+N(O130)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T130" s="12" t="str">
+        <f aca="false">IF(C130="","",N(R130)+N(S130))</f>
+        <v/>
+      </c>
+      <c r="U130" s="10" t="str">
         <f aca="false">IF(C130="","",IF(P130&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L130)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T130" s="11"/>
+      <c r="V130" s="11"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="str">
@@ -6196,11 +7279,19 @@
         <f aca="false">IF(OR(C131="",N(J131)=0),"",K131*2*(N(H131)*پارامترها!$B$4+N(I131)*پارامترها!$B$5)/J131)</f>
         <v/>
       </c>
-      <c r="S131" s="10" t="str">
+      <c r="S131" s="12" t="str">
+        <f aca="false">IF(C131="","",N(M131)*پارامترها!$B$6+N(N131)*پارامترها!$B$7+N(O131)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T131" s="12" t="str">
+        <f aca="false">IF(C131="","",N(R131)+N(S131))</f>
+        <v/>
+      </c>
+      <c r="U131" s="10" t="str">
         <f aca="false">IF(C131="","",IF(P131&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L131)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T131" s="11"/>
+      <c r="V131" s="11"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="str">
@@ -6236,11 +7327,19 @@
         <f aca="false">IF(OR(C132="",N(J132)=0),"",K132*2*(N(H132)*پارامترها!$B$4+N(I132)*پارامترها!$B$5)/J132)</f>
         <v/>
       </c>
-      <c r="S132" s="10" t="str">
+      <c r="S132" s="12" t="str">
+        <f aca="false">IF(C132="","",N(M132)*پارامترها!$B$6+N(N132)*پارامترها!$B$7+N(O132)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T132" s="12" t="str">
+        <f aca="false">IF(C132="","",N(R132)+N(S132))</f>
+        <v/>
+      </c>
+      <c r="U132" s="10" t="str">
         <f aca="false">IF(C132="","",IF(P132&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L132)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T132" s="11"/>
+      <c r="V132" s="11"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="str">
@@ -6276,11 +7375,19 @@
         <f aca="false">IF(OR(C133="",N(J133)=0),"",K133*2*(N(H133)*پارامترها!$B$4+N(I133)*پارامترها!$B$5)/J133)</f>
         <v/>
       </c>
-      <c r="S133" s="10" t="str">
+      <c r="S133" s="12" t="str">
+        <f aca="false">IF(C133="","",N(M133)*پارامترها!$B$6+N(N133)*پارامترها!$B$7+N(O133)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T133" s="12" t="str">
+        <f aca="false">IF(C133="","",N(R133)+N(S133))</f>
+        <v/>
+      </c>
+      <c r="U133" s="10" t="str">
         <f aca="false">IF(C133="","",IF(P133&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L133)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T133" s="11"/>
+      <c r="V133" s="11"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="str">
@@ -6316,11 +7423,19 @@
         <f aca="false">IF(OR(C134="",N(J134)=0),"",K134*2*(N(H134)*پارامترها!$B$4+N(I134)*پارامترها!$B$5)/J134)</f>
         <v/>
       </c>
-      <c r="S134" s="10" t="str">
+      <c r="S134" s="12" t="str">
+        <f aca="false">IF(C134="","",N(M134)*پارامترها!$B$6+N(N134)*پارامترها!$B$7+N(O134)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T134" s="12" t="str">
+        <f aca="false">IF(C134="","",N(R134)+N(S134))</f>
+        <v/>
+      </c>
+      <c r="U134" s="10" t="str">
         <f aca="false">IF(C134="","",IF(P134&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L134)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T134" s="11"/>
+      <c r="V134" s="11"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="str">
@@ -6356,11 +7471,19 @@
         <f aca="false">IF(OR(C135="",N(J135)=0),"",K135*2*(N(H135)*پارامترها!$B$4+N(I135)*پارامترها!$B$5)/J135)</f>
         <v/>
       </c>
-      <c r="S135" s="10" t="str">
+      <c r="S135" s="12" t="str">
+        <f aca="false">IF(C135="","",N(M135)*پارامترها!$B$6+N(N135)*پارامترها!$B$7+N(O135)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T135" s="12" t="str">
+        <f aca="false">IF(C135="","",N(R135)+N(S135))</f>
+        <v/>
+      </c>
+      <c r="U135" s="10" t="str">
         <f aca="false">IF(C135="","",IF(P135&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L135)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T135" s="11"/>
+      <c r="V135" s="11"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="str">
@@ -6396,11 +7519,19 @@
         <f aca="false">IF(OR(C136="",N(J136)=0),"",K136*2*(N(H136)*پارامترها!$B$4+N(I136)*پارامترها!$B$5)/J136)</f>
         <v/>
       </c>
-      <c r="S136" s="10" t="str">
+      <c r="S136" s="12" t="str">
+        <f aca="false">IF(C136="","",N(M136)*پارامترها!$B$6+N(N136)*پارامترها!$B$7+N(O136)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T136" s="12" t="str">
+        <f aca="false">IF(C136="","",N(R136)+N(S136))</f>
+        <v/>
+      </c>
+      <c r="U136" s="10" t="str">
         <f aca="false">IF(C136="","",IF(P136&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L136)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T136" s="11"/>
+      <c r="V136" s="11"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="10" t="str">
@@ -6436,11 +7567,19 @@
         <f aca="false">IF(OR(C137="",N(J137)=0),"",K137*2*(N(H137)*پارامترها!$B$4+N(I137)*پارامترها!$B$5)/J137)</f>
         <v/>
       </c>
-      <c r="S137" s="10" t="str">
+      <c r="S137" s="12" t="str">
+        <f aca="false">IF(C137="","",N(M137)*پارامترها!$B$6+N(N137)*پارامترها!$B$7+N(O137)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T137" s="12" t="str">
+        <f aca="false">IF(C137="","",N(R137)+N(S137))</f>
+        <v/>
+      </c>
+      <c r="U137" s="10" t="str">
         <f aca="false">IF(C137="","",IF(P137&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L137)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T137" s="11"/>
+      <c r="V137" s="11"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="str">
@@ -6476,11 +7615,19 @@
         <f aca="false">IF(OR(C138="",N(J138)=0),"",K138*2*(N(H138)*پارامترها!$B$4+N(I138)*پارامترها!$B$5)/J138)</f>
         <v/>
       </c>
-      <c r="S138" s="10" t="str">
+      <c r="S138" s="12" t="str">
+        <f aca="false">IF(C138="","",N(M138)*پارامترها!$B$6+N(N138)*پارامترها!$B$7+N(O138)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T138" s="12" t="str">
+        <f aca="false">IF(C138="","",N(R138)+N(S138))</f>
+        <v/>
+      </c>
+      <c r="U138" s="10" t="str">
         <f aca="false">IF(C138="","",IF(P138&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L138)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T138" s="11"/>
+      <c r="V138" s="11"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="str">
@@ -6516,11 +7663,19 @@
         <f aca="false">IF(OR(C139="",N(J139)=0),"",K139*2*(N(H139)*پارامترها!$B$4+N(I139)*پارامترها!$B$5)/J139)</f>
         <v/>
       </c>
-      <c r="S139" s="10" t="str">
+      <c r="S139" s="12" t="str">
+        <f aca="false">IF(C139="","",N(M139)*پارامترها!$B$6+N(N139)*پارامترها!$B$7+N(O139)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T139" s="12" t="str">
+        <f aca="false">IF(C139="","",N(R139)+N(S139))</f>
+        <v/>
+      </c>
+      <c r="U139" s="10" t="str">
         <f aca="false">IF(C139="","",IF(P139&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L139)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T139" s="11"/>
+      <c r="V139" s="11"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="10" t="str">
@@ -6556,11 +7711,19 @@
         <f aca="false">IF(OR(C140="",N(J140)=0),"",K140*2*(N(H140)*پارامترها!$B$4+N(I140)*پارامترها!$B$5)/J140)</f>
         <v/>
       </c>
-      <c r="S140" s="10" t="str">
+      <c r="S140" s="12" t="str">
+        <f aca="false">IF(C140="","",N(M140)*پارامترها!$B$6+N(N140)*پارامترها!$B$7+N(O140)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T140" s="12" t="str">
+        <f aca="false">IF(C140="","",N(R140)+N(S140))</f>
+        <v/>
+      </c>
+      <c r="U140" s="10" t="str">
         <f aca="false">IF(C140="","",IF(P140&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L140)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T140" s="11"/>
+      <c r="V140" s="11"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="10" t="str">
@@ -6596,11 +7759,19 @@
         <f aca="false">IF(OR(C141="",N(J141)=0),"",K141*2*(N(H141)*پارامترها!$B$4+N(I141)*پارامترها!$B$5)/J141)</f>
         <v/>
       </c>
-      <c r="S141" s="10" t="str">
+      <c r="S141" s="12" t="str">
+        <f aca="false">IF(C141="","",N(M141)*پارامترها!$B$6+N(N141)*پارامترها!$B$7+N(O141)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T141" s="12" t="str">
+        <f aca="false">IF(C141="","",N(R141)+N(S141))</f>
+        <v/>
+      </c>
+      <c r="U141" s="10" t="str">
         <f aca="false">IF(C141="","",IF(P141&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L141)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T141" s="11"/>
+      <c r="V141" s="11"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="10" t="str">
@@ -6636,11 +7807,19 @@
         <f aca="false">IF(OR(C142="",N(J142)=0),"",K142*2*(N(H142)*پارامترها!$B$4+N(I142)*پارامترها!$B$5)/J142)</f>
         <v/>
       </c>
-      <c r="S142" s="10" t="str">
+      <c r="S142" s="12" t="str">
+        <f aca="false">IF(C142="","",N(M142)*پارامترها!$B$6+N(N142)*پارامترها!$B$7+N(O142)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T142" s="12" t="str">
+        <f aca="false">IF(C142="","",N(R142)+N(S142))</f>
+        <v/>
+      </c>
+      <c r="U142" s="10" t="str">
         <f aca="false">IF(C142="","",IF(P142&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L142)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T142" s="11"/>
+      <c r="V142" s="11"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="10" t="str">
@@ -6676,11 +7855,19 @@
         <f aca="false">IF(OR(C143="",N(J143)=0),"",K143*2*(N(H143)*پارامترها!$B$4+N(I143)*پارامترها!$B$5)/J143)</f>
         <v/>
       </c>
-      <c r="S143" s="10" t="str">
+      <c r="S143" s="12" t="str">
+        <f aca="false">IF(C143="","",N(M143)*پارامترها!$B$6+N(N143)*پارامترها!$B$7+N(O143)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T143" s="12" t="str">
+        <f aca="false">IF(C143="","",N(R143)+N(S143))</f>
+        <v/>
+      </c>
+      <c r="U143" s="10" t="str">
         <f aca="false">IF(C143="","",IF(P143&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L143)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T143" s="11"/>
+      <c r="V143" s="11"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="str">
@@ -6716,11 +7903,19 @@
         <f aca="false">IF(OR(C144="",N(J144)=0),"",K144*2*(N(H144)*پارامترها!$B$4+N(I144)*پارامترها!$B$5)/J144)</f>
         <v/>
       </c>
-      <c r="S144" s="10" t="str">
+      <c r="S144" s="12" t="str">
+        <f aca="false">IF(C144="","",N(M144)*پارامترها!$B$6+N(N144)*پارامترها!$B$7+N(O144)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T144" s="12" t="str">
+        <f aca="false">IF(C144="","",N(R144)+N(S144))</f>
+        <v/>
+      </c>
+      <c r="U144" s="10" t="str">
         <f aca="false">IF(C144="","",IF(P144&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L144)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T144" s="11"/>
+      <c r="V144" s="11"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="str">
@@ -6756,11 +7951,19 @@
         <f aca="false">IF(OR(C145="",N(J145)=0),"",K145*2*(N(H145)*پارامترها!$B$4+N(I145)*پارامترها!$B$5)/J145)</f>
         <v/>
       </c>
-      <c r="S145" s="10" t="str">
+      <c r="S145" s="12" t="str">
+        <f aca="false">IF(C145="","",N(M145)*پارامترها!$B$6+N(N145)*پارامترها!$B$7+N(O145)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T145" s="12" t="str">
+        <f aca="false">IF(C145="","",N(R145)+N(S145))</f>
+        <v/>
+      </c>
+      <c r="U145" s="10" t="str">
         <f aca="false">IF(C145="","",IF(P145&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L145)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T145" s="11"/>
+      <c r="V145" s="11"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="10" t="str">
@@ -6796,11 +7999,19 @@
         <f aca="false">IF(OR(C146="",N(J146)=0),"",K146*2*(N(H146)*پارامترها!$B$4+N(I146)*پارامترها!$B$5)/J146)</f>
         <v/>
       </c>
-      <c r="S146" s="10" t="str">
+      <c r="S146" s="12" t="str">
+        <f aca="false">IF(C146="","",N(M146)*پارامترها!$B$6+N(N146)*پارامترها!$B$7+N(O146)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T146" s="12" t="str">
+        <f aca="false">IF(C146="","",N(R146)+N(S146))</f>
+        <v/>
+      </c>
+      <c r="U146" s="10" t="str">
         <f aca="false">IF(C146="","",IF(P146&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L146)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T146" s="11"/>
+      <c r="V146" s="11"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="10" t="str">
@@ -6836,11 +8047,19 @@
         <f aca="false">IF(OR(C147="",N(J147)=0),"",K147*2*(N(H147)*پارامترها!$B$4+N(I147)*پارامترها!$B$5)/J147)</f>
         <v/>
       </c>
-      <c r="S147" s="10" t="str">
+      <c r="S147" s="12" t="str">
+        <f aca="false">IF(C147="","",N(M147)*پارامترها!$B$6+N(N147)*پارامترها!$B$7+N(O147)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T147" s="12" t="str">
+        <f aca="false">IF(C147="","",N(R147)+N(S147))</f>
+        <v/>
+      </c>
+      <c r="U147" s="10" t="str">
         <f aca="false">IF(C147="","",IF(P147&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L147)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T147" s="11"/>
+      <c r="V147" s="11"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="str">
@@ -6876,11 +8095,19 @@
         <f aca="false">IF(OR(C148="",N(J148)=0),"",K148*2*(N(H148)*پارامترها!$B$4+N(I148)*پارامترها!$B$5)/J148)</f>
         <v/>
       </c>
-      <c r="S148" s="10" t="str">
+      <c r="S148" s="12" t="str">
+        <f aca="false">IF(C148="","",N(M148)*پارامترها!$B$6+N(N148)*پارامترها!$B$7+N(O148)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T148" s="12" t="str">
+        <f aca="false">IF(C148="","",N(R148)+N(S148))</f>
+        <v/>
+      </c>
+      <c r="U148" s="10" t="str">
         <f aca="false">IF(C148="","",IF(P148&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L148)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T148" s="11"/>
+      <c r="V148" s="11"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="str">
@@ -6916,11 +8143,19 @@
         <f aca="false">IF(OR(C149="",N(J149)=0),"",K149*2*(N(H149)*پارامترها!$B$4+N(I149)*پارامترها!$B$5)/J149)</f>
         <v/>
       </c>
-      <c r="S149" s="10" t="str">
+      <c r="S149" s="12" t="str">
+        <f aca="false">IF(C149="","",N(M149)*پارامترها!$B$6+N(N149)*پارامترها!$B$7+N(O149)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T149" s="12" t="str">
+        <f aca="false">IF(C149="","",N(R149)+N(S149))</f>
+        <v/>
+      </c>
+      <c r="U149" s="10" t="str">
         <f aca="false">IF(C149="","",IF(P149&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L149)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T149" s="11"/>
+      <c r="V149" s="11"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="str">
@@ -6956,11 +8191,19 @@
         <f aca="false">IF(OR(C150="",N(J150)=0),"",K150*2*(N(H150)*پارامترها!$B$4+N(I150)*پارامترها!$B$5)/J150)</f>
         <v/>
       </c>
-      <c r="S150" s="10" t="str">
+      <c r="S150" s="12" t="str">
+        <f aca="false">IF(C150="","",N(M150)*پارامترها!$B$6+N(N150)*پارامترها!$B$7+N(O150)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T150" s="12" t="str">
+        <f aca="false">IF(C150="","",N(R150)+N(S150))</f>
+        <v/>
+      </c>
+      <c r="U150" s="10" t="str">
         <f aca="false">IF(C150="","",IF(P150&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L150)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T150" s="11"/>
+      <c r="V150" s="11"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="str">
@@ -6996,11 +8239,19 @@
         <f aca="false">IF(OR(C151="",N(J151)=0),"",K151*2*(N(H151)*پارامترها!$B$4+N(I151)*پارامترها!$B$5)/J151)</f>
         <v/>
       </c>
-      <c r="S151" s="10" t="str">
+      <c r="S151" s="12" t="str">
+        <f aca="false">IF(C151="","",N(M151)*پارامترها!$B$6+N(N151)*پارامترها!$B$7+N(O151)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T151" s="12" t="str">
+        <f aca="false">IF(C151="","",N(R151)+N(S151))</f>
+        <v/>
+      </c>
+      <c r="U151" s="10" t="str">
         <f aca="false">IF(C151="","",IF(P151&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L151)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T151" s="11"/>
+      <c r="V151" s="11"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="str">
@@ -7036,11 +8287,19 @@
         <f aca="false">IF(OR(C152="",N(J152)=0),"",K152*2*(N(H152)*پارامترها!$B$4+N(I152)*پارامترها!$B$5)/J152)</f>
         <v/>
       </c>
-      <c r="S152" s="10" t="str">
+      <c r="S152" s="12" t="str">
+        <f aca="false">IF(C152="","",N(M152)*پارامترها!$B$6+N(N152)*پارامترها!$B$7+N(O152)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T152" s="12" t="str">
+        <f aca="false">IF(C152="","",N(R152)+N(S152))</f>
+        <v/>
+      </c>
+      <c r="U152" s="10" t="str">
         <f aca="false">IF(C152="","",IF(P152&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L152)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T152" s="11"/>
+      <c r="V152" s="11"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="str">
@@ -7076,11 +8335,19 @@
         <f aca="false">IF(OR(C153="",N(J153)=0),"",K153*2*(N(H153)*پارامترها!$B$4+N(I153)*پارامترها!$B$5)/J153)</f>
         <v/>
       </c>
-      <c r="S153" s="10" t="str">
+      <c r="S153" s="12" t="str">
+        <f aca="false">IF(C153="","",N(M153)*پارامترها!$B$6+N(N153)*پارامترها!$B$7+N(O153)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T153" s="12" t="str">
+        <f aca="false">IF(C153="","",N(R153)+N(S153))</f>
+        <v/>
+      </c>
+      <c r="U153" s="10" t="str">
         <f aca="false">IF(C153="","",IF(P153&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L153)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T153" s="11"/>
+      <c r="V153" s="11"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="str">
@@ -7116,11 +8383,19 @@
         <f aca="false">IF(OR(C154="",N(J154)=0),"",K154*2*(N(H154)*پارامترها!$B$4+N(I154)*پارامترها!$B$5)/J154)</f>
         <v/>
       </c>
-      <c r="S154" s="10" t="str">
+      <c r="S154" s="12" t="str">
+        <f aca="false">IF(C154="","",N(M154)*پارامترها!$B$6+N(N154)*پارامترها!$B$7+N(O154)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T154" s="12" t="str">
+        <f aca="false">IF(C154="","",N(R154)+N(S154))</f>
+        <v/>
+      </c>
+      <c r="U154" s="10" t="str">
         <f aca="false">IF(C154="","",IF(P154&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L154)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T154" s="11"/>
+      <c r="V154" s="11"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="10" t="str">
@@ -7156,11 +8431,19 @@
         <f aca="false">IF(OR(C155="",N(J155)=0),"",K155*2*(N(H155)*پارامترها!$B$4+N(I155)*پارامترها!$B$5)/J155)</f>
         <v/>
       </c>
-      <c r="S155" s="10" t="str">
+      <c r="S155" s="12" t="str">
+        <f aca="false">IF(C155="","",N(M155)*پارامترها!$B$6+N(N155)*پارامترها!$B$7+N(O155)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T155" s="12" t="str">
+        <f aca="false">IF(C155="","",N(R155)+N(S155))</f>
+        <v/>
+      </c>
+      <c r="U155" s="10" t="str">
         <f aca="false">IF(C155="","",IF(P155&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L155)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T155" s="11"/>
+      <c r="V155" s="11"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="str">
@@ -7196,11 +8479,19 @@
         <f aca="false">IF(OR(C156="",N(J156)=0),"",K156*2*(N(H156)*پارامترها!$B$4+N(I156)*پارامترها!$B$5)/J156)</f>
         <v/>
       </c>
-      <c r="S156" s="10" t="str">
+      <c r="S156" s="12" t="str">
+        <f aca="false">IF(C156="","",N(M156)*پارامترها!$B$6+N(N156)*پارامترها!$B$7+N(O156)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T156" s="12" t="str">
+        <f aca="false">IF(C156="","",N(R156)+N(S156))</f>
+        <v/>
+      </c>
+      <c r="U156" s="10" t="str">
         <f aca="false">IF(C156="","",IF(P156&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L156)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T156" s="11"/>
+      <c r="V156" s="11"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="str">
@@ -7236,11 +8527,19 @@
         <f aca="false">IF(OR(C157="",N(J157)=0),"",K157*2*(N(H157)*پارامترها!$B$4+N(I157)*پارامترها!$B$5)/J157)</f>
         <v/>
       </c>
-      <c r="S157" s="10" t="str">
+      <c r="S157" s="12" t="str">
+        <f aca="false">IF(C157="","",N(M157)*پارامترها!$B$6+N(N157)*پارامترها!$B$7+N(O157)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T157" s="12" t="str">
+        <f aca="false">IF(C157="","",N(R157)+N(S157))</f>
+        <v/>
+      </c>
+      <c r="U157" s="10" t="str">
         <f aca="false">IF(C157="","",IF(P157&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L157)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T157" s="11"/>
+      <c r="V157" s="11"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="str">
@@ -7276,11 +8575,19 @@
         <f aca="false">IF(OR(C158="",N(J158)=0),"",K158*2*(N(H158)*پارامترها!$B$4+N(I158)*پارامترها!$B$5)/J158)</f>
         <v/>
       </c>
-      <c r="S158" s="10" t="str">
+      <c r="S158" s="12" t="str">
+        <f aca="false">IF(C158="","",N(M158)*پارامترها!$B$6+N(N158)*پارامترها!$B$7+N(O158)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T158" s="12" t="str">
+        <f aca="false">IF(C158="","",N(R158)+N(S158))</f>
+        <v/>
+      </c>
+      <c r="U158" s="10" t="str">
         <f aca="false">IF(C158="","",IF(P158&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L158)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T158" s="11"/>
+      <c r="V158" s="11"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="10" t="str">
@@ -7316,11 +8623,19 @@
         <f aca="false">IF(OR(C159="",N(J159)=0),"",K159*2*(N(H159)*پارامترها!$B$4+N(I159)*پارامترها!$B$5)/J159)</f>
         <v/>
       </c>
-      <c r="S159" s="10" t="str">
+      <c r="S159" s="12" t="str">
+        <f aca="false">IF(C159="","",N(M159)*پارامترها!$B$6+N(N159)*پارامترها!$B$7+N(O159)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T159" s="12" t="str">
+        <f aca="false">IF(C159="","",N(R159)+N(S159))</f>
+        <v/>
+      </c>
+      <c r="U159" s="10" t="str">
         <f aca="false">IF(C159="","",IF(P159&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L159)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T159" s="11"/>
+      <c r="V159" s="11"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="str">
@@ -7356,11 +8671,19 @@
         <f aca="false">IF(OR(C160="",N(J160)=0),"",K160*2*(N(H160)*پارامترها!$B$4+N(I160)*پارامترها!$B$5)/J160)</f>
         <v/>
       </c>
-      <c r="S160" s="10" t="str">
+      <c r="S160" s="12" t="str">
+        <f aca="false">IF(C160="","",N(M160)*پارامترها!$B$6+N(N160)*پارامترها!$B$7+N(O160)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T160" s="12" t="str">
+        <f aca="false">IF(C160="","",N(R160)+N(S160))</f>
+        <v/>
+      </c>
+      <c r="U160" s="10" t="str">
         <f aca="false">IF(C160="","",IF(P160&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L160)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T160" s="11"/>
+      <c r="V160" s="11"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="str">
@@ -7396,11 +8719,19 @@
         <f aca="false">IF(OR(C161="",N(J161)=0),"",K161*2*(N(H161)*پارامترها!$B$4+N(I161)*پارامترها!$B$5)/J161)</f>
         <v/>
       </c>
-      <c r="S161" s="10" t="str">
+      <c r="S161" s="12" t="str">
+        <f aca="false">IF(C161="","",N(M161)*پارامترها!$B$6+N(N161)*پارامترها!$B$7+N(O161)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T161" s="12" t="str">
+        <f aca="false">IF(C161="","",N(R161)+N(S161))</f>
+        <v/>
+      </c>
+      <c r="U161" s="10" t="str">
         <f aca="false">IF(C161="","",IF(P161&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L161)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T161" s="11"/>
+      <c r="V161" s="11"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="str">
@@ -7436,11 +8767,19 @@
         <f aca="false">IF(OR(C162="",N(J162)=0),"",K162*2*(N(H162)*پارامترها!$B$4+N(I162)*پارامترها!$B$5)/J162)</f>
         <v/>
       </c>
-      <c r="S162" s="10" t="str">
+      <c r="S162" s="12" t="str">
+        <f aca="false">IF(C162="","",N(M162)*پارامترها!$B$6+N(N162)*پارامترها!$B$7+N(O162)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T162" s="12" t="str">
+        <f aca="false">IF(C162="","",N(R162)+N(S162))</f>
+        <v/>
+      </c>
+      <c r="U162" s="10" t="str">
         <f aca="false">IF(C162="","",IF(P162&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L162)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T162" s="11"/>
+      <c r="V162" s="11"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="10" t="str">
@@ -7476,11 +8815,19 @@
         <f aca="false">IF(OR(C163="",N(J163)=0),"",K163*2*(N(H163)*پارامترها!$B$4+N(I163)*پارامترها!$B$5)/J163)</f>
         <v/>
       </c>
-      <c r="S163" s="10" t="str">
+      <c r="S163" s="12" t="str">
+        <f aca="false">IF(C163="","",N(M163)*پارامترها!$B$6+N(N163)*پارامترها!$B$7+N(O163)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T163" s="12" t="str">
+        <f aca="false">IF(C163="","",N(R163)+N(S163))</f>
+        <v/>
+      </c>
+      <c r="U163" s="10" t="str">
         <f aca="false">IF(C163="","",IF(P163&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L163)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T163" s="11"/>
+      <c r="V163" s="11"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="10" t="str">
@@ -7516,11 +8863,19 @@
         <f aca="false">IF(OR(C164="",N(J164)=0),"",K164*2*(N(H164)*پارامترها!$B$4+N(I164)*پارامترها!$B$5)/J164)</f>
         <v/>
       </c>
-      <c r="S164" s="10" t="str">
+      <c r="S164" s="12" t="str">
+        <f aca="false">IF(C164="","",N(M164)*پارامترها!$B$6+N(N164)*پارامترها!$B$7+N(O164)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T164" s="12" t="str">
+        <f aca="false">IF(C164="","",N(R164)+N(S164))</f>
+        <v/>
+      </c>
+      <c r="U164" s="10" t="str">
         <f aca="false">IF(C164="","",IF(P164&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L164)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T164" s="11"/>
+      <c r="V164" s="11"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="10" t="str">
@@ -7556,11 +8911,19 @@
         <f aca="false">IF(OR(C165="",N(J165)=0),"",K165*2*(N(H165)*پارامترها!$B$4+N(I165)*پارامترها!$B$5)/J165)</f>
         <v/>
       </c>
-      <c r="S165" s="10" t="str">
+      <c r="S165" s="12" t="str">
+        <f aca="false">IF(C165="","",N(M165)*پارامترها!$B$6+N(N165)*پارامترها!$B$7+N(O165)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T165" s="12" t="str">
+        <f aca="false">IF(C165="","",N(R165)+N(S165))</f>
+        <v/>
+      </c>
+      <c r="U165" s="10" t="str">
         <f aca="false">IF(C165="","",IF(P165&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L165)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T165" s="11"/>
+      <c r="V165" s="11"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="10" t="str">
@@ -7596,11 +8959,19 @@
         <f aca="false">IF(OR(C166="",N(J166)=0),"",K166*2*(N(H166)*پارامترها!$B$4+N(I166)*پارامترها!$B$5)/J166)</f>
         <v/>
       </c>
-      <c r="S166" s="10" t="str">
+      <c r="S166" s="12" t="str">
+        <f aca="false">IF(C166="","",N(M166)*پارامترها!$B$6+N(N166)*پارامترها!$B$7+N(O166)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T166" s="12" t="str">
+        <f aca="false">IF(C166="","",N(R166)+N(S166))</f>
+        <v/>
+      </c>
+      <c r="U166" s="10" t="str">
         <f aca="false">IF(C166="","",IF(P166&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L166)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T166" s="11"/>
+      <c r="V166" s="11"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="10" t="str">
@@ -7636,11 +9007,19 @@
         <f aca="false">IF(OR(C167="",N(J167)=0),"",K167*2*(N(H167)*پارامترها!$B$4+N(I167)*پارامترها!$B$5)/J167)</f>
         <v/>
       </c>
-      <c r="S167" s="10" t="str">
+      <c r="S167" s="12" t="str">
+        <f aca="false">IF(C167="","",N(M167)*پارامترها!$B$6+N(N167)*پارامترها!$B$7+N(O167)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T167" s="12" t="str">
+        <f aca="false">IF(C167="","",N(R167)+N(S167))</f>
+        <v/>
+      </c>
+      <c r="U167" s="10" t="str">
         <f aca="false">IF(C167="","",IF(P167&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L167)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T167" s="11"/>
+      <c r="V167" s="11"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="10" t="str">
@@ -7676,11 +9055,19 @@
         <f aca="false">IF(OR(C168="",N(J168)=0),"",K168*2*(N(H168)*پارامترها!$B$4+N(I168)*پارامترها!$B$5)/J168)</f>
         <v/>
       </c>
-      <c r="S168" s="10" t="str">
+      <c r="S168" s="12" t="str">
+        <f aca="false">IF(C168="","",N(M168)*پارامترها!$B$6+N(N168)*پارامترها!$B$7+N(O168)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T168" s="12" t="str">
+        <f aca="false">IF(C168="","",N(R168)+N(S168))</f>
+        <v/>
+      </c>
+      <c r="U168" s="10" t="str">
         <f aca="false">IF(C168="","",IF(P168&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L168)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T168" s="11"/>
+      <c r="V168" s="11"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="10" t="str">
@@ -7716,11 +9103,19 @@
         <f aca="false">IF(OR(C169="",N(J169)=0),"",K169*2*(N(H169)*پارامترها!$B$4+N(I169)*پارامترها!$B$5)/J169)</f>
         <v/>
       </c>
-      <c r="S169" s="10" t="str">
+      <c r="S169" s="12" t="str">
+        <f aca="false">IF(C169="","",N(M169)*پارامترها!$B$6+N(N169)*پارامترها!$B$7+N(O169)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T169" s="12" t="str">
+        <f aca="false">IF(C169="","",N(R169)+N(S169))</f>
+        <v/>
+      </c>
+      <c r="U169" s="10" t="str">
         <f aca="false">IF(C169="","",IF(P169&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L169)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T169" s="11"/>
+      <c r="V169" s="11"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="10" t="str">
@@ -7756,11 +9151,19 @@
         <f aca="false">IF(OR(C170="",N(J170)=0),"",K170*2*(N(H170)*پارامترها!$B$4+N(I170)*پارامترها!$B$5)/J170)</f>
         <v/>
       </c>
-      <c r="S170" s="10" t="str">
+      <c r="S170" s="12" t="str">
+        <f aca="false">IF(C170="","",N(M170)*پارامترها!$B$6+N(N170)*پارامترها!$B$7+N(O170)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T170" s="12" t="str">
+        <f aca="false">IF(C170="","",N(R170)+N(S170))</f>
+        <v/>
+      </c>
+      <c r="U170" s="10" t="str">
         <f aca="false">IF(C170="","",IF(P170&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L170)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T170" s="11"/>
+      <c r="V170" s="11"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="10" t="str">
@@ -7796,11 +9199,19 @@
         <f aca="false">IF(OR(C171="",N(J171)=0),"",K171*2*(N(H171)*پارامترها!$B$4+N(I171)*پارامترها!$B$5)/J171)</f>
         <v/>
       </c>
-      <c r="S171" s="10" t="str">
+      <c r="S171" s="12" t="str">
+        <f aca="false">IF(C171="","",N(M171)*پارامترها!$B$6+N(N171)*پارامترها!$B$7+N(O171)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T171" s="12" t="str">
+        <f aca="false">IF(C171="","",N(R171)+N(S171))</f>
+        <v/>
+      </c>
+      <c r="U171" s="10" t="str">
         <f aca="false">IF(C171="","",IF(P171&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L171)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T171" s="11"/>
+      <c r="V171" s="11"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="str">
@@ -7836,11 +9247,19 @@
         <f aca="false">IF(OR(C172="",N(J172)=0),"",K172*2*(N(H172)*پارامترها!$B$4+N(I172)*پارامترها!$B$5)/J172)</f>
         <v/>
       </c>
-      <c r="S172" s="10" t="str">
+      <c r="S172" s="12" t="str">
+        <f aca="false">IF(C172="","",N(M172)*پارامترها!$B$6+N(N172)*پارامترها!$B$7+N(O172)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T172" s="12" t="str">
+        <f aca="false">IF(C172="","",N(R172)+N(S172))</f>
+        <v/>
+      </c>
+      <c r="U172" s="10" t="str">
         <f aca="false">IF(C172="","",IF(P172&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L172)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T172" s="11"/>
+      <c r="V172" s="11"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="10" t="str">
@@ -7876,11 +9295,19 @@
         <f aca="false">IF(OR(C173="",N(J173)=0),"",K173*2*(N(H173)*پارامترها!$B$4+N(I173)*پارامترها!$B$5)/J173)</f>
         <v/>
       </c>
-      <c r="S173" s="10" t="str">
+      <c r="S173" s="12" t="str">
+        <f aca="false">IF(C173="","",N(M173)*پارامترها!$B$6+N(N173)*پارامترها!$B$7+N(O173)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T173" s="12" t="str">
+        <f aca="false">IF(C173="","",N(R173)+N(S173))</f>
+        <v/>
+      </c>
+      <c r="U173" s="10" t="str">
         <f aca="false">IF(C173="","",IF(P173&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L173)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T173" s="11"/>
+      <c r="V173" s="11"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="10" t="str">
@@ -7916,11 +9343,19 @@
         <f aca="false">IF(OR(C174="",N(J174)=0),"",K174*2*(N(H174)*پارامترها!$B$4+N(I174)*پارامترها!$B$5)/J174)</f>
         <v/>
       </c>
-      <c r="S174" s="10" t="str">
+      <c r="S174" s="12" t="str">
+        <f aca="false">IF(C174="","",N(M174)*پارامترها!$B$6+N(N174)*پارامترها!$B$7+N(O174)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T174" s="12" t="str">
+        <f aca="false">IF(C174="","",N(R174)+N(S174))</f>
+        <v/>
+      </c>
+      <c r="U174" s="10" t="str">
         <f aca="false">IF(C174="","",IF(P174&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L174)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T174" s="11"/>
+      <c r="V174" s="11"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="10" t="str">
@@ -7956,11 +9391,19 @@
         <f aca="false">IF(OR(C175="",N(J175)=0),"",K175*2*(N(H175)*پارامترها!$B$4+N(I175)*پارامترها!$B$5)/J175)</f>
         <v/>
       </c>
-      <c r="S175" s="10" t="str">
+      <c r="S175" s="12" t="str">
+        <f aca="false">IF(C175="","",N(M175)*پارامترها!$B$6+N(N175)*پارامترها!$B$7+N(O175)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T175" s="12" t="str">
+        <f aca="false">IF(C175="","",N(R175)+N(S175))</f>
+        <v/>
+      </c>
+      <c r="U175" s="10" t="str">
         <f aca="false">IF(C175="","",IF(P175&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L175)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T175" s="11"/>
+      <c r="V175" s="11"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="10" t="str">
@@ -7996,11 +9439,19 @@
         <f aca="false">IF(OR(C176="",N(J176)=0),"",K176*2*(N(H176)*پارامترها!$B$4+N(I176)*پارامترها!$B$5)/J176)</f>
         <v/>
       </c>
-      <c r="S176" s="10" t="str">
+      <c r="S176" s="12" t="str">
+        <f aca="false">IF(C176="","",N(M176)*پارامترها!$B$6+N(N176)*پارامترها!$B$7+N(O176)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T176" s="12" t="str">
+        <f aca="false">IF(C176="","",N(R176)+N(S176))</f>
+        <v/>
+      </c>
+      <c r="U176" s="10" t="str">
         <f aca="false">IF(C176="","",IF(P176&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L176)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T176" s="11"/>
+      <c r="V176" s="11"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="10" t="str">
@@ -8036,11 +9487,19 @@
         <f aca="false">IF(OR(C177="",N(J177)=0),"",K177*2*(N(H177)*پارامترها!$B$4+N(I177)*پارامترها!$B$5)/J177)</f>
         <v/>
       </c>
-      <c r="S177" s="10" t="str">
+      <c r="S177" s="12" t="str">
+        <f aca="false">IF(C177="","",N(M177)*پارامترها!$B$6+N(N177)*پارامترها!$B$7+N(O177)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T177" s="12" t="str">
+        <f aca="false">IF(C177="","",N(R177)+N(S177))</f>
+        <v/>
+      </c>
+      <c r="U177" s="10" t="str">
         <f aca="false">IF(C177="","",IF(P177&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L177)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T177" s="11"/>
+      <c r="V177" s="11"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="10" t="str">
@@ -8076,11 +9535,19 @@
         <f aca="false">IF(OR(C178="",N(J178)=0),"",K178*2*(N(H178)*پارامترها!$B$4+N(I178)*پارامترها!$B$5)/J178)</f>
         <v/>
       </c>
-      <c r="S178" s="10" t="str">
+      <c r="S178" s="12" t="str">
+        <f aca="false">IF(C178="","",N(M178)*پارامترها!$B$6+N(N178)*پارامترها!$B$7+N(O178)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T178" s="12" t="str">
+        <f aca="false">IF(C178="","",N(R178)+N(S178))</f>
+        <v/>
+      </c>
+      <c r="U178" s="10" t="str">
         <f aca="false">IF(C178="","",IF(P178&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L178)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T178" s="11"/>
+      <c r="V178" s="11"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="10" t="str">
@@ -8116,11 +9583,19 @@
         <f aca="false">IF(OR(C179="",N(J179)=0),"",K179*2*(N(H179)*پارامترها!$B$4+N(I179)*پارامترها!$B$5)/J179)</f>
         <v/>
       </c>
-      <c r="S179" s="10" t="str">
+      <c r="S179" s="12" t="str">
+        <f aca="false">IF(C179="","",N(M179)*پارامترها!$B$6+N(N179)*پارامترها!$B$7+N(O179)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T179" s="12" t="str">
+        <f aca="false">IF(C179="","",N(R179)+N(S179))</f>
+        <v/>
+      </c>
+      <c r="U179" s="10" t="str">
         <f aca="false">IF(C179="","",IF(P179&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L179)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T179" s="11"/>
+      <c r="V179" s="11"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="10" t="str">
@@ -8156,11 +9631,19 @@
         <f aca="false">IF(OR(C180="",N(J180)=0),"",K180*2*(N(H180)*پارامترها!$B$4+N(I180)*پارامترها!$B$5)/J180)</f>
         <v/>
       </c>
-      <c r="S180" s="10" t="str">
+      <c r="S180" s="12" t="str">
+        <f aca="false">IF(C180="","",N(M180)*پارامترها!$B$6+N(N180)*پارامترها!$B$7+N(O180)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T180" s="12" t="str">
+        <f aca="false">IF(C180="","",N(R180)+N(S180))</f>
+        <v/>
+      </c>
+      <c r="U180" s="10" t="str">
         <f aca="false">IF(C180="","",IF(P180&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L180)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T180" s="11"/>
+      <c r="V180" s="11"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="10" t="str">
@@ -8196,11 +9679,19 @@
         <f aca="false">IF(OR(C181="",N(J181)=0),"",K181*2*(N(H181)*پارامترها!$B$4+N(I181)*پارامترها!$B$5)/J181)</f>
         <v/>
       </c>
-      <c r="S181" s="10" t="str">
+      <c r="S181" s="12" t="str">
+        <f aca="false">IF(C181="","",N(M181)*پارامترها!$B$6+N(N181)*پارامترها!$B$7+N(O181)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T181" s="12" t="str">
+        <f aca="false">IF(C181="","",N(R181)+N(S181))</f>
+        <v/>
+      </c>
+      <c r="U181" s="10" t="str">
         <f aca="false">IF(C181="","",IF(P181&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L181)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T181" s="11"/>
+      <c r="V181" s="11"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="10" t="str">
@@ -8236,11 +9727,19 @@
         <f aca="false">IF(OR(C182="",N(J182)=0),"",K182*2*(N(H182)*پارامترها!$B$4+N(I182)*پارامترها!$B$5)/J182)</f>
         <v/>
       </c>
-      <c r="S182" s="10" t="str">
+      <c r="S182" s="12" t="str">
+        <f aca="false">IF(C182="","",N(M182)*پارامترها!$B$6+N(N182)*پارامترها!$B$7+N(O182)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T182" s="12" t="str">
+        <f aca="false">IF(C182="","",N(R182)+N(S182))</f>
+        <v/>
+      </c>
+      <c r="U182" s="10" t="str">
         <f aca="false">IF(C182="","",IF(P182&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L182)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T182" s="11"/>
+      <c r="V182" s="11"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="10" t="str">
@@ -8276,11 +9775,19 @@
         <f aca="false">IF(OR(C183="",N(J183)=0),"",K183*2*(N(H183)*پارامترها!$B$4+N(I183)*پارامترها!$B$5)/J183)</f>
         <v/>
       </c>
-      <c r="S183" s="10" t="str">
+      <c r="S183" s="12" t="str">
+        <f aca="false">IF(C183="","",N(M183)*پارامترها!$B$6+N(N183)*پارامترها!$B$7+N(O183)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T183" s="12" t="str">
+        <f aca="false">IF(C183="","",N(R183)+N(S183))</f>
+        <v/>
+      </c>
+      <c r="U183" s="10" t="str">
         <f aca="false">IF(C183="","",IF(P183&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L183)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T183" s="11"/>
+      <c r="V183" s="11"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="10" t="str">
@@ -8316,11 +9823,19 @@
         <f aca="false">IF(OR(C184="",N(J184)=0),"",K184*2*(N(H184)*پارامترها!$B$4+N(I184)*پارامترها!$B$5)/J184)</f>
         <v/>
       </c>
-      <c r="S184" s="10" t="str">
+      <c r="S184" s="12" t="str">
+        <f aca="false">IF(C184="","",N(M184)*پارامترها!$B$6+N(N184)*پارامترها!$B$7+N(O184)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T184" s="12" t="str">
+        <f aca="false">IF(C184="","",N(R184)+N(S184))</f>
+        <v/>
+      </c>
+      <c r="U184" s="10" t="str">
         <f aca="false">IF(C184="","",IF(P184&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L184)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T184" s="11"/>
+      <c r="V184" s="11"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="10" t="str">
@@ -8356,11 +9871,19 @@
         <f aca="false">IF(OR(C185="",N(J185)=0),"",K185*2*(N(H185)*پارامترها!$B$4+N(I185)*پارامترها!$B$5)/J185)</f>
         <v/>
       </c>
-      <c r="S185" s="10" t="str">
+      <c r="S185" s="12" t="str">
+        <f aca="false">IF(C185="","",N(M185)*پارامترها!$B$6+N(N185)*پارامترها!$B$7+N(O185)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T185" s="12" t="str">
+        <f aca="false">IF(C185="","",N(R185)+N(S185))</f>
+        <v/>
+      </c>
+      <c r="U185" s="10" t="str">
         <f aca="false">IF(C185="","",IF(P185&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L185)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T185" s="11"/>
+      <c r="V185" s="11"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="10" t="str">
@@ -8396,11 +9919,19 @@
         <f aca="false">IF(OR(C186="",N(J186)=0),"",K186*2*(N(H186)*پارامترها!$B$4+N(I186)*پارامترها!$B$5)/J186)</f>
         <v/>
       </c>
-      <c r="S186" s="10" t="str">
+      <c r="S186" s="12" t="str">
+        <f aca="false">IF(C186="","",N(M186)*پارامترها!$B$6+N(N186)*پارامترها!$B$7+N(O186)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T186" s="12" t="str">
+        <f aca="false">IF(C186="","",N(R186)+N(S186))</f>
+        <v/>
+      </c>
+      <c r="U186" s="10" t="str">
         <f aca="false">IF(C186="","",IF(P186&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L186)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T186" s="11"/>
+      <c r="V186" s="11"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="10" t="str">
@@ -8436,11 +9967,19 @@
         <f aca="false">IF(OR(C187="",N(J187)=0),"",K187*2*(N(H187)*پارامترها!$B$4+N(I187)*پارامترها!$B$5)/J187)</f>
         <v/>
       </c>
-      <c r="S187" s="10" t="str">
+      <c r="S187" s="12" t="str">
+        <f aca="false">IF(C187="","",N(M187)*پارامترها!$B$6+N(N187)*پارامترها!$B$7+N(O187)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T187" s="12" t="str">
+        <f aca="false">IF(C187="","",N(R187)+N(S187))</f>
+        <v/>
+      </c>
+      <c r="U187" s="10" t="str">
         <f aca="false">IF(C187="","",IF(P187&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L187)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T187" s="11"/>
+      <c r="V187" s="11"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="10" t="str">
@@ -8476,11 +10015,19 @@
         <f aca="false">IF(OR(C188="",N(J188)=0),"",K188*2*(N(H188)*پارامترها!$B$4+N(I188)*پارامترها!$B$5)/J188)</f>
         <v/>
       </c>
-      <c r="S188" s="10" t="str">
+      <c r="S188" s="12" t="str">
+        <f aca="false">IF(C188="","",N(M188)*پارامترها!$B$6+N(N188)*پارامترها!$B$7+N(O188)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T188" s="12" t="str">
+        <f aca="false">IF(C188="","",N(R188)+N(S188))</f>
+        <v/>
+      </c>
+      <c r="U188" s="10" t="str">
         <f aca="false">IF(C188="","",IF(P188&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L188)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T188" s="11"/>
+      <c r="V188" s="11"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="10" t="str">
@@ -8516,11 +10063,19 @@
         <f aca="false">IF(OR(C189="",N(J189)=0),"",K189*2*(N(H189)*پارامترها!$B$4+N(I189)*پارامترها!$B$5)/J189)</f>
         <v/>
       </c>
-      <c r="S189" s="10" t="str">
+      <c r="S189" s="12" t="str">
+        <f aca="false">IF(C189="","",N(M189)*پارامترها!$B$6+N(N189)*پارامترها!$B$7+N(O189)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T189" s="12" t="str">
+        <f aca="false">IF(C189="","",N(R189)+N(S189))</f>
+        <v/>
+      </c>
+      <c r="U189" s="10" t="str">
         <f aca="false">IF(C189="","",IF(P189&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L189)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T189" s="11"/>
+      <c r="V189" s="11"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="10" t="str">
@@ -8556,11 +10111,19 @@
         <f aca="false">IF(OR(C190="",N(J190)=0),"",K190*2*(N(H190)*پارامترها!$B$4+N(I190)*پارامترها!$B$5)/J190)</f>
         <v/>
       </c>
-      <c r="S190" s="10" t="str">
+      <c r="S190" s="12" t="str">
+        <f aca="false">IF(C190="","",N(M190)*پارامترها!$B$6+N(N190)*پارامترها!$B$7+N(O190)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T190" s="12" t="str">
+        <f aca="false">IF(C190="","",N(R190)+N(S190))</f>
+        <v/>
+      </c>
+      <c r="U190" s="10" t="str">
         <f aca="false">IF(C190="","",IF(P190&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L190)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T190" s="11"/>
+      <c r="V190" s="11"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="10" t="str">
@@ -8596,11 +10159,19 @@
         <f aca="false">IF(OR(C191="",N(J191)=0),"",K191*2*(N(H191)*پارامترها!$B$4+N(I191)*پارامترها!$B$5)/J191)</f>
         <v/>
       </c>
-      <c r="S191" s="10" t="str">
+      <c r="S191" s="12" t="str">
+        <f aca="false">IF(C191="","",N(M191)*پارامترها!$B$6+N(N191)*پارامترها!$B$7+N(O191)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T191" s="12" t="str">
+        <f aca="false">IF(C191="","",N(R191)+N(S191))</f>
+        <v/>
+      </c>
+      <c r="U191" s="10" t="str">
         <f aca="false">IF(C191="","",IF(P191&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L191)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T191" s="11"/>
+      <c r="V191" s="11"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="10" t="str">
@@ -8636,11 +10207,19 @@
         <f aca="false">IF(OR(C192="",N(J192)=0),"",K192*2*(N(H192)*پارامترها!$B$4+N(I192)*پارامترها!$B$5)/J192)</f>
         <v/>
       </c>
-      <c r="S192" s="10" t="str">
+      <c r="S192" s="12" t="str">
+        <f aca="false">IF(C192="","",N(M192)*پارامترها!$B$6+N(N192)*پارامترها!$B$7+N(O192)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T192" s="12" t="str">
+        <f aca="false">IF(C192="","",N(R192)+N(S192))</f>
+        <v/>
+      </c>
+      <c r="U192" s="10" t="str">
         <f aca="false">IF(C192="","",IF(P192&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L192)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T192" s="11"/>
+      <c r="V192" s="11"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="10" t="str">
@@ -8676,11 +10255,19 @@
         <f aca="false">IF(OR(C193="",N(J193)=0),"",K193*2*(N(H193)*پارامترها!$B$4+N(I193)*پارامترها!$B$5)/J193)</f>
         <v/>
       </c>
-      <c r="S193" s="10" t="str">
+      <c r="S193" s="12" t="str">
+        <f aca="false">IF(C193="","",N(M193)*پارامترها!$B$6+N(N193)*پارامترها!$B$7+N(O193)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T193" s="12" t="str">
+        <f aca="false">IF(C193="","",N(R193)+N(S193))</f>
+        <v/>
+      </c>
+      <c r="U193" s="10" t="str">
         <f aca="false">IF(C193="","",IF(P193&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L193)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T193" s="11"/>
+      <c r="V193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="10" t="str">
@@ -8716,11 +10303,19 @@
         <f aca="false">IF(OR(C194="",N(J194)=0),"",K194*2*(N(H194)*پارامترها!$B$4+N(I194)*پارامترها!$B$5)/J194)</f>
         <v/>
       </c>
-      <c r="S194" s="10" t="str">
+      <c r="S194" s="12" t="str">
+        <f aca="false">IF(C194="","",N(M194)*پارامترها!$B$6+N(N194)*پارامترها!$B$7+N(O194)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T194" s="12" t="str">
+        <f aca="false">IF(C194="","",N(R194)+N(S194))</f>
+        <v/>
+      </c>
+      <c r="U194" s="10" t="str">
         <f aca="false">IF(C194="","",IF(P194&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L194)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T194" s="11"/>
+      <c r="V194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="10" t="str">
@@ -8756,11 +10351,19 @@
         <f aca="false">IF(OR(C195="",N(J195)=0),"",K195*2*(N(H195)*پارامترها!$B$4+N(I195)*پارامترها!$B$5)/J195)</f>
         <v/>
       </c>
-      <c r="S195" s="10" t="str">
+      <c r="S195" s="12" t="str">
+        <f aca="false">IF(C195="","",N(M195)*پارامترها!$B$6+N(N195)*پارامترها!$B$7+N(O195)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T195" s="12" t="str">
+        <f aca="false">IF(C195="","",N(R195)+N(S195))</f>
+        <v/>
+      </c>
+      <c r="U195" s="10" t="str">
         <f aca="false">IF(C195="","",IF(P195&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L195)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T195" s="11"/>
+      <c r="V195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="10" t="str">
@@ -8796,11 +10399,19 @@
         <f aca="false">IF(OR(C196="",N(J196)=0),"",K196*2*(N(H196)*پارامترها!$B$4+N(I196)*پارامترها!$B$5)/J196)</f>
         <v/>
       </c>
-      <c r="S196" s="10" t="str">
+      <c r="S196" s="12" t="str">
+        <f aca="false">IF(C196="","",N(M196)*پارامترها!$B$6+N(N196)*پارامترها!$B$7+N(O196)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T196" s="12" t="str">
+        <f aca="false">IF(C196="","",N(R196)+N(S196))</f>
+        <v/>
+      </c>
+      <c r="U196" s="10" t="str">
         <f aca="false">IF(C196="","",IF(P196&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L196)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T196" s="11"/>
+      <c r="V196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="10" t="str">
@@ -8836,11 +10447,19 @@
         <f aca="false">IF(OR(C197="",N(J197)=0),"",K197*2*(N(H197)*پارامترها!$B$4+N(I197)*پارامترها!$B$5)/J197)</f>
         <v/>
       </c>
-      <c r="S197" s="10" t="str">
+      <c r="S197" s="12" t="str">
+        <f aca="false">IF(C197="","",N(M197)*پارامترها!$B$6+N(N197)*پارامترها!$B$7+N(O197)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T197" s="12" t="str">
+        <f aca="false">IF(C197="","",N(R197)+N(S197))</f>
+        <v/>
+      </c>
+      <c r="U197" s="10" t="str">
         <f aca="false">IF(C197="","",IF(P197&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L197)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T197" s="11"/>
+      <c r="V197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="10" t="str">
@@ -8876,11 +10495,19 @@
         <f aca="false">IF(OR(C198="",N(J198)=0),"",K198*2*(N(H198)*پارامترها!$B$4+N(I198)*پارامترها!$B$5)/J198)</f>
         <v/>
       </c>
-      <c r="S198" s="10" t="str">
+      <c r="S198" s="12" t="str">
+        <f aca="false">IF(C198="","",N(M198)*پارامترها!$B$6+N(N198)*پارامترها!$B$7+N(O198)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T198" s="12" t="str">
+        <f aca="false">IF(C198="","",N(R198)+N(S198))</f>
+        <v/>
+      </c>
+      <c r="U198" s="10" t="str">
         <f aca="false">IF(C198="","",IF(P198&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L198)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T198" s="11"/>
+      <c r="V198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="10" t="str">
@@ -8916,11 +10543,19 @@
         <f aca="false">IF(OR(C199="",N(J199)=0),"",K199*2*(N(H199)*پارامترها!$B$4+N(I199)*پارامترها!$B$5)/J199)</f>
         <v/>
       </c>
-      <c r="S199" s="10" t="str">
+      <c r="S199" s="12" t="str">
+        <f aca="false">IF(C199="","",N(M199)*پارامترها!$B$6+N(N199)*پارامترها!$B$7+N(O199)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T199" s="12" t="str">
+        <f aca="false">IF(C199="","",N(R199)+N(S199))</f>
+        <v/>
+      </c>
+      <c r="U199" s="10" t="str">
         <f aca="false">IF(C199="","",IF(P199&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L199)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T199" s="11"/>
+      <c r="V199" s="11"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="10" t="str">
@@ -8956,11 +10591,19 @@
         <f aca="false">IF(OR(C200="",N(J200)=0),"",K200*2*(N(H200)*پارامترها!$B$4+N(I200)*پارامترها!$B$5)/J200)</f>
         <v/>
       </c>
-      <c r="S200" s="10" t="str">
+      <c r="S200" s="12" t="str">
+        <f aca="false">IF(C200="","",N(M200)*پارامترها!$B$6+N(N200)*پارامترها!$B$7+N(O200)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T200" s="12" t="str">
+        <f aca="false">IF(C200="","",N(R200)+N(S200))</f>
+        <v/>
+      </c>
+      <c r="U200" s="10" t="str">
         <f aca="false">IF(C200="","",IF(P200&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L200)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T200" s="11"/>
+      <c r="V200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="10" t="str">
@@ -8996,11 +10639,19 @@
         <f aca="false">IF(OR(C201="",N(J201)=0),"",K201*2*(N(H201)*پارامترها!$B$4+N(I201)*پارامترها!$B$5)/J201)</f>
         <v/>
       </c>
-      <c r="S201" s="10" t="str">
+      <c r="S201" s="12" t="str">
+        <f aca="false">IF(C201="","",N(M201)*پارامترها!$B$6+N(N201)*پارامترها!$B$7+N(O201)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T201" s="12" t="str">
+        <f aca="false">IF(C201="","",N(R201)+N(S201))</f>
+        <v/>
+      </c>
+      <c r="U201" s="10" t="str">
         <f aca="false">IF(C201="","",IF(P201&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L201)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T201" s="11"/>
+      <c r="V201" s="11"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="10" t="str">
@@ -9036,11 +10687,19 @@
         <f aca="false">IF(OR(C202="",N(J202)=0),"",K202*2*(N(H202)*پارامترها!$B$4+N(I202)*پارامترها!$B$5)/J202)</f>
         <v/>
       </c>
-      <c r="S202" s="10" t="str">
+      <c r="S202" s="12" t="str">
+        <f aca="false">IF(C202="","",N(M202)*پارامترها!$B$6+N(N202)*پارامترها!$B$7+N(O202)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T202" s="12" t="str">
+        <f aca="false">IF(C202="","",N(R202)+N(S202))</f>
+        <v/>
+      </c>
+      <c r="U202" s="10" t="str">
         <f aca="false">IF(C202="","",IF(P202&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L202)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T202" s="11"/>
+      <c r="V202" s="11"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="10" t="str">
@@ -9076,11 +10735,19 @@
         <f aca="false">IF(OR(C203="",N(J203)=0),"",K203*2*(N(H203)*پارامترها!$B$4+N(I203)*پارامترها!$B$5)/J203)</f>
         <v/>
       </c>
-      <c r="S203" s="10" t="str">
+      <c r="S203" s="12" t="str">
+        <f aca="false">IF(C203="","",N(M203)*پارامترها!$B$6+N(N203)*پارامترها!$B$7+N(O203)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T203" s="12" t="str">
+        <f aca="false">IF(C203="","",N(R203)+N(S203))</f>
+        <v/>
+      </c>
+      <c r="U203" s="10" t="str">
         <f aca="false">IF(C203="","",IF(P203&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L203)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T203" s="11"/>
+      <c r="V203" s="11"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="10" t="str">
@@ -9116,11 +10783,19 @@
         <f aca="false">IF(OR(C204="",N(J204)=0),"",K204*2*(N(H204)*پارامترها!$B$4+N(I204)*پارامترها!$B$5)/J204)</f>
         <v/>
       </c>
-      <c r="S204" s="10" t="str">
+      <c r="S204" s="12" t="str">
+        <f aca="false">IF(C204="","",N(M204)*پارامترها!$B$6+N(N204)*پارامترها!$B$7+N(O204)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T204" s="12" t="str">
+        <f aca="false">IF(C204="","",N(R204)+N(S204))</f>
+        <v/>
+      </c>
+      <c r="U204" s="10" t="str">
         <f aca="false">IF(C204="","",IF(P204&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L204)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T204" s="11"/>
+      <c r="V204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="10" t="str">
@@ -9156,11 +10831,19 @@
         <f aca="false">IF(OR(C205="",N(J205)=0),"",K205*2*(N(H205)*پارامترها!$B$4+N(I205)*پارامترها!$B$5)/J205)</f>
         <v/>
       </c>
-      <c r="S205" s="10" t="str">
+      <c r="S205" s="12" t="str">
+        <f aca="false">IF(C205="","",N(M205)*پارامترها!$B$6+N(N205)*پارامترها!$B$7+N(O205)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T205" s="12" t="str">
+        <f aca="false">IF(C205="","",N(R205)+N(S205))</f>
+        <v/>
+      </c>
+      <c r="U205" s="10" t="str">
         <f aca="false">IF(C205="","",IF(P205&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L205)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T205" s="11"/>
+      <c r="V205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="10" t="str">
@@ -9196,11 +10879,19 @@
         <f aca="false">IF(OR(C206="",N(J206)=0),"",K206*2*(N(H206)*پارامترها!$B$4+N(I206)*پارامترها!$B$5)/J206)</f>
         <v/>
       </c>
-      <c r="S206" s="10" t="str">
+      <c r="S206" s="12" t="str">
+        <f aca="false">IF(C206="","",N(M206)*پارامترها!$B$6+N(N206)*پارامترها!$B$7+N(O206)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T206" s="12" t="str">
+        <f aca="false">IF(C206="","",N(R206)+N(S206))</f>
+        <v/>
+      </c>
+      <c r="U206" s="10" t="str">
         <f aca="false">IF(C206="","",IF(P206&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L206)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T206" s="11"/>
+      <c r="V206" s="11"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="10" t="str">
@@ -9236,11 +10927,19 @@
         <f aca="false">IF(OR(C207="",N(J207)=0),"",K207*2*(N(H207)*پارامترها!$B$4+N(I207)*پارامترها!$B$5)/J207)</f>
         <v/>
       </c>
-      <c r="S207" s="10" t="str">
+      <c r="S207" s="12" t="str">
+        <f aca="false">IF(C207="","",N(M207)*پارامترها!$B$6+N(N207)*پارامترها!$B$7+N(O207)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T207" s="12" t="str">
+        <f aca="false">IF(C207="","",N(R207)+N(S207))</f>
+        <v/>
+      </c>
+      <c r="U207" s="10" t="str">
         <f aca="false">IF(C207="","",IF(P207&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L207)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T207" s="11"/>
+      <c r="V207" s="11"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="10" t="str">
@@ -9276,11 +10975,19 @@
         <f aca="false">IF(OR(C208="",N(J208)=0),"",K208*2*(N(H208)*پارامترها!$B$4+N(I208)*پارامترها!$B$5)/J208)</f>
         <v/>
       </c>
-      <c r="S208" s="10" t="str">
+      <c r="S208" s="12" t="str">
+        <f aca="false">IF(C208="","",N(M208)*پارامترها!$B$6+N(N208)*پارامترها!$B$7+N(O208)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T208" s="12" t="str">
+        <f aca="false">IF(C208="","",N(R208)+N(S208))</f>
+        <v/>
+      </c>
+      <c r="U208" s="10" t="str">
         <f aca="false">IF(C208="","",IF(P208&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L208)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T208" s="11"/>
+      <c r="V208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="10" t="str">
@@ -9316,11 +11023,19 @@
         <f aca="false">IF(OR(C209="",N(J209)=0),"",K209*2*(N(H209)*پارامترها!$B$4+N(I209)*پارامترها!$B$5)/J209)</f>
         <v/>
       </c>
-      <c r="S209" s="10" t="str">
+      <c r="S209" s="12" t="str">
+        <f aca="false">IF(C209="","",N(M209)*پارامترها!$B$6+N(N209)*پارامترها!$B$7+N(O209)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T209" s="12" t="str">
+        <f aca="false">IF(C209="","",N(R209)+N(S209))</f>
+        <v/>
+      </c>
+      <c r="U209" s="10" t="str">
         <f aca="false">IF(C209="","",IF(P209&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L209)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T209" s="11"/>
+      <c r="V209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="10" t="str">
@@ -9356,11 +11071,19 @@
         <f aca="false">IF(OR(C210="",N(J210)=0),"",K210*2*(N(H210)*پارامترها!$B$4+N(I210)*پارامترها!$B$5)/J210)</f>
         <v/>
       </c>
-      <c r="S210" s="10" t="str">
+      <c r="S210" s="12" t="str">
+        <f aca="false">IF(C210="","",N(M210)*پارامترها!$B$6+N(N210)*پارامترها!$B$7+N(O210)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T210" s="12" t="str">
+        <f aca="false">IF(C210="","",N(R210)+N(S210))</f>
+        <v/>
+      </c>
+      <c r="U210" s="10" t="str">
         <f aca="false">IF(C210="","",IF(P210&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L210)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T210" s="11"/>
+      <c r="V210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="10" t="str">
@@ -9396,11 +11119,19 @@
         <f aca="false">IF(OR(C211="",N(J211)=0),"",K211*2*(N(H211)*پارامترها!$B$4+N(I211)*پارامترها!$B$5)/J211)</f>
         <v/>
       </c>
-      <c r="S211" s="10" t="str">
+      <c r="S211" s="12" t="str">
+        <f aca="false">IF(C211="","",N(M211)*پارامترها!$B$6+N(N211)*پارامترها!$B$7+N(O211)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T211" s="12" t="str">
+        <f aca="false">IF(C211="","",N(R211)+N(S211))</f>
+        <v/>
+      </c>
+      <c r="U211" s="10" t="str">
         <f aca="false">IF(C211="","",IF(P211&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L211)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T211" s="11"/>
+      <c r="V211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="10" t="str">
@@ -9436,11 +11167,19 @@
         <f aca="false">IF(OR(C212="",N(J212)=0),"",K212*2*(N(H212)*پارامترها!$B$4+N(I212)*پارامترها!$B$5)/J212)</f>
         <v/>
       </c>
-      <c r="S212" s="10" t="str">
+      <c r="S212" s="12" t="str">
+        <f aca="false">IF(C212="","",N(M212)*پارامترها!$B$6+N(N212)*پارامترها!$B$7+N(O212)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T212" s="12" t="str">
+        <f aca="false">IF(C212="","",N(R212)+N(S212))</f>
+        <v/>
+      </c>
+      <c r="U212" s="10" t="str">
         <f aca="false">IF(C212="","",IF(P212&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L212)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T212" s="11"/>
+      <c r="V212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="10" t="str">
@@ -9476,11 +11215,19 @@
         <f aca="false">IF(OR(C213="",N(J213)=0),"",K213*2*(N(H213)*پارامترها!$B$4+N(I213)*پارامترها!$B$5)/J213)</f>
         <v/>
       </c>
-      <c r="S213" s="10" t="str">
+      <c r="S213" s="12" t="str">
+        <f aca="false">IF(C213="","",N(M213)*پارامترها!$B$6+N(N213)*پارامترها!$B$7+N(O213)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T213" s="12" t="str">
+        <f aca="false">IF(C213="","",N(R213)+N(S213))</f>
+        <v/>
+      </c>
+      <c r="U213" s="10" t="str">
         <f aca="false">IF(C213="","",IF(P213&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L213)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T213" s="11"/>
+      <c r="V213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="10" t="str">
@@ -9516,11 +11263,19 @@
         <f aca="false">IF(OR(C214="",N(J214)=0),"",K214*2*(N(H214)*پارامترها!$B$4+N(I214)*پارامترها!$B$5)/J214)</f>
         <v/>
       </c>
-      <c r="S214" s="10" t="str">
+      <c r="S214" s="12" t="str">
+        <f aca="false">IF(C214="","",N(M214)*پارامترها!$B$6+N(N214)*پارامترها!$B$7+N(O214)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T214" s="12" t="str">
+        <f aca="false">IF(C214="","",N(R214)+N(S214))</f>
+        <v/>
+      </c>
+      <c r="U214" s="10" t="str">
         <f aca="false">IF(C214="","",IF(P214&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L214)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T214" s="11"/>
+      <c r="V214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="10" t="str">
@@ -9556,11 +11311,19 @@
         <f aca="false">IF(OR(C215="",N(J215)=0),"",K215*2*(N(H215)*پارامترها!$B$4+N(I215)*پارامترها!$B$5)/J215)</f>
         <v/>
       </c>
-      <c r="S215" s="10" t="str">
+      <c r="S215" s="12" t="str">
+        <f aca="false">IF(C215="","",N(M215)*پارامترها!$B$6+N(N215)*پارامترها!$B$7+N(O215)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T215" s="12" t="str">
+        <f aca="false">IF(C215="","",N(R215)+N(S215))</f>
+        <v/>
+      </c>
+      <c r="U215" s="10" t="str">
         <f aca="false">IF(C215="","",IF(P215&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L215)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T215" s="11"/>
+      <c r="V215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="10" t="str">
@@ -9596,11 +11359,19 @@
         <f aca="false">IF(OR(C216="",N(J216)=0),"",K216*2*(N(H216)*پارامترها!$B$4+N(I216)*پارامترها!$B$5)/J216)</f>
         <v/>
       </c>
-      <c r="S216" s="10" t="str">
+      <c r="S216" s="12" t="str">
+        <f aca="false">IF(C216="","",N(M216)*پارامترها!$B$6+N(N216)*پارامترها!$B$7+N(O216)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T216" s="12" t="str">
+        <f aca="false">IF(C216="","",N(R216)+N(S216))</f>
+        <v/>
+      </c>
+      <c r="U216" s="10" t="str">
         <f aca="false">IF(C216="","",IF(P216&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L216)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T216" s="11"/>
+      <c r="V216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="10" t="str">
@@ -9636,11 +11407,19 @@
         <f aca="false">IF(OR(C217="",N(J217)=0),"",K217*2*(N(H217)*پارامترها!$B$4+N(I217)*پارامترها!$B$5)/J217)</f>
         <v/>
       </c>
-      <c r="S217" s="10" t="str">
+      <c r="S217" s="12" t="str">
+        <f aca="false">IF(C217="","",N(M217)*پارامترها!$B$6+N(N217)*پارامترها!$B$7+N(O217)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T217" s="12" t="str">
+        <f aca="false">IF(C217="","",N(R217)+N(S217))</f>
+        <v/>
+      </c>
+      <c r="U217" s="10" t="str">
         <f aca="false">IF(C217="","",IF(P217&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L217)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T217" s="11"/>
+      <c r="V217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="10" t="str">
@@ -9676,11 +11455,19 @@
         <f aca="false">IF(OR(C218="",N(J218)=0),"",K218*2*(N(H218)*پارامترها!$B$4+N(I218)*پارامترها!$B$5)/J218)</f>
         <v/>
       </c>
-      <c r="S218" s="10" t="str">
+      <c r="S218" s="12" t="str">
+        <f aca="false">IF(C218="","",N(M218)*پارامترها!$B$6+N(N218)*پارامترها!$B$7+N(O218)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T218" s="12" t="str">
+        <f aca="false">IF(C218="","",N(R218)+N(S218))</f>
+        <v/>
+      </c>
+      <c r="U218" s="10" t="str">
         <f aca="false">IF(C218="","",IF(P218&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L218)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T218" s="11"/>
+      <c r="V218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="10" t="str">
@@ -9716,11 +11503,19 @@
         <f aca="false">IF(OR(C219="",N(J219)=0),"",K219*2*(N(H219)*پارامترها!$B$4+N(I219)*پارامترها!$B$5)/J219)</f>
         <v/>
       </c>
-      <c r="S219" s="10" t="str">
+      <c r="S219" s="12" t="str">
+        <f aca="false">IF(C219="","",N(M219)*پارامترها!$B$6+N(N219)*پارامترها!$B$7+N(O219)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T219" s="12" t="str">
+        <f aca="false">IF(C219="","",N(R219)+N(S219))</f>
+        <v/>
+      </c>
+      <c r="U219" s="10" t="str">
         <f aca="false">IF(C219="","",IF(P219&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L219)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T219" s="11"/>
+      <c r="V219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="10" t="str">
@@ -9756,11 +11551,19 @@
         <f aca="false">IF(OR(C220="",N(J220)=0),"",K220*2*(N(H220)*پارامترها!$B$4+N(I220)*پارامترها!$B$5)/J220)</f>
         <v/>
       </c>
-      <c r="S220" s="10" t="str">
+      <c r="S220" s="12" t="str">
+        <f aca="false">IF(C220="","",N(M220)*پارامترها!$B$6+N(N220)*پارامترها!$B$7+N(O220)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T220" s="12" t="str">
+        <f aca="false">IF(C220="","",N(R220)+N(S220))</f>
+        <v/>
+      </c>
+      <c r="U220" s="10" t="str">
         <f aca="false">IF(C220="","",IF(P220&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L220)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T220" s="11"/>
+      <c r="V220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="10" t="str">
@@ -9796,11 +11599,19 @@
         <f aca="false">IF(OR(C221="",N(J221)=0),"",K221*2*(N(H221)*پارامترها!$B$4+N(I221)*پارامترها!$B$5)/J221)</f>
         <v/>
       </c>
-      <c r="S221" s="10" t="str">
+      <c r="S221" s="12" t="str">
+        <f aca="false">IF(C221="","",N(M221)*پارامترها!$B$6+N(N221)*پارامترها!$B$7+N(O221)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T221" s="12" t="str">
+        <f aca="false">IF(C221="","",N(R221)+N(S221))</f>
+        <v/>
+      </c>
+      <c r="U221" s="10" t="str">
         <f aca="false">IF(C221="","",IF(P221&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L221)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T221" s="11"/>
+      <c r="V221" s="11"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="10" t="str">
@@ -9836,11 +11647,19 @@
         <f aca="false">IF(OR(C222="",N(J222)=0),"",K222*2*(N(H222)*پارامترها!$B$4+N(I222)*پارامترها!$B$5)/J222)</f>
         <v/>
       </c>
-      <c r="S222" s="10" t="str">
+      <c r="S222" s="12" t="str">
+        <f aca="false">IF(C222="","",N(M222)*پارامترها!$B$6+N(N222)*پارامترها!$B$7+N(O222)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T222" s="12" t="str">
+        <f aca="false">IF(C222="","",N(R222)+N(S222))</f>
+        <v/>
+      </c>
+      <c r="U222" s="10" t="str">
         <f aca="false">IF(C222="","",IF(P222&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L222)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T222" s="11"/>
+      <c r="V222" s="11"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="10" t="str">
@@ -9876,11 +11695,19 @@
         <f aca="false">IF(OR(C223="",N(J223)=0),"",K223*2*(N(H223)*پارامترها!$B$4+N(I223)*پارامترها!$B$5)/J223)</f>
         <v/>
       </c>
-      <c r="S223" s="10" t="str">
+      <c r="S223" s="12" t="str">
+        <f aca="false">IF(C223="","",N(M223)*پارامترها!$B$6+N(N223)*پارامترها!$B$7+N(O223)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T223" s="12" t="str">
+        <f aca="false">IF(C223="","",N(R223)+N(S223))</f>
+        <v/>
+      </c>
+      <c r="U223" s="10" t="str">
         <f aca="false">IF(C223="","",IF(P223&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L223)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T223" s="11"/>
+      <c r="V223" s="11"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="10" t="str">
@@ -9916,11 +11743,19 @@
         <f aca="false">IF(OR(C224="",N(J224)=0),"",K224*2*(N(H224)*پارامترها!$B$4+N(I224)*پارامترها!$B$5)/J224)</f>
         <v/>
       </c>
-      <c r="S224" s="10" t="str">
+      <c r="S224" s="12" t="str">
+        <f aca="false">IF(C224="","",N(M224)*پارامترها!$B$6+N(N224)*پارامترها!$B$7+N(O224)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T224" s="12" t="str">
+        <f aca="false">IF(C224="","",N(R224)+N(S224))</f>
+        <v/>
+      </c>
+      <c r="U224" s="10" t="str">
         <f aca="false">IF(C224="","",IF(P224&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L224)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T224" s="11"/>
+      <c r="V224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="10" t="str">
@@ -9956,11 +11791,19 @@
         <f aca="false">IF(OR(C225="",N(J225)=0),"",K225*2*(N(H225)*پارامترها!$B$4+N(I225)*پارامترها!$B$5)/J225)</f>
         <v/>
       </c>
-      <c r="S225" s="10" t="str">
+      <c r="S225" s="12" t="str">
+        <f aca="false">IF(C225="","",N(M225)*پارامترها!$B$6+N(N225)*پارامترها!$B$7+N(O225)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T225" s="12" t="str">
+        <f aca="false">IF(C225="","",N(R225)+N(S225))</f>
+        <v/>
+      </c>
+      <c r="U225" s="10" t="str">
         <f aca="false">IF(C225="","",IF(P225&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L225)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T225" s="11"/>
+      <c r="V225" s="11"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="10" t="str">
@@ -9996,11 +11839,19 @@
         <f aca="false">IF(OR(C226="",N(J226)=0),"",K226*2*(N(H226)*پارامترها!$B$4+N(I226)*پارامترها!$B$5)/J226)</f>
         <v/>
       </c>
-      <c r="S226" s="10" t="str">
+      <c r="S226" s="12" t="str">
+        <f aca="false">IF(C226="","",N(M226)*پارامترها!$B$6+N(N226)*پارامترها!$B$7+N(O226)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T226" s="12" t="str">
+        <f aca="false">IF(C226="","",N(R226)+N(S226))</f>
+        <v/>
+      </c>
+      <c r="U226" s="10" t="str">
         <f aca="false">IF(C226="","",IF(P226&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L226)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T226" s="11"/>
+      <c r="V226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="10" t="str">
@@ -10036,11 +11887,19 @@
         <f aca="false">IF(OR(C227="",N(J227)=0),"",K227*2*(N(H227)*پارامترها!$B$4+N(I227)*پارامترها!$B$5)/J227)</f>
         <v/>
       </c>
-      <c r="S227" s="10" t="str">
+      <c r="S227" s="12" t="str">
+        <f aca="false">IF(C227="","",N(M227)*پارامترها!$B$6+N(N227)*پارامترها!$B$7+N(O227)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T227" s="12" t="str">
+        <f aca="false">IF(C227="","",N(R227)+N(S227))</f>
+        <v/>
+      </c>
+      <c r="U227" s="10" t="str">
         <f aca="false">IF(C227="","",IF(P227&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L227)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T227" s="11"/>
+      <c r="V227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="10" t="str">
@@ -10076,11 +11935,19 @@
         <f aca="false">IF(OR(C228="",N(J228)=0),"",K228*2*(N(H228)*پارامترها!$B$4+N(I228)*پارامترها!$B$5)/J228)</f>
         <v/>
       </c>
-      <c r="S228" s="10" t="str">
+      <c r="S228" s="12" t="str">
+        <f aca="false">IF(C228="","",N(M228)*پارامترها!$B$6+N(N228)*پارامترها!$B$7+N(O228)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T228" s="12" t="str">
+        <f aca="false">IF(C228="","",N(R228)+N(S228))</f>
+        <v/>
+      </c>
+      <c r="U228" s="10" t="str">
         <f aca="false">IF(C228="","",IF(P228&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L228)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T228" s="11"/>
+      <c r="V228" s="11"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="10" t="str">
@@ -10116,11 +11983,19 @@
         <f aca="false">IF(OR(C229="",N(J229)=0),"",K229*2*(N(H229)*پارامترها!$B$4+N(I229)*پارامترها!$B$5)/J229)</f>
         <v/>
       </c>
-      <c r="S229" s="10" t="str">
+      <c r="S229" s="12" t="str">
+        <f aca="false">IF(C229="","",N(M229)*پارامترها!$B$6+N(N229)*پارامترها!$B$7+N(O229)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T229" s="12" t="str">
+        <f aca="false">IF(C229="","",N(R229)+N(S229))</f>
+        <v/>
+      </c>
+      <c r="U229" s="10" t="str">
         <f aca="false">IF(C229="","",IF(P229&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L229)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T229" s="11"/>
+      <c r="V229" s="11"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="10" t="str">
@@ -10156,11 +12031,19 @@
         <f aca="false">IF(OR(C230="",N(J230)=0),"",K230*2*(N(H230)*پارامترها!$B$4+N(I230)*پارامترها!$B$5)/J230)</f>
         <v/>
       </c>
-      <c r="S230" s="10" t="str">
+      <c r="S230" s="12" t="str">
+        <f aca="false">IF(C230="","",N(M230)*پارامترها!$B$6+N(N230)*پارامترها!$B$7+N(O230)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T230" s="12" t="str">
+        <f aca="false">IF(C230="","",N(R230)+N(S230))</f>
+        <v/>
+      </c>
+      <c r="U230" s="10" t="str">
         <f aca="false">IF(C230="","",IF(P230&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L230)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T230" s="11"/>
+      <c r="V230" s="11"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="10" t="str">
@@ -10196,11 +12079,19 @@
         <f aca="false">IF(OR(C231="",N(J231)=0),"",K231*2*(N(H231)*پارامترها!$B$4+N(I231)*پارامترها!$B$5)/J231)</f>
         <v/>
       </c>
-      <c r="S231" s="10" t="str">
+      <c r="S231" s="12" t="str">
+        <f aca="false">IF(C231="","",N(M231)*پارامترها!$B$6+N(N231)*پارامترها!$B$7+N(O231)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T231" s="12" t="str">
+        <f aca="false">IF(C231="","",N(R231)+N(S231))</f>
+        <v/>
+      </c>
+      <c r="U231" s="10" t="str">
         <f aca="false">IF(C231="","",IF(P231&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L231)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T231" s="11"/>
+      <c r="V231" s="11"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="10" t="str">
@@ -10236,11 +12127,19 @@
         <f aca="false">IF(OR(C232="",N(J232)=0),"",K232*2*(N(H232)*پارامترها!$B$4+N(I232)*پارامترها!$B$5)/J232)</f>
         <v/>
       </c>
-      <c r="S232" s="10" t="str">
+      <c r="S232" s="12" t="str">
+        <f aca="false">IF(C232="","",N(M232)*پارامترها!$B$6+N(N232)*پارامترها!$B$7+N(O232)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T232" s="12" t="str">
+        <f aca="false">IF(C232="","",N(R232)+N(S232))</f>
+        <v/>
+      </c>
+      <c r="U232" s="10" t="str">
         <f aca="false">IF(C232="","",IF(P232&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L232)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T232" s="11"/>
+      <c r="V232" s="11"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="10" t="str">
@@ -10276,11 +12175,19 @@
         <f aca="false">IF(OR(C233="",N(J233)=0),"",K233*2*(N(H233)*پارامترها!$B$4+N(I233)*پارامترها!$B$5)/J233)</f>
         <v/>
       </c>
-      <c r="S233" s="10" t="str">
+      <c r="S233" s="12" t="str">
+        <f aca="false">IF(C233="","",N(M233)*پارامترها!$B$6+N(N233)*پارامترها!$B$7+N(O233)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T233" s="12" t="str">
+        <f aca="false">IF(C233="","",N(R233)+N(S233))</f>
+        <v/>
+      </c>
+      <c r="U233" s="10" t="str">
         <f aca="false">IF(C233="","",IF(P233&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L233)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T233" s="11"/>
+      <c r="V233" s="11"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="10" t="str">
@@ -10316,11 +12223,19 @@
         <f aca="false">IF(OR(C234="",N(J234)=0),"",K234*2*(N(H234)*پارامترها!$B$4+N(I234)*پارامترها!$B$5)/J234)</f>
         <v/>
       </c>
-      <c r="S234" s="10" t="str">
+      <c r="S234" s="12" t="str">
+        <f aca="false">IF(C234="","",N(M234)*پارامترها!$B$6+N(N234)*پارامترها!$B$7+N(O234)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T234" s="12" t="str">
+        <f aca="false">IF(C234="","",N(R234)+N(S234))</f>
+        <v/>
+      </c>
+      <c r="U234" s="10" t="str">
         <f aca="false">IF(C234="","",IF(P234&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L234)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T234" s="11"/>
+      <c r="V234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="10" t="str">
@@ -10356,11 +12271,19 @@
         <f aca="false">IF(OR(C235="",N(J235)=0),"",K235*2*(N(H235)*پارامترها!$B$4+N(I235)*پارامترها!$B$5)/J235)</f>
         <v/>
       </c>
-      <c r="S235" s="10" t="str">
+      <c r="S235" s="12" t="str">
+        <f aca="false">IF(C235="","",N(M235)*پارامترها!$B$6+N(N235)*پارامترها!$B$7+N(O235)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T235" s="12" t="str">
+        <f aca="false">IF(C235="","",N(R235)+N(S235))</f>
+        <v/>
+      </c>
+      <c r="U235" s="10" t="str">
         <f aca="false">IF(C235="","",IF(P235&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L235)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T235" s="11"/>
+      <c r="V235" s="11"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="10" t="str">
@@ -10396,11 +12319,19 @@
         <f aca="false">IF(OR(C236="",N(J236)=0),"",K236*2*(N(H236)*پارامترها!$B$4+N(I236)*پارامترها!$B$5)/J236)</f>
         <v/>
       </c>
-      <c r="S236" s="10" t="str">
+      <c r="S236" s="12" t="str">
+        <f aca="false">IF(C236="","",N(M236)*پارامترها!$B$6+N(N236)*پارامترها!$B$7+N(O236)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T236" s="12" t="str">
+        <f aca="false">IF(C236="","",N(R236)+N(S236))</f>
+        <v/>
+      </c>
+      <c r="U236" s="10" t="str">
         <f aca="false">IF(C236="","",IF(P236&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L236)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T236" s="11"/>
+      <c r="V236" s="11"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="10" t="str">
@@ -10436,11 +12367,19 @@
         <f aca="false">IF(OR(C237="",N(J237)=0),"",K237*2*(N(H237)*پارامترها!$B$4+N(I237)*پارامترها!$B$5)/J237)</f>
         <v/>
       </c>
-      <c r="S237" s="10" t="str">
+      <c r="S237" s="12" t="str">
+        <f aca="false">IF(C237="","",N(M237)*پارامترها!$B$6+N(N237)*پارامترها!$B$7+N(O237)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T237" s="12" t="str">
+        <f aca="false">IF(C237="","",N(R237)+N(S237))</f>
+        <v/>
+      </c>
+      <c r="U237" s="10" t="str">
         <f aca="false">IF(C237="","",IF(P237&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L237)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T237" s="11"/>
+      <c r="V237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="10" t="str">
@@ -10476,11 +12415,19 @@
         <f aca="false">IF(OR(C238="",N(J238)=0),"",K238*2*(N(H238)*پارامترها!$B$4+N(I238)*پارامترها!$B$5)/J238)</f>
         <v/>
       </c>
-      <c r="S238" s="10" t="str">
+      <c r="S238" s="12" t="str">
+        <f aca="false">IF(C238="","",N(M238)*پارامترها!$B$6+N(N238)*پارامترها!$B$7+N(O238)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T238" s="12" t="str">
+        <f aca="false">IF(C238="","",N(R238)+N(S238))</f>
+        <v/>
+      </c>
+      <c r="U238" s="10" t="str">
         <f aca="false">IF(C238="","",IF(P238&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L238)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T238" s="11"/>
+      <c r="V238" s="11"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="10" t="str">
@@ -10516,11 +12463,19 @@
         <f aca="false">IF(OR(C239="",N(J239)=0),"",K239*2*(N(H239)*پارامترها!$B$4+N(I239)*پارامترها!$B$5)/J239)</f>
         <v/>
       </c>
-      <c r="S239" s="10" t="str">
+      <c r="S239" s="12" t="str">
+        <f aca="false">IF(C239="","",N(M239)*پارامترها!$B$6+N(N239)*پارامترها!$B$7+N(O239)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T239" s="12" t="str">
+        <f aca="false">IF(C239="","",N(R239)+N(S239))</f>
+        <v/>
+      </c>
+      <c r="U239" s="10" t="str">
         <f aca="false">IF(C239="","",IF(P239&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L239)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T239" s="11"/>
+      <c r="V239" s="11"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="10" t="str">
@@ -10556,11 +12511,19 @@
         <f aca="false">IF(OR(C240="",N(J240)=0),"",K240*2*(N(H240)*پارامترها!$B$4+N(I240)*پارامترها!$B$5)/J240)</f>
         <v/>
       </c>
-      <c r="S240" s="10" t="str">
+      <c r="S240" s="12" t="str">
+        <f aca="false">IF(C240="","",N(M240)*پارامترها!$B$6+N(N240)*پارامترها!$B$7+N(O240)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T240" s="12" t="str">
+        <f aca="false">IF(C240="","",N(R240)+N(S240))</f>
+        <v/>
+      </c>
+      <c r="U240" s="10" t="str">
         <f aca="false">IF(C240="","",IF(P240&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L240)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T240" s="11"/>
+      <c r="V240" s="11"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="10" t="str">
@@ -10596,11 +12559,19 @@
         <f aca="false">IF(OR(C241="",N(J241)=0),"",K241*2*(N(H241)*پارامترها!$B$4+N(I241)*پارامترها!$B$5)/J241)</f>
         <v/>
       </c>
-      <c r="S241" s="10" t="str">
+      <c r="S241" s="12" t="str">
+        <f aca="false">IF(C241="","",N(M241)*پارامترها!$B$6+N(N241)*پارامترها!$B$7+N(O241)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T241" s="12" t="str">
+        <f aca="false">IF(C241="","",N(R241)+N(S241))</f>
+        <v/>
+      </c>
+      <c r="U241" s="10" t="str">
         <f aca="false">IF(C241="","",IF(P241&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L241)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T241" s="11"/>
+      <c r="V241" s="11"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="10" t="str">
@@ -10636,11 +12607,19 @@
         <f aca="false">IF(OR(C242="",N(J242)=0),"",K242*2*(N(H242)*پارامترها!$B$4+N(I242)*پارامترها!$B$5)/J242)</f>
         <v/>
       </c>
-      <c r="S242" s="10" t="str">
+      <c r="S242" s="12" t="str">
+        <f aca="false">IF(C242="","",N(M242)*پارامترها!$B$6+N(N242)*پارامترها!$B$7+N(O242)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T242" s="12" t="str">
+        <f aca="false">IF(C242="","",N(R242)+N(S242))</f>
+        <v/>
+      </c>
+      <c r="U242" s="10" t="str">
         <f aca="false">IF(C242="","",IF(P242&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L242)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T242" s="11"/>
+      <c r="V242" s="11"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="10" t="str">
@@ -10676,11 +12655,19 @@
         <f aca="false">IF(OR(C243="",N(J243)=0),"",K243*2*(N(H243)*پارامترها!$B$4+N(I243)*پارامترها!$B$5)/J243)</f>
         <v/>
       </c>
-      <c r="S243" s="10" t="str">
+      <c r="S243" s="12" t="str">
+        <f aca="false">IF(C243="","",N(M243)*پارامترها!$B$6+N(N243)*پارامترها!$B$7+N(O243)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T243" s="12" t="str">
+        <f aca="false">IF(C243="","",N(R243)+N(S243))</f>
+        <v/>
+      </c>
+      <c r="U243" s="10" t="str">
         <f aca="false">IF(C243="","",IF(P243&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L243)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T243" s="11"/>
+      <c r="V243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="10" t="str">
@@ -10716,11 +12703,19 @@
         <f aca="false">IF(OR(C244="",N(J244)=0),"",K244*2*(N(H244)*پارامترها!$B$4+N(I244)*پارامترها!$B$5)/J244)</f>
         <v/>
       </c>
-      <c r="S244" s="10" t="str">
+      <c r="S244" s="12" t="str">
+        <f aca="false">IF(C244="","",N(M244)*پارامترها!$B$6+N(N244)*پارامترها!$B$7+N(O244)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T244" s="12" t="str">
+        <f aca="false">IF(C244="","",N(R244)+N(S244))</f>
+        <v/>
+      </c>
+      <c r="U244" s="10" t="str">
         <f aca="false">IF(C244="","",IF(P244&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L244)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T244" s="11"/>
+      <c r="V244" s="11"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="10" t="str">
@@ -10756,11 +12751,19 @@
         <f aca="false">IF(OR(C245="",N(J245)=0),"",K245*2*(N(H245)*پارامترها!$B$4+N(I245)*پارامترها!$B$5)/J245)</f>
         <v/>
       </c>
-      <c r="S245" s="10" t="str">
+      <c r="S245" s="12" t="str">
+        <f aca="false">IF(C245="","",N(M245)*پارامترها!$B$6+N(N245)*پارامترها!$B$7+N(O245)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T245" s="12" t="str">
+        <f aca="false">IF(C245="","",N(R245)+N(S245))</f>
+        <v/>
+      </c>
+      <c r="U245" s="10" t="str">
         <f aca="false">IF(C245="","",IF(P245&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L245)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T245" s="11"/>
+      <c r="V245" s="11"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="10" t="str">
@@ -10796,11 +12799,19 @@
         <f aca="false">IF(OR(C246="",N(J246)=0),"",K246*2*(N(H246)*پارامترها!$B$4+N(I246)*پارامترها!$B$5)/J246)</f>
         <v/>
       </c>
-      <c r="S246" s="10" t="str">
+      <c r="S246" s="12" t="str">
+        <f aca="false">IF(C246="","",N(M246)*پارامترها!$B$6+N(N246)*پارامترها!$B$7+N(O246)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T246" s="12" t="str">
+        <f aca="false">IF(C246="","",N(R246)+N(S246))</f>
+        <v/>
+      </c>
+      <c r="U246" s="10" t="str">
         <f aca="false">IF(C246="","",IF(P246&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L246)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T246" s="11"/>
+      <c r="V246" s="11"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="10" t="str">
@@ -10836,11 +12847,19 @@
         <f aca="false">IF(OR(C247="",N(J247)=0),"",K247*2*(N(H247)*پارامترها!$B$4+N(I247)*پارامترها!$B$5)/J247)</f>
         <v/>
       </c>
-      <c r="S247" s="10" t="str">
+      <c r="S247" s="12" t="str">
+        <f aca="false">IF(C247="","",N(M247)*پارامترها!$B$6+N(N247)*پارامترها!$B$7+N(O247)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T247" s="12" t="str">
+        <f aca="false">IF(C247="","",N(R247)+N(S247))</f>
+        <v/>
+      </c>
+      <c r="U247" s="10" t="str">
         <f aca="false">IF(C247="","",IF(P247&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L247)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T247" s="11"/>
+      <c r="V247" s="11"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="10" t="str">
@@ -10876,11 +12895,19 @@
         <f aca="false">IF(OR(C248="",N(J248)=0),"",K248*2*(N(H248)*پارامترها!$B$4+N(I248)*پارامترها!$B$5)/J248)</f>
         <v/>
       </c>
-      <c r="S248" s="10" t="str">
+      <c r="S248" s="12" t="str">
+        <f aca="false">IF(C248="","",N(M248)*پارامترها!$B$6+N(N248)*پارامترها!$B$7+N(O248)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T248" s="12" t="str">
+        <f aca="false">IF(C248="","",N(R248)+N(S248))</f>
+        <v/>
+      </c>
+      <c r="U248" s="10" t="str">
         <f aca="false">IF(C248="","",IF(P248&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L248)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T248" s="11"/>
+      <c r="V248" s="11"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="10" t="str">
@@ -10916,11 +12943,19 @@
         <f aca="false">IF(OR(C249="",N(J249)=0),"",K249*2*(N(H249)*پارامترها!$B$4+N(I249)*پارامترها!$B$5)/J249)</f>
         <v/>
       </c>
-      <c r="S249" s="10" t="str">
+      <c r="S249" s="12" t="str">
+        <f aca="false">IF(C249="","",N(M249)*پارامترها!$B$6+N(N249)*پارامترها!$B$7+N(O249)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T249" s="12" t="str">
+        <f aca="false">IF(C249="","",N(R249)+N(S249))</f>
+        <v/>
+      </c>
+      <c r="U249" s="10" t="str">
         <f aca="false">IF(C249="","",IF(P249&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L249)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T249" s="11"/>
+      <c r="V249" s="11"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="10" t="str">
@@ -10956,11 +12991,19 @@
         <f aca="false">IF(OR(C250="",N(J250)=0),"",K250*2*(N(H250)*پارامترها!$B$4+N(I250)*پارامترها!$B$5)/J250)</f>
         <v/>
       </c>
-      <c r="S250" s="10" t="str">
+      <c r="S250" s="12" t="str">
+        <f aca="false">IF(C250="","",N(M250)*پارامترها!$B$6+N(N250)*پارامترها!$B$7+N(O250)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T250" s="12" t="str">
+        <f aca="false">IF(C250="","",N(R250)+N(S250))</f>
+        <v/>
+      </c>
+      <c r="U250" s="10" t="str">
         <f aca="false">IF(C250="","",IF(P250&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L250)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T250" s="11"/>
+      <c r="V250" s="11"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="10" t="str">
@@ -10996,11 +13039,19 @@
         <f aca="false">IF(OR(C251="",N(J251)=0),"",K251*2*(N(H251)*پارامترها!$B$4+N(I251)*پارامترها!$B$5)/J251)</f>
         <v/>
       </c>
-      <c r="S251" s="10" t="str">
+      <c r="S251" s="12" t="str">
+        <f aca="false">IF(C251="","",N(M251)*پارامترها!$B$6+N(N251)*پارامترها!$B$7+N(O251)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T251" s="12" t="str">
+        <f aca="false">IF(C251="","",N(R251)+N(S251))</f>
+        <v/>
+      </c>
+      <c r="U251" s="10" t="str">
         <f aca="false">IF(C251="","",IF(P251&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L251)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T251" s="11"/>
+      <c r="V251" s="11"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="10" t="str">
@@ -11036,11 +13087,19 @@
         <f aca="false">IF(OR(C252="",N(J252)=0),"",K252*2*(N(H252)*پارامترها!$B$4+N(I252)*پارامترها!$B$5)/J252)</f>
         <v/>
       </c>
-      <c r="S252" s="10" t="str">
+      <c r="S252" s="12" t="str">
+        <f aca="false">IF(C252="","",N(M252)*پارامترها!$B$6+N(N252)*پارامترها!$B$7+N(O252)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T252" s="12" t="str">
+        <f aca="false">IF(C252="","",N(R252)+N(S252))</f>
+        <v/>
+      </c>
+      <c r="U252" s="10" t="str">
         <f aca="false">IF(C252="","",IF(P252&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L252)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T252" s="11"/>
+      <c r="V252" s="11"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="10" t="str">
@@ -11076,11 +13135,19 @@
         <f aca="false">IF(OR(C253="",N(J253)=0),"",K253*2*(N(H253)*پارامترها!$B$4+N(I253)*پارامترها!$B$5)/J253)</f>
         <v/>
       </c>
-      <c r="S253" s="10" t="str">
+      <c r="S253" s="12" t="str">
+        <f aca="false">IF(C253="","",N(M253)*پارامترها!$B$6+N(N253)*پارامترها!$B$7+N(O253)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T253" s="12" t="str">
+        <f aca="false">IF(C253="","",N(R253)+N(S253))</f>
+        <v/>
+      </c>
+      <c r="U253" s="10" t="str">
         <f aca="false">IF(C253="","",IF(P253&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L253)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T253" s="11"/>
+      <c r="V253" s="11"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="10" t="str">
@@ -11116,11 +13183,19 @@
         <f aca="false">IF(OR(C254="",N(J254)=0),"",K254*2*(N(H254)*پارامترها!$B$4+N(I254)*پارامترها!$B$5)/J254)</f>
         <v/>
       </c>
-      <c r="S254" s="10" t="str">
+      <c r="S254" s="12" t="str">
+        <f aca="false">IF(C254="","",N(M254)*پارامترها!$B$6+N(N254)*پارامترها!$B$7+N(O254)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T254" s="12" t="str">
+        <f aca="false">IF(C254="","",N(R254)+N(S254))</f>
+        <v/>
+      </c>
+      <c r="U254" s="10" t="str">
         <f aca="false">IF(C254="","",IF(P254&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L254)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T254" s="11"/>
+      <c r="V254" s="11"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="10" t="str">
@@ -11156,11 +13231,19 @@
         <f aca="false">IF(OR(C255="",N(J255)=0),"",K255*2*(N(H255)*پارامترها!$B$4+N(I255)*پارامترها!$B$5)/J255)</f>
         <v/>
       </c>
-      <c r="S255" s="10" t="str">
+      <c r="S255" s="12" t="str">
+        <f aca="false">IF(C255="","",N(M255)*پارامترها!$B$6+N(N255)*پارامترها!$B$7+N(O255)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T255" s="12" t="str">
+        <f aca="false">IF(C255="","",N(R255)+N(S255))</f>
+        <v/>
+      </c>
+      <c r="U255" s="10" t="str">
         <f aca="false">IF(C255="","",IF(P255&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L255)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T255" s="11"/>
+      <c r="V255" s="11"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="10" t="str">
@@ -11196,11 +13279,19 @@
         <f aca="false">IF(OR(C256="",N(J256)=0),"",K256*2*(N(H256)*پارامترها!$B$4+N(I256)*پارامترها!$B$5)/J256)</f>
         <v/>
       </c>
-      <c r="S256" s="10" t="str">
+      <c r="S256" s="12" t="str">
+        <f aca="false">IF(C256="","",N(M256)*پارامترها!$B$6+N(N256)*پارامترها!$B$7+N(O256)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T256" s="12" t="str">
+        <f aca="false">IF(C256="","",N(R256)+N(S256))</f>
+        <v/>
+      </c>
+      <c r="U256" s="10" t="str">
         <f aca="false">IF(C256="","",IF(P256&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L256)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T256" s="11"/>
+      <c r="V256" s="11"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="10" t="str">
@@ -11236,11 +13327,19 @@
         <f aca="false">IF(OR(C257="",N(J257)=0),"",K257*2*(N(H257)*پارامترها!$B$4+N(I257)*پارامترها!$B$5)/J257)</f>
         <v/>
       </c>
-      <c r="S257" s="10" t="str">
+      <c r="S257" s="12" t="str">
+        <f aca="false">IF(C257="","",N(M257)*پارامترها!$B$6+N(N257)*پارامترها!$B$7+N(O257)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T257" s="12" t="str">
+        <f aca="false">IF(C257="","",N(R257)+N(S257))</f>
+        <v/>
+      </c>
+      <c r="U257" s="10" t="str">
         <f aca="false">IF(C257="","",IF(P257&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L257)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T257" s="11"/>
+      <c r="V257" s="11"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="10" t="str">
@@ -11276,11 +13375,19 @@
         <f aca="false">IF(OR(C258="",N(J258)=0),"",K258*2*(N(H258)*پارامترها!$B$4+N(I258)*پارامترها!$B$5)/J258)</f>
         <v/>
       </c>
-      <c r="S258" s="10" t="str">
+      <c r="S258" s="12" t="str">
+        <f aca="false">IF(C258="","",N(M258)*پارامترها!$B$6+N(N258)*پارامترها!$B$7+N(O258)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T258" s="12" t="str">
+        <f aca="false">IF(C258="","",N(R258)+N(S258))</f>
+        <v/>
+      </c>
+      <c r="U258" s="10" t="str">
         <f aca="false">IF(C258="","",IF(P258&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L258)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T258" s="11"/>
+      <c r="V258" s="11"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="10" t="str">
@@ -11316,11 +13423,19 @@
         <f aca="false">IF(OR(C259="",N(J259)=0),"",K259*2*(N(H259)*پارامترها!$B$4+N(I259)*پارامترها!$B$5)/J259)</f>
         <v/>
       </c>
-      <c r="S259" s="10" t="str">
+      <c r="S259" s="12" t="str">
+        <f aca="false">IF(C259="","",N(M259)*پارامترها!$B$6+N(N259)*پارامترها!$B$7+N(O259)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T259" s="12" t="str">
+        <f aca="false">IF(C259="","",N(R259)+N(S259))</f>
+        <v/>
+      </c>
+      <c r="U259" s="10" t="str">
         <f aca="false">IF(C259="","",IF(P259&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L259)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T259" s="11"/>
+      <c r="V259" s="11"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="10" t="str">
@@ -11356,11 +13471,19 @@
         <f aca="false">IF(OR(C260="",N(J260)=0),"",K260*2*(N(H260)*پارامترها!$B$4+N(I260)*پارامترها!$B$5)/J260)</f>
         <v/>
       </c>
-      <c r="S260" s="10" t="str">
+      <c r="S260" s="12" t="str">
+        <f aca="false">IF(C260="","",N(M260)*پارامترها!$B$6+N(N260)*پارامترها!$B$7+N(O260)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T260" s="12" t="str">
+        <f aca="false">IF(C260="","",N(R260)+N(S260))</f>
+        <v/>
+      </c>
+      <c r="U260" s="10" t="str">
         <f aca="false">IF(C260="","",IF(P260&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L260)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T260" s="11"/>
+      <c r="V260" s="11"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="10" t="str">
@@ -11396,11 +13519,19 @@
         <f aca="false">IF(OR(C261="",N(J261)=0),"",K261*2*(N(H261)*پارامترها!$B$4+N(I261)*پارامترها!$B$5)/J261)</f>
         <v/>
       </c>
-      <c r="S261" s="10" t="str">
+      <c r="S261" s="12" t="str">
+        <f aca="false">IF(C261="","",N(M261)*پارامترها!$B$6+N(N261)*پارامترها!$B$7+N(O261)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T261" s="12" t="str">
+        <f aca="false">IF(C261="","",N(R261)+N(S261))</f>
+        <v/>
+      </c>
+      <c r="U261" s="10" t="str">
         <f aca="false">IF(C261="","",IF(P261&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L261)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T261" s="11"/>
+      <c r="V261" s="11"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="10" t="str">
@@ -11436,11 +13567,19 @@
         <f aca="false">IF(OR(C262="",N(J262)=0),"",K262*2*(N(H262)*پارامترها!$B$4+N(I262)*پارامترها!$B$5)/J262)</f>
         <v/>
       </c>
-      <c r="S262" s="10" t="str">
+      <c r="S262" s="12" t="str">
+        <f aca="false">IF(C262="","",N(M262)*پارامترها!$B$6+N(N262)*پارامترها!$B$7+N(O262)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T262" s="12" t="str">
+        <f aca="false">IF(C262="","",N(R262)+N(S262))</f>
+        <v/>
+      </c>
+      <c r="U262" s="10" t="str">
         <f aca="false">IF(C262="","",IF(P262&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L262)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T262" s="11"/>
+      <c r="V262" s="11"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="10" t="str">
@@ -11476,11 +13615,19 @@
         <f aca="false">IF(OR(C263="",N(J263)=0),"",K263*2*(N(H263)*پارامترها!$B$4+N(I263)*پارامترها!$B$5)/J263)</f>
         <v/>
       </c>
-      <c r="S263" s="10" t="str">
+      <c r="S263" s="12" t="str">
+        <f aca="false">IF(C263="","",N(M263)*پارامترها!$B$6+N(N263)*پارامترها!$B$7+N(O263)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T263" s="12" t="str">
+        <f aca="false">IF(C263="","",N(R263)+N(S263))</f>
+        <v/>
+      </c>
+      <c r="U263" s="10" t="str">
         <f aca="false">IF(C263="","",IF(P263&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L263)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T263" s="11"/>
+      <c r="V263" s="11"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="10" t="str">
@@ -11516,11 +13663,19 @@
         <f aca="false">IF(OR(C264="",N(J264)=0),"",K264*2*(N(H264)*پارامترها!$B$4+N(I264)*پارامترها!$B$5)/J264)</f>
         <v/>
       </c>
-      <c r="S264" s="10" t="str">
+      <c r="S264" s="12" t="str">
+        <f aca="false">IF(C264="","",N(M264)*پارامترها!$B$6+N(N264)*پارامترها!$B$7+N(O264)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T264" s="12" t="str">
+        <f aca="false">IF(C264="","",N(R264)+N(S264))</f>
+        <v/>
+      </c>
+      <c r="U264" s="10" t="str">
         <f aca="false">IF(C264="","",IF(P264&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L264)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T264" s="11"/>
+      <c r="V264" s="11"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="10" t="str">
@@ -11556,11 +13711,19 @@
         <f aca="false">IF(OR(C265="",N(J265)=0),"",K265*2*(N(H265)*پارامترها!$B$4+N(I265)*پارامترها!$B$5)/J265)</f>
         <v/>
       </c>
-      <c r="S265" s="10" t="str">
+      <c r="S265" s="12" t="str">
+        <f aca="false">IF(C265="","",N(M265)*پارامترها!$B$6+N(N265)*پارامترها!$B$7+N(O265)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T265" s="12" t="str">
+        <f aca="false">IF(C265="","",N(R265)+N(S265))</f>
+        <v/>
+      </c>
+      <c r="U265" s="10" t="str">
         <f aca="false">IF(C265="","",IF(P265&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L265)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T265" s="11"/>
+      <c r="V265" s="11"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="10" t="str">
@@ -11596,11 +13759,19 @@
         <f aca="false">IF(OR(C266="",N(J266)=0),"",K266*2*(N(H266)*پارامترها!$B$4+N(I266)*پارامترها!$B$5)/J266)</f>
         <v/>
       </c>
-      <c r="S266" s="10" t="str">
+      <c r="S266" s="12" t="str">
+        <f aca="false">IF(C266="","",N(M266)*پارامترها!$B$6+N(N266)*پارامترها!$B$7+N(O266)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T266" s="12" t="str">
+        <f aca="false">IF(C266="","",N(R266)+N(S266))</f>
+        <v/>
+      </c>
+      <c r="U266" s="10" t="str">
         <f aca="false">IF(C266="","",IF(P266&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L266)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T266" s="11"/>
+      <c r="V266" s="11"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="10" t="str">
@@ -11636,11 +13807,19 @@
         <f aca="false">IF(OR(C267="",N(J267)=0),"",K267*2*(N(H267)*پارامترها!$B$4+N(I267)*پارامترها!$B$5)/J267)</f>
         <v/>
       </c>
-      <c r="S267" s="10" t="str">
+      <c r="S267" s="12" t="str">
+        <f aca="false">IF(C267="","",N(M267)*پارامترها!$B$6+N(N267)*پارامترها!$B$7+N(O267)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T267" s="12" t="str">
+        <f aca="false">IF(C267="","",N(R267)+N(S267))</f>
+        <v/>
+      </c>
+      <c r="U267" s="10" t="str">
         <f aca="false">IF(C267="","",IF(P267&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L267)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T267" s="11"/>
+      <c r="V267" s="11"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="10" t="str">
@@ -11676,11 +13855,19 @@
         <f aca="false">IF(OR(C268="",N(J268)=0),"",K268*2*(N(H268)*پارامترها!$B$4+N(I268)*پارامترها!$B$5)/J268)</f>
         <v/>
       </c>
-      <c r="S268" s="10" t="str">
+      <c r="S268" s="12" t="str">
+        <f aca="false">IF(C268="","",N(M268)*پارامترها!$B$6+N(N268)*پارامترها!$B$7+N(O268)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T268" s="12" t="str">
+        <f aca="false">IF(C268="","",N(R268)+N(S268))</f>
+        <v/>
+      </c>
+      <c r="U268" s="10" t="str">
         <f aca="false">IF(C268="","",IF(P268&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L268)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T268" s="11"/>
+      <c r="V268" s="11"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="10" t="str">
@@ -11716,11 +13903,19 @@
         <f aca="false">IF(OR(C269="",N(J269)=0),"",K269*2*(N(H269)*پارامترها!$B$4+N(I269)*پارامترها!$B$5)/J269)</f>
         <v/>
       </c>
-      <c r="S269" s="10" t="str">
+      <c r="S269" s="12" t="str">
+        <f aca="false">IF(C269="","",N(M269)*پارامترها!$B$6+N(N269)*پارامترها!$B$7+N(O269)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T269" s="12" t="str">
+        <f aca="false">IF(C269="","",N(R269)+N(S269))</f>
+        <v/>
+      </c>
+      <c r="U269" s="10" t="str">
         <f aca="false">IF(C269="","",IF(P269&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L269)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T269" s="11"/>
+      <c r="V269" s="11"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="10" t="str">
@@ -11756,11 +13951,19 @@
         <f aca="false">IF(OR(C270="",N(J270)=0),"",K270*2*(N(H270)*پارامترها!$B$4+N(I270)*پارامترها!$B$5)/J270)</f>
         <v/>
       </c>
-      <c r="S270" s="10" t="str">
+      <c r="S270" s="12" t="str">
+        <f aca="false">IF(C270="","",N(M270)*پارامترها!$B$6+N(N270)*پارامترها!$B$7+N(O270)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T270" s="12" t="str">
+        <f aca="false">IF(C270="","",N(R270)+N(S270))</f>
+        <v/>
+      </c>
+      <c r="U270" s="10" t="str">
         <f aca="false">IF(C270="","",IF(P270&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L270)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T270" s="11"/>
+      <c r="V270" s="11"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="10" t="str">
@@ -11796,11 +13999,19 @@
         <f aca="false">IF(OR(C271="",N(J271)=0),"",K271*2*(N(H271)*پارامترها!$B$4+N(I271)*پارامترها!$B$5)/J271)</f>
         <v/>
       </c>
-      <c r="S271" s="10" t="str">
+      <c r="S271" s="12" t="str">
+        <f aca="false">IF(C271="","",N(M271)*پارامترها!$B$6+N(N271)*پارامترها!$B$7+N(O271)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T271" s="12" t="str">
+        <f aca="false">IF(C271="","",N(R271)+N(S271))</f>
+        <v/>
+      </c>
+      <c r="U271" s="10" t="str">
         <f aca="false">IF(C271="","",IF(P271&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L271)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T271" s="11"/>
+      <c r="V271" s="11"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="10" t="str">
@@ -11836,11 +14047,19 @@
         <f aca="false">IF(OR(C272="",N(J272)=0),"",K272*2*(N(H272)*پارامترها!$B$4+N(I272)*پارامترها!$B$5)/J272)</f>
         <v/>
       </c>
-      <c r="S272" s="10" t="str">
+      <c r="S272" s="12" t="str">
+        <f aca="false">IF(C272="","",N(M272)*پارامترها!$B$6+N(N272)*پارامترها!$B$7+N(O272)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T272" s="12" t="str">
+        <f aca="false">IF(C272="","",N(R272)+N(S272))</f>
+        <v/>
+      </c>
+      <c r="U272" s="10" t="str">
         <f aca="false">IF(C272="","",IF(P272&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L272)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T272" s="11"/>
+      <c r="V272" s="11"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="10" t="str">
@@ -11876,11 +14095,19 @@
         <f aca="false">IF(OR(C273="",N(J273)=0),"",K273*2*(N(H273)*پارامترها!$B$4+N(I273)*پارامترها!$B$5)/J273)</f>
         <v/>
       </c>
-      <c r="S273" s="10" t="str">
+      <c r="S273" s="12" t="str">
+        <f aca="false">IF(C273="","",N(M273)*پارامترها!$B$6+N(N273)*پارامترها!$B$7+N(O273)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T273" s="12" t="str">
+        <f aca="false">IF(C273="","",N(R273)+N(S273))</f>
+        <v/>
+      </c>
+      <c r="U273" s="10" t="str">
         <f aca="false">IF(C273="","",IF(P273&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L273)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T273" s="11"/>
+      <c r="V273" s="11"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="10" t="str">
@@ -11916,11 +14143,19 @@
         <f aca="false">IF(OR(C274="",N(J274)=0),"",K274*2*(N(H274)*پارامترها!$B$4+N(I274)*پارامترها!$B$5)/J274)</f>
         <v/>
       </c>
-      <c r="S274" s="10" t="str">
+      <c r="S274" s="12" t="str">
+        <f aca="false">IF(C274="","",N(M274)*پارامترها!$B$6+N(N274)*پارامترها!$B$7+N(O274)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T274" s="12" t="str">
+        <f aca="false">IF(C274="","",N(R274)+N(S274))</f>
+        <v/>
+      </c>
+      <c r="U274" s="10" t="str">
         <f aca="false">IF(C274="","",IF(P274&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L274)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T274" s="11"/>
+      <c r="V274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="10" t="str">
@@ -11956,11 +14191,19 @@
         <f aca="false">IF(OR(C275="",N(J275)=0),"",K275*2*(N(H275)*پارامترها!$B$4+N(I275)*پارامترها!$B$5)/J275)</f>
         <v/>
       </c>
-      <c r="S275" s="10" t="str">
+      <c r="S275" s="12" t="str">
+        <f aca="false">IF(C275="","",N(M275)*پارامترها!$B$6+N(N275)*پارامترها!$B$7+N(O275)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T275" s="12" t="str">
+        <f aca="false">IF(C275="","",N(R275)+N(S275))</f>
+        <v/>
+      </c>
+      <c r="U275" s="10" t="str">
         <f aca="false">IF(C275="","",IF(P275&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L275)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T275" s="11"/>
+      <c r="V275" s="11"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="10" t="str">
@@ -11996,11 +14239,19 @@
         <f aca="false">IF(OR(C276="",N(J276)=0),"",K276*2*(N(H276)*پارامترها!$B$4+N(I276)*پارامترها!$B$5)/J276)</f>
         <v/>
       </c>
-      <c r="S276" s="10" t="str">
+      <c r="S276" s="12" t="str">
+        <f aca="false">IF(C276="","",N(M276)*پارامترها!$B$6+N(N276)*پارامترها!$B$7+N(O276)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T276" s="12" t="str">
+        <f aca="false">IF(C276="","",N(R276)+N(S276))</f>
+        <v/>
+      </c>
+      <c r="U276" s="10" t="str">
         <f aca="false">IF(C276="","",IF(P276&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L276)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T276" s="11"/>
+      <c r="V276" s="11"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="10" t="str">
@@ -12036,11 +14287,19 @@
         <f aca="false">IF(OR(C277="",N(J277)=0),"",K277*2*(N(H277)*پارامترها!$B$4+N(I277)*پارامترها!$B$5)/J277)</f>
         <v/>
       </c>
-      <c r="S277" s="10" t="str">
+      <c r="S277" s="12" t="str">
+        <f aca="false">IF(C277="","",N(M277)*پارامترها!$B$6+N(N277)*پارامترها!$B$7+N(O277)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T277" s="12" t="str">
+        <f aca="false">IF(C277="","",N(R277)+N(S277))</f>
+        <v/>
+      </c>
+      <c r="U277" s="10" t="str">
         <f aca="false">IF(C277="","",IF(P277&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L277)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T277" s="11"/>
+      <c r="V277" s="11"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="10" t="str">
@@ -12076,11 +14335,19 @@
         <f aca="false">IF(OR(C278="",N(J278)=0),"",K278*2*(N(H278)*پارامترها!$B$4+N(I278)*پارامترها!$B$5)/J278)</f>
         <v/>
       </c>
-      <c r="S278" s="10" t="str">
+      <c r="S278" s="12" t="str">
+        <f aca="false">IF(C278="","",N(M278)*پارامترها!$B$6+N(N278)*پارامترها!$B$7+N(O278)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T278" s="12" t="str">
+        <f aca="false">IF(C278="","",N(R278)+N(S278))</f>
+        <v/>
+      </c>
+      <c r="U278" s="10" t="str">
         <f aca="false">IF(C278="","",IF(P278&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L278)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T278" s="11"/>
+      <c r="V278" s="11"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="10" t="str">
@@ -12116,11 +14383,19 @@
         <f aca="false">IF(OR(C279="",N(J279)=0),"",K279*2*(N(H279)*پارامترها!$B$4+N(I279)*پارامترها!$B$5)/J279)</f>
         <v/>
       </c>
-      <c r="S279" s="10" t="str">
+      <c r="S279" s="12" t="str">
+        <f aca="false">IF(C279="","",N(M279)*پارامترها!$B$6+N(N279)*پارامترها!$B$7+N(O279)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T279" s="12" t="str">
+        <f aca="false">IF(C279="","",N(R279)+N(S279))</f>
+        <v/>
+      </c>
+      <c r="U279" s="10" t="str">
         <f aca="false">IF(C279="","",IF(P279&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L279)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T279" s="11"/>
+      <c r="V279" s="11"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="10" t="str">
@@ -12156,11 +14431,19 @@
         <f aca="false">IF(OR(C280="",N(J280)=0),"",K280*2*(N(H280)*پارامترها!$B$4+N(I280)*پارامترها!$B$5)/J280)</f>
         <v/>
       </c>
-      <c r="S280" s="10" t="str">
+      <c r="S280" s="12" t="str">
+        <f aca="false">IF(C280="","",N(M280)*پارامترها!$B$6+N(N280)*پارامترها!$B$7+N(O280)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T280" s="12" t="str">
+        <f aca="false">IF(C280="","",N(R280)+N(S280))</f>
+        <v/>
+      </c>
+      <c r="U280" s="10" t="str">
         <f aca="false">IF(C280="","",IF(P280&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L280)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T280" s="11"/>
+      <c r="V280" s="11"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="10" t="str">
@@ -12196,11 +14479,19 @@
         <f aca="false">IF(OR(C281="",N(J281)=0),"",K281*2*(N(H281)*پارامترها!$B$4+N(I281)*پارامترها!$B$5)/J281)</f>
         <v/>
       </c>
-      <c r="S281" s="10" t="str">
+      <c r="S281" s="12" t="str">
+        <f aca="false">IF(C281="","",N(M281)*پارامترها!$B$6+N(N281)*پارامترها!$B$7+N(O281)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T281" s="12" t="str">
+        <f aca="false">IF(C281="","",N(R281)+N(S281))</f>
+        <v/>
+      </c>
+      <c r="U281" s="10" t="str">
         <f aca="false">IF(C281="","",IF(P281&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L281)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T281" s="11"/>
+      <c r="V281" s="11"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="10" t="str">
@@ -12236,11 +14527,19 @@
         <f aca="false">IF(OR(C282="",N(J282)=0),"",K282*2*(N(H282)*پارامترها!$B$4+N(I282)*پارامترها!$B$5)/J282)</f>
         <v/>
       </c>
-      <c r="S282" s="10" t="str">
+      <c r="S282" s="12" t="str">
+        <f aca="false">IF(C282="","",N(M282)*پارامترها!$B$6+N(N282)*پارامترها!$B$7+N(O282)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T282" s="12" t="str">
+        <f aca="false">IF(C282="","",N(R282)+N(S282))</f>
+        <v/>
+      </c>
+      <c r="U282" s="10" t="str">
         <f aca="false">IF(C282="","",IF(P282&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L282)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T282" s="11"/>
+      <c r="V282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="10" t="str">
@@ -12276,11 +14575,19 @@
         <f aca="false">IF(OR(C283="",N(J283)=0),"",K283*2*(N(H283)*پارامترها!$B$4+N(I283)*پارامترها!$B$5)/J283)</f>
         <v/>
       </c>
-      <c r="S283" s="10" t="str">
+      <c r="S283" s="12" t="str">
+        <f aca="false">IF(C283="","",N(M283)*پارامترها!$B$6+N(N283)*پارامترها!$B$7+N(O283)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T283" s="12" t="str">
+        <f aca="false">IF(C283="","",N(R283)+N(S283))</f>
+        <v/>
+      </c>
+      <c r="U283" s="10" t="str">
         <f aca="false">IF(C283="","",IF(P283&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L283)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T283" s="11"/>
+      <c r="V283" s="11"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="10" t="str">
@@ -12316,11 +14623,19 @@
         <f aca="false">IF(OR(C284="",N(J284)=0),"",K284*2*(N(H284)*پارامترها!$B$4+N(I284)*پارامترها!$B$5)/J284)</f>
         <v/>
       </c>
-      <c r="S284" s="10" t="str">
+      <c r="S284" s="12" t="str">
+        <f aca="false">IF(C284="","",N(M284)*پارامترها!$B$6+N(N284)*پارامترها!$B$7+N(O284)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T284" s="12" t="str">
+        <f aca="false">IF(C284="","",N(R284)+N(S284))</f>
+        <v/>
+      </c>
+      <c r="U284" s="10" t="str">
         <f aca="false">IF(C284="","",IF(P284&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L284)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T284" s="11"/>
+      <c r="V284" s="11"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="10" t="str">
@@ -12356,11 +14671,19 @@
         <f aca="false">IF(OR(C285="",N(J285)=0),"",K285*2*(N(H285)*پارامترها!$B$4+N(I285)*پارامترها!$B$5)/J285)</f>
         <v/>
       </c>
-      <c r="S285" s="10" t="str">
+      <c r="S285" s="12" t="str">
+        <f aca="false">IF(C285="","",N(M285)*پارامترها!$B$6+N(N285)*پارامترها!$B$7+N(O285)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T285" s="12" t="str">
+        <f aca="false">IF(C285="","",N(R285)+N(S285))</f>
+        <v/>
+      </c>
+      <c r="U285" s="10" t="str">
         <f aca="false">IF(C285="","",IF(P285&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L285)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T285" s="11"/>
+      <c r="V285" s="11"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="10" t="str">
@@ -12396,11 +14719,19 @@
         <f aca="false">IF(OR(C286="",N(J286)=0),"",K286*2*(N(H286)*پارامترها!$B$4+N(I286)*پارامترها!$B$5)/J286)</f>
         <v/>
       </c>
-      <c r="S286" s="10" t="str">
+      <c r="S286" s="12" t="str">
+        <f aca="false">IF(C286="","",N(M286)*پارامترها!$B$6+N(N286)*پارامترها!$B$7+N(O286)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T286" s="12" t="str">
+        <f aca="false">IF(C286="","",N(R286)+N(S286))</f>
+        <v/>
+      </c>
+      <c r="U286" s="10" t="str">
         <f aca="false">IF(C286="","",IF(P286&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L286)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T286" s="11"/>
+      <c r="V286" s="11"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="10" t="str">
@@ -12436,11 +14767,19 @@
         <f aca="false">IF(OR(C287="",N(J287)=0),"",K287*2*(N(H287)*پارامترها!$B$4+N(I287)*پارامترها!$B$5)/J287)</f>
         <v/>
       </c>
-      <c r="S287" s="10" t="str">
+      <c r="S287" s="12" t="str">
+        <f aca="false">IF(C287="","",N(M287)*پارامترها!$B$6+N(N287)*پارامترها!$B$7+N(O287)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T287" s="12" t="str">
+        <f aca="false">IF(C287="","",N(R287)+N(S287))</f>
+        <v/>
+      </c>
+      <c r="U287" s="10" t="str">
         <f aca="false">IF(C287="","",IF(P287&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L287)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T287" s="11"/>
+      <c r="V287" s="11"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="10" t="str">
@@ -12476,11 +14815,19 @@
         <f aca="false">IF(OR(C288="",N(J288)=0),"",K288*2*(N(H288)*پارامترها!$B$4+N(I288)*پارامترها!$B$5)/J288)</f>
         <v/>
       </c>
-      <c r="S288" s="10" t="str">
+      <c r="S288" s="12" t="str">
+        <f aca="false">IF(C288="","",N(M288)*پارامترها!$B$6+N(N288)*پارامترها!$B$7+N(O288)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T288" s="12" t="str">
+        <f aca="false">IF(C288="","",N(R288)+N(S288))</f>
+        <v/>
+      </c>
+      <c r="U288" s="10" t="str">
         <f aca="false">IF(C288="","",IF(P288&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L288)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T288" s="11"/>
+      <c r="V288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="10" t="str">
@@ -12516,11 +14863,19 @@
         <f aca="false">IF(OR(C289="",N(J289)=0),"",K289*2*(N(H289)*پارامترها!$B$4+N(I289)*پارامترها!$B$5)/J289)</f>
         <v/>
       </c>
-      <c r="S289" s="10" t="str">
+      <c r="S289" s="12" t="str">
+        <f aca="false">IF(C289="","",N(M289)*پارامترها!$B$6+N(N289)*پارامترها!$B$7+N(O289)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T289" s="12" t="str">
+        <f aca="false">IF(C289="","",N(R289)+N(S289))</f>
+        <v/>
+      </c>
+      <c r="U289" s="10" t="str">
         <f aca="false">IF(C289="","",IF(P289&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L289)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T289" s="11"/>
+      <c r="V289" s="11"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="10" t="str">
@@ -12556,11 +14911,19 @@
         <f aca="false">IF(OR(C290="",N(J290)=0),"",K290*2*(N(H290)*پارامترها!$B$4+N(I290)*پارامترها!$B$5)/J290)</f>
         <v/>
       </c>
-      <c r="S290" s="10" t="str">
+      <c r="S290" s="12" t="str">
+        <f aca="false">IF(C290="","",N(M290)*پارامترها!$B$6+N(N290)*پارامترها!$B$7+N(O290)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T290" s="12" t="str">
+        <f aca="false">IF(C290="","",N(R290)+N(S290))</f>
+        <v/>
+      </c>
+      <c r="U290" s="10" t="str">
         <f aca="false">IF(C290="","",IF(P290&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L290)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T290" s="11"/>
+      <c r="V290" s="11"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="10" t="str">
@@ -12596,11 +14959,19 @@
         <f aca="false">IF(OR(C291="",N(J291)=0),"",K291*2*(N(H291)*پارامترها!$B$4+N(I291)*پارامترها!$B$5)/J291)</f>
         <v/>
       </c>
-      <c r="S291" s="10" t="str">
+      <c r="S291" s="12" t="str">
+        <f aca="false">IF(C291="","",N(M291)*پارامترها!$B$6+N(N291)*پارامترها!$B$7+N(O291)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T291" s="12" t="str">
+        <f aca="false">IF(C291="","",N(R291)+N(S291))</f>
+        <v/>
+      </c>
+      <c r="U291" s="10" t="str">
         <f aca="false">IF(C291="","",IF(P291&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L291)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T291" s="11"/>
+      <c r="V291" s="11"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="10" t="str">
@@ -12636,11 +15007,19 @@
         <f aca="false">IF(OR(C292="",N(J292)=0),"",K292*2*(N(H292)*پارامترها!$B$4+N(I292)*پارامترها!$B$5)/J292)</f>
         <v/>
       </c>
-      <c r="S292" s="10" t="str">
+      <c r="S292" s="12" t="str">
+        <f aca="false">IF(C292="","",N(M292)*پارامترها!$B$6+N(N292)*پارامترها!$B$7+N(O292)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T292" s="12" t="str">
+        <f aca="false">IF(C292="","",N(R292)+N(S292))</f>
+        <v/>
+      </c>
+      <c r="U292" s="10" t="str">
         <f aca="false">IF(C292="","",IF(P292&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L292)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T292" s="11"/>
+      <c r="V292" s="11"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="10" t="str">
@@ -12676,11 +15055,19 @@
         <f aca="false">IF(OR(C293="",N(J293)=0),"",K293*2*(N(H293)*پارامترها!$B$4+N(I293)*پارامترها!$B$5)/J293)</f>
         <v/>
       </c>
-      <c r="S293" s="10" t="str">
+      <c r="S293" s="12" t="str">
+        <f aca="false">IF(C293="","",N(M293)*پارامترها!$B$6+N(N293)*پارامترها!$B$7+N(O293)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T293" s="12" t="str">
+        <f aca="false">IF(C293="","",N(R293)+N(S293))</f>
+        <v/>
+      </c>
+      <c r="U293" s="10" t="str">
         <f aca="false">IF(C293="","",IF(P293&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L293)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T293" s="11"/>
+      <c r="V293" s="11"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="10" t="str">
@@ -12716,11 +15103,19 @@
         <f aca="false">IF(OR(C294="",N(J294)=0),"",K294*2*(N(H294)*پارامترها!$B$4+N(I294)*پارامترها!$B$5)/J294)</f>
         <v/>
       </c>
-      <c r="S294" s="10" t="str">
+      <c r="S294" s="12" t="str">
+        <f aca="false">IF(C294="","",N(M294)*پارامترها!$B$6+N(N294)*پارامترها!$B$7+N(O294)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T294" s="12" t="str">
+        <f aca="false">IF(C294="","",N(R294)+N(S294))</f>
+        <v/>
+      </c>
+      <c r="U294" s="10" t="str">
         <f aca="false">IF(C294="","",IF(P294&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L294)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T294" s="11"/>
+      <c r="V294" s="11"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="10" t="str">
@@ -12756,11 +15151,19 @@
         <f aca="false">IF(OR(C295="",N(J295)=0),"",K295*2*(N(H295)*پارامترها!$B$4+N(I295)*پارامترها!$B$5)/J295)</f>
         <v/>
       </c>
-      <c r="S295" s="10" t="str">
+      <c r="S295" s="12" t="str">
+        <f aca="false">IF(C295="","",N(M295)*پارامترها!$B$6+N(N295)*پارامترها!$B$7+N(O295)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T295" s="12" t="str">
+        <f aca="false">IF(C295="","",N(R295)+N(S295))</f>
+        <v/>
+      </c>
+      <c r="U295" s="10" t="str">
         <f aca="false">IF(C295="","",IF(P295&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L295)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T295" s="11"/>
+      <c r="V295" s="11"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="10" t="str">
@@ -12796,11 +15199,19 @@
         <f aca="false">IF(OR(C296="",N(J296)=0),"",K296*2*(N(H296)*پارامترها!$B$4+N(I296)*پارامترها!$B$5)/J296)</f>
         <v/>
       </c>
-      <c r="S296" s="10" t="str">
+      <c r="S296" s="12" t="str">
+        <f aca="false">IF(C296="","",N(M296)*پارامترها!$B$6+N(N296)*پارامترها!$B$7+N(O296)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T296" s="12" t="str">
+        <f aca="false">IF(C296="","",N(R296)+N(S296))</f>
+        <v/>
+      </c>
+      <c r="U296" s="10" t="str">
         <f aca="false">IF(C296="","",IF(P296&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L296)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T296" s="11"/>
+      <c r="V296" s="11"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="10" t="str">
@@ -12836,11 +15247,19 @@
         <f aca="false">IF(OR(C297="",N(J297)=0),"",K297*2*(N(H297)*پارامترها!$B$4+N(I297)*پارامترها!$B$5)/J297)</f>
         <v/>
       </c>
-      <c r="S297" s="10" t="str">
+      <c r="S297" s="12" t="str">
+        <f aca="false">IF(C297="","",N(M297)*پارامترها!$B$6+N(N297)*پارامترها!$B$7+N(O297)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T297" s="12" t="str">
+        <f aca="false">IF(C297="","",N(R297)+N(S297))</f>
+        <v/>
+      </c>
+      <c r="U297" s="10" t="str">
         <f aca="false">IF(C297="","",IF(P297&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L297)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T297" s="11"/>
+      <c r="V297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="10" t="str">
@@ -12876,11 +15295,19 @@
         <f aca="false">IF(OR(C298="",N(J298)=0),"",K298*2*(N(H298)*پارامترها!$B$4+N(I298)*پارامترها!$B$5)/J298)</f>
         <v/>
       </c>
-      <c r="S298" s="10" t="str">
+      <c r="S298" s="12" t="str">
+        <f aca="false">IF(C298="","",N(M298)*پارامترها!$B$6+N(N298)*پارامترها!$B$7+N(O298)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T298" s="12" t="str">
+        <f aca="false">IF(C298="","",N(R298)+N(S298))</f>
+        <v/>
+      </c>
+      <c r="U298" s="10" t="str">
         <f aca="false">IF(C298="","",IF(P298&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L298)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T298" s="11"/>
+      <c r="V298" s="11"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="10" t="str">
@@ -12916,11 +15343,19 @@
         <f aca="false">IF(OR(C299="",N(J299)=0),"",K299*2*(N(H299)*پارامترها!$B$4+N(I299)*پارامترها!$B$5)/J299)</f>
         <v/>
       </c>
-      <c r="S299" s="10" t="str">
+      <c r="S299" s="12" t="str">
+        <f aca="false">IF(C299="","",N(M299)*پارامترها!$B$6+N(N299)*پارامترها!$B$7+N(O299)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T299" s="12" t="str">
+        <f aca="false">IF(C299="","",N(R299)+N(S299))</f>
+        <v/>
+      </c>
+      <c r="U299" s="10" t="str">
         <f aca="false">IF(C299="","",IF(P299&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L299)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T299" s="11"/>
+      <c r="V299" s="11"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="10" t="str">
@@ -12956,11 +15391,19 @@
         <f aca="false">IF(OR(C300="",N(J300)=0),"",K300*2*(N(H300)*پارامترها!$B$4+N(I300)*پارامترها!$B$5)/J300)</f>
         <v/>
       </c>
-      <c r="S300" s="10" t="str">
+      <c r="S300" s="12" t="str">
+        <f aca="false">IF(C300="","",N(M300)*پارامترها!$B$6+N(N300)*پارامترها!$B$7+N(O300)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T300" s="12" t="str">
+        <f aca="false">IF(C300="","",N(R300)+N(S300))</f>
+        <v/>
+      </c>
+      <c r="U300" s="10" t="str">
         <f aca="false">IF(C300="","",IF(P300&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L300)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T300" s="11"/>
+      <c r="V300" s="11"/>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="10" t="str">
@@ -12996,11 +15439,19 @@
         <f aca="false">IF(OR(C301="",N(J301)=0),"",K301*2*(N(H301)*پارامترها!$B$4+N(I301)*پارامترها!$B$5)/J301)</f>
         <v/>
       </c>
-      <c r="S301" s="10" t="str">
+      <c r="S301" s="12" t="str">
+        <f aca="false">IF(C301="","",N(M301)*پارامترها!$B$6+N(N301)*پارامترها!$B$7+N(O301)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T301" s="12" t="str">
+        <f aca="false">IF(C301="","",N(R301)+N(S301))</f>
+        <v/>
+      </c>
+      <c r="U301" s="10" t="str">
         <f aca="false">IF(C301="","",IF(P301&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L301)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T301" s="11"/>
+      <c r="V301" s="11"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="10" t="str">
@@ -13036,11 +15487,19 @@
         <f aca="false">IF(OR(C302="",N(J302)=0),"",K302*2*(N(H302)*پارامترها!$B$4+N(I302)*پارامترها!$B$5)/J302)</f>
         <v/>
       </c>
-      <c r="S302" s="10" t="str">
+      <c r="S302" s="12" t="str">
+        <f aca="false">IF(C302="","",N(M302)*پارامترها!$B$6+N(N302)*پارامترها!$B$7+N(O302)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T302" s="12" t="str">
+        <f aca="false">IF(C302="","",N(R302)+N(S302))</f>
+        <v/>
+      </c>
+      <c r="U302" s="10" t="str">
         <f aca="false">IF(C302="","",IF(P302&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L302)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T302" s="11"/>
+      <c r="V302" s="11"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="10" t="str">
@@ -13076,11 +15535,19 @@
         <f aca="false">IF(OR(C303="",N(J303)=0),"",K303*2*(N(H303)*پارامترها!$B$4+N(I303)*پارامترها!$B$5)/J303)</f>
         <v/>
       </c>
-      <c r="S303" s="10" t="str">
+      <c r="S303" s="12" t="str">
+        <f aca="false">IF(C303="","",N(M303)*پارامترها!$B$6+N(N303)*پارامترها!$B$7+N(O303)*پارامترها!$B$8)</f>
+        <v/>
+      </c>
+      <c r="T303" s="12" t="str">
+        <f aca="false">IF(C303="","",N(R303)+N(S303))</f>
+        <v/>
+      </c>
+      <c r="U303" s="10" t="str">
         <f aca="false">IF(C303="","",IF(P303&lt;&gt;"بله","ثبت نشده در HIS",IF(N(L303)&gt;0,"ثبت‌شده؛ مازاد بر سقف","ثبت‌شده")))</f>
         <v/>
       </c>
-      <c r="T303" s="11"/>
+      <c r="V303" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L4:L303">
@@ -13088,9 +15555,9 @@
       <formula>AND(L4&lt;&gt;"",N(L4)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S303">
+  <conditionalFormatting sqref="U4:U303">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>S4="ثبت نشده در HIS"</formula>
+      <formula>U4="ثبت نشده در HIS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -13124,12 +15591,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -13148,7 +15615,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -13157,12 +15624,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTA('ثبت روزانه'!$C$4:$C$303)</f>
@@ -13171,7 +15638,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTIF('ثبت روزانه'!$P$4:$P$303,"بله")</f>
@@ -13180,7 +15647,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
@@ -13189,7 +15656,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">SUM('ثبت روزانه'!$J$4:$J$303)</f>
@@ -13198,7 +15665,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">SUM('ثبت روزانه'!$K$4:$K$303)</f>
@@ -13207,7 +15674,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">SUM('ثبت روزانه'!$L$4:$L$303)</f>
@@ -13216,7 +15683,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">COUNTIF('ثبت روزانه'!$L$4:$L$303,"&gt;0")</f>
@@ -13225,7 +15692,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">IFERROR(B6/B3,0)</f>
@@ -13234,7 +15701,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">SUM('ثبت روزانه'!$R$4:$R$303)</f>
@@ -13243,43 +15710,61 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B12" s="17" t="n">
-        <f aca="false">SUMIF('ثبت روزانه'!$P$4:$P$303,"&lt;&gt;بله",'ثبت روزانه'!$R$4:$R$303)</f>
+        <f aca="false">SUM('ثبت روزانه'!$M$4:$M$303)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B13" s="17" t="n">
-        <f aca="false">SUM('ثبت روزانه'!$M$4:$M$303)</f>
+        <f aca="false">SUM('ثبت روزانه'!$N$4:$N$303)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B14" s="17" t="n">
-        <f aca="false">SUM('ثبت روزانه'!$N$4:$N$303)</f>
+        <f aca="false">SUM('ثبت روزانه'!$O$4:$O$303)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B15" s="17" t="n">
-        <f aca="false">SUM('ثبت روزانه'!$O$4:$O$303)</f>
+        <f aca="false">SUM('ثبت روزانه'!$S$4:$S$303)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>59</v>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <f aca="false">SUM('ثبت روزانه'!$T$4:$T$303)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <f aca="false">SUMIF('ثبت روزانه'!$P$4:$P$303,"&lt;&gt;بله",'ثبت روزانه'!$T$4:$T$303)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
